--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -1079,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373673</v>
+        <v>128374165</v>
       </c>
       <c r="B6" t="n">
         <v>79031</v>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440297</v>
+        <v>440024</v>
       </c>
       <c r="R6" t="n">
-        <v>6763071</v>
+        <v>6762784</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373475</v>
+        <v>128374108</v>
       </c>
       <c r="B7" t="n">
         <v>79031</v>
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440406</v>
+        <v>439941</v>
       </c>
       <c r="R7" t="n">
-        <v>6763080</v>
+        <v>6762833</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,48 +1281,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373481</v>
+        <v>128374324</v>
       </c>
       <c r="B8" t="n">
-        <v>79031</v>
+        <v>96598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440418</v>
+        <v>440191</v>
       </c>
       <c r="R8" t="n">
-        <v>6763099</v>
+        <v>6762689</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,7 +1383,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373878</v>
+        <v>128373673</v>
       </c>
       <c r="B9" t="n">
         <v>79031</v>
@@ -1420,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440202</v>
+        <v>440297</v>
       </c>
       <c r="R9" t="n">
-        <v>6763032</v>
+        <v>6763071</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1483,7 +1484,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373873</v>
+        <v>128373475</v>
       </c>
       <c r="B10" t="n">
         <v>79031</v>
@@ -1521,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440201</v>
+        <v>440406</v>
       </c>
       <c r="R10" t="n">
-        <v>6763012</v>
+        <v>6763080</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1584,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373860</v>
+        <v>128373481</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,31 +1596,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1627,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440187</v>
+        <v>440418</v>
       </c>
       <c r="R11" t="n">
-        <v>6763085</v>
+        <v>6763099</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1665,17 +1661,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1694,7 +1686,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373899</v>
+        <v>128373878</v>
       </c>
       <c r="B12" t="n">
         <v>79031</v>
@@ -1732,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440199</v>
+        <v>440202</v>
       </c>
       <c r="R12" t="n">
-        <v>6762979</v>
+        <v>6763032</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1795,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374165</v>
+        <v>128373873</v>
       </c>
       <c r="B13" t="n">
         <v>79031</v>
@@ -1833,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440024</v>
+        <v>440201</v>
       </c>
       <c r="R13" t="n">
-        <v>6762784</v>
+        <v>6763012</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1896,10 +1888,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374108</v>
+        <v>128373860</v>
       </c>
       <c r="B14" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1907,26 +1899,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1934,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439941</v>
+        <v>440187</v>
       </c>
       <c r="R14" t="n">
-        <v>6762833</v>
+        <v>6763085</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1972,13 +1969,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1997,49 +1998,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128374324</v>
+        <v>128373899</v>
       </c>
       <c r="B15" t="n">
-        <v>96598</v>
+        <v>79031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440191</v>
+        <v>440199</v>
       </c>
       <c r="R15" t="n">
-        <v>6762689</v>
+        <v>6762979</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -4443,49 +4443,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128374321</v>
+        <v>128373747</v>
       </c>
       <c r="B39" t="n">
-        <v>96598</v>
+        <v>79031</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440185</v>
+        <v>440332</v>
       </c>
       <c r="R39" t="n">
-        <v>6762702</v>
+        <v>6762998</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4545,48 +4544,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374129</v>
+        <v>128374321</v>
       </c>
       <c r="B40" t="n">
-        <v>79031</v>
+        <v>96598</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439996</v>
+        <v>440185</v>
       </c>
       <c r="R40" t="n">
-        <v>6762772</v>
+        <v>6762702</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128373747</v>
+        <v>128374129</v>
       </c>
       <c r="B41" t="n">
         <v>79031</v>
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440332</v>
+        <v>439996</v>
       </c>
       <c r="R41" t="n">
-        <v>6762998</v>
+        <v>6762772</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373403</v>
+        <v>128373782</v>
       </c>
       <c r="B51" t="n">
-        <v>79031</v>
+        <v>91375</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5673,24 +5673,28 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -5700,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440444</v>
+        <v>440285</v>
       </c>
       <c r="R51" t="n">
-        <v>6763182</v>
+        <v>6762985</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,10 +5767,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373782</v>
+        <v>128373752</v>
       </c>
       <c r="B52" t="n">
-        <v>91375</v>
+        <v>79031</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5774,28 +5778,24 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440285</v>
+        <v>440310</v>
       </c>
       <c r="R52" t="n">
-        <v>6762985</v>
+        <v>6762992</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5868,7 +5868,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373752</v>
+        <v>128373403</v>
       </c>
       <c r="B53" t="n">
         <v>79031</v>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440310</v>
+        <v>440444</v>
       </c>
       <c r="R53" t="n">
-        <v>6762992</v>
+        <v>6763182</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128374441</v>
+        <v>128373817</v>
       </c>
       <c r="B4" t="n">
         <v>79031</v>
@@ -911,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440344</v>
+        <v>440235</v>
       </c>
       <c r="R4" t="n">
-        <v>6762829</v>
+        <v>6763090</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373817</v>
+        <v>128374441</v>
       </c>
       <c r="B5" t="n">
         <v>79031</v>
@@ -1012,14 +1012,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440235</v>
+        <v>440344</v>
       </c>
       <c r="R5" t="n">
-        <v>6763090</v>
+        <v>6762829</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -3620,54 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374425</v>
+        <v>128373374</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79031</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440328</v>
+        <v>440502</v>
       </c>
       <c r="R31" t="n">
-        <v>6762829</v>
+        <v>6763186</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3727,37 +3721,43 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374437</v>
+        <v>128374425</v>
       </c>
       <c r="B32" t="n">
-        <v>79031</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440322</v>
+        <v>440328</v>
       </c>
       <c r="R32" t="n">
-        <v>6762821</v>
+        <v>6762829</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128373955</v>
+        <v>128374437</v>
       </c>
       <c r="B33" t="n">
         <v>79031</v>
@@ -3862,14 +3862,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440100</v>
+        <v>440322</v>
       </c>
       <c r="R33" t="n">
-        <v>6762947</v>
+        <v>6762821</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3929,7 +3929,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373374</v>
+        <v>128373955</v>
       </c>
       <c r="B34" t="n">
         <v>79031</v>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440502</v>
+        <v>440100</v>
       </c>
       <c r="R34" t="n">
-        <v>6763186</v>
+        <v>6762947</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128373817</v>
+        <v>128374441</v>
       </c>
       <c r="B4" t="n">
         <v>79031</v>
@@ -911,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440235</v>
+        <v>440344</v>
       </c>
       <c r="R4" t="n">
-        <v>6763090</v>
+        <v>6762829</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128374441</v>
+        <v>128373817</v>
       </c>
       <c r="B5" t="n">
         <v>79031</v>
@@ -1012,14 +1012,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440344</v>
+        <v>440235</v>
       </c>
       <c r="R5" t="n">
-        <v>6762829</v>
+        <v>6763090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128374454</v>
+        <v>128373960</v>
       </c>
       <c r="B27" t="n">
         <v>79031</v>
@@ -3250,14 +3250,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440400</v>
+        <v>440101</v>
       </c>
       <c r="R27" t="n">
-        <v>6762886</v>
+        <v>6762969</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3317,7 +3317,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128373960</v>
+        <v>128374000</v>
       </c>
       <c r="B28" t="n">
         <v>79031</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440101</v>
+        <v>440054</v>
       </c>
       <c r="R28" t="n">
-        <v>6762969</v>
+        <v>6762902</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128374000</v>
+        <v>128373992</v>
       </c>
       <c r="B29" t="n">
         <v>79031</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440054</v>
+        <v>440043</v>
       </c>
       <c r="R29" t="n">
-        <v>6762902</v>
+        <v>6762922</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128373992</v>
+        <v>128374454</v>
       </c>
       <c r="B30" t="n">
         <v>79031</v>
@@ -3553,14 +3553,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440043</v>
+        <v>440400</v>
       </c>
       <c r="R30" t="n">
-        <v>6762922</v>
+        <v>6762886</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3620,48 +3620,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128373374</v>
+        <v>128374425</v>
       </c>
       <c r="B31" t="n">
-        <v>79031</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440502</v>
+        <v>440328</v>
       </c>
       <c r="R31" t="n">
-        <v>6763186</v>
+        <v>6762829</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3721,43 +3727,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374425</v>
+        <v>128374437</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79031</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440328</v>
+        <v>440322</v>
       </c>
       <c r="R32" t="n">
-        <v>6762829</v>
+        <v>6762821</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128374437</v>
+        <v>128373955</v>
       </c>
       <c r="B33" t="n">
         <v>79031</v>
@@ -3862,14 +3862,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440322</v>
+        <v>440100</v>
       </c>
       <c r="R33" t="n">
-        <v>6762821</v>
+        <v>6762947</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3929,7 +3929,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373955</v>
+        <v>128373374</v>
       </c>
       <c r="B34" t="n">
         <v>79031</v>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440100</v>
+        <v>440502</v>
       </c>
       <c r="R34" t="n">
-        <v>6762947</v>
+        <v>6763186</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373782</v>
+        <v>128373403</v>
       </c>
       <c r="B51" t="n">
-        <v>91375</v>
+        <v>79031</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5673,28 +5673,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -5704,10 +5700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440285</v>
+        <v>440444</v>
       </c>
       <c r="R51" t="n">
-        <v>6762985</v>
+        <v>6763182</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5767,10 +5763,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373752</v>
+        <v>128373782</v>
       </c>
       <c r="B52" t="n">
-        <v>79031</v>
+        <v>91375</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5778,24 +5774,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440310</v>
+        <v>440285</v>
       </c>
       <c r="R52" t="n">
-        <v>6762992</v>
+        <v>6762985</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5868,7 +5868,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373403</v>
+        <v>128373752</v>
       </c>
       <c r="B53" t="n">
         <v>79031</v>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440444</v>
+        <v>440310</v>
       </c>
       <c r="R53" t="n">
-        <v>6763182</v>
+        <v>6762992</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128374441</v>
+        <v>128373817</v>
       </c>
       <c r="B4" t="n">
         <v>79031</v>
@@ -911,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440344</v>
+        <v>440235</v>
       </c>
       <c r="R4" t="n">
-        <v>6762829</v>
+        <v>6763090</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373817</v>
+        <v>128374441</v>
       </c>
       <c r="B5" t="n">
         <v>79031</v>
@@ -1012,14 +1012,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440235</v>
+        <v>440344</v>
       </c>
       <c r="R5" t="n">
-        <v>6763090</v>
+        <v>6762829</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374165</v>
+        <v>128373673</v>
       </c>
       <c r="B6" t="n">
         <v>79031</v>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440024</v>
+        <v>440297</v>
       </c>
       <c r="R6" t="n">
-        <v>6762784</v>
+        <v>6763071</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128374108</v>
+        <v>128373475</v>
       </c>
       <c r="B7" t="n">
         <v>79031</v>
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439941</v>
+        <v>440406</v>
       </c>
       <c r="R7" t="n">
-        <v>6762833</v>
+        <v>6763080</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,49 +1281,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374324</v>
+        <v>128373481</v>
       </c>
       <c r="B8" t="n">
-        <v>96598</v>
+        <v>79031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440191</v>
+        <v>440418</v>
       </c>
       <c r="R8" t="n">
-        <v>6762689</v>
+        <v>6763099</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1383,7 +1382,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373673</v>
+        <v>128373878</v>
       </c>
       <c r="B9" t="n">
         <v>79031</v>
@@ -1421,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440297</v>
+        <v>440202</v>
       </c>
       <c r="R9" t="n">
-        <v>6763071</v>
+        <v>6763032</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,7 +1483,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373475</v>
+        <v>128373873</v>
       </c>
       <c r="B10" t="n">
         <v>79031</v>
@@ -1522,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440406</v>
+        <v>440201</v>
       </c>
       <c r="R10" t="n">
-        <v>6763080</v>
+        <v>6763012</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373481</v>
+        <v>128373860</v>
       </c>
       <c r="B11" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,26 +1595,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1623,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440418</v>
+        <v>440187</v>
       </c>
       <c r="R11" t="n">
-        <v>6763099</v>
+        <v>6763085</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1661,13 +1665,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1686,7 +1694,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373878</v>
+        <v>128373899</v>
       </c>
       <c r="B12" t="n">
         <v>79031</v>
@@ -1724,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440202</v>
+        <v>440199</v>
       </c>
       <c r="R12" t="n">
-        <v>6763032</v>
+        <v>6762979</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1787,7 +1795,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128373873</v>
+        <v>128374165</v>
       </c>
       <c r="B13" t="n">
         <v>79031</v>
@@ -1825,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440201</v>
+        <v>440024</v>
       </c>
       <c r="R13" t="n">
-        <v>6763012</v>
+        <v>6762784</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,10 +1896,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128373860</v>
+        <v>128374108</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,31 +1907,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1931,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440187</v>
+        <v>439941</v>
       </c>
       <c r="R14" t="n">
-        <v>6763085</v>
+        <v>6762833</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1969,17 +1972,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1998,48 +1997,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128373899</v>
+        <v>128374324</v>
       </c>
       <c r="B15" t="n">
-        <v>79031</v>
+        <v>96598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440199</v>
+        <v>440191</v>
       </c>
       <c r="R15" t="n">
-        <v>6762979</v>
+        <v>6762689</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374321</v>
+        <v>128373466</v>
       </c>
       <c r="B40" t="n">
-        <v>96598</v>
+        <v>92645</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4555,38 +4555,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440185</v>
+        <v>440428</v>
       </c>
       <c r="R40" t="n">
-        <v>6762702</v>
+        <v>6763185</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4619,6 +4618,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4646,7 +4650,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128374129</v>
+        <v>128373380</v>
       </c>
       <c r="B41" t="n">
         <v>79031</v>
@@ -4684,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439996</v>
+        <v>440499</v>
       </c>
       <c r="R41" t="n">
-        <v>6762772</v>
+        <v>6763177</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4747,10 +4751,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373466</v>
+        <v>128374321</v>
       </c>
       <c r="B42" t="n">
-        <v>92645</v>
+        <v>96598</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4758,37 +4762,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440428</v>
+        <v>440185</v>
       </c>
       <c r="R42" t="n">
-        <v>6763185</v>
+        <v>6762702</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4821,11 +4826,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128373380</v>
+        <v>128374129</v>
       </c>
       <c r="B43" t="n">
         <v>79031</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440499</v>
+        <v>439996</v>
       </c>
       <c r="R43" t="n">
-        <v>6763177</v>
+        <v>6762772</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373403</v>
+        <v>128373782</v>
       </c>
       <c r="B51" t="n">
-        <v>79031</v>
+        <v>91375</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5673,24 +5673,28 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -5700,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440444</v>
+        <v>440285</v>
       </c>
       <c r="R51" t="n">
-        <v>6763182</v>
+        <v>6762985</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,10 +5767,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373782</v>
+        <v>128373752</v>
       </c>
       <c r="B52" t="n">
-        <v>91375</v>
+        <v>79031</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5774,28 +5778,24 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440285</v>
+        <v>440310</v>
       </c>
       <c r="R52" t="n">
-        <v>6762985</v>
+        <v>6762992</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5868,7 +5868,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373752</v>
+        <v>128373403</v>
       </c>
       <c r="B53" t="n">
         <v>79031</v>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440310</v>
+        <v>440444</v>
       </c>
       <c r="R53" t="n">
-        <v>6762992</v>
+        <v>6763182</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -7810,6 +7810,240 @@
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128464117</v>
+      </c>
+      <c r="B72" t="n">
+        <v>56864</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Skarpmyrbäcken, Skarpmyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>440375</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6763136</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Tjäderspillning nedanför betad Tall</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128463867</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skarpmyrbäcken, Skarpmyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>440308</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6763123</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Kåda</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373617</v>
+        <v>128373419</v>
       </c>
       <c r="B2" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440313</v>
+        <v>440412</v>
       </c>
       <c r="R2" t="n">
-        <v>6763067</v>
+        <v>6763165</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373419</v>
+        <v>128373617</v>
       </c>
       <c r="B3" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440412</v>
+        <v>440313</v>
       </c>
       <c r="R3" t="n">
-        <v>6763165</v>
+        <v>6763067</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128373817</v>
+        <v>128374441</v>
       </c>
       <c r="B4" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440235</v>
+        <v>440344</v>
       </c>
       <c r="R4" t="n">
-        <v>6763090</v>
+        <v>6762829</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128374441</v>
+        <v>128373817</v>
       </c>
       <c r="B5" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,14 +1012,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440344</v>
+        <v>440235</v>
       </c>
       <c r="R5" t="n">
-        <v>6762829</v>
+        <v>6763090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,48 +1079,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373673</v>
+        <v>128374324</v>
       </c>
       <c r="B6" t="n">
-        <v>79031</v>
+        <v>96603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440297</v>
+        <v>440191</v>
       </c>
       <c r="R6" t="n">
-        <v>6763071</v>
+        <v>6762689</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373475</v>
+        <v>128373673</v>
       </c>
       <c r="B7" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440406</v>
+        <v>440297</v>
       </c>
       <c r="R7" t="n">
-        <v>6763080</v>
+        <v>6763071</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373481</v>
+        <v>128373873</v>
       </c>
       <c r="B8" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440418</v>
+        <v>440201</v>
       </c>
       <c r="R8" t="n">
-        <v>6763099</v>
+        <v>6763012</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,10 +1383,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373878</v>
+        <v>128373899</v>
       </c>
       <c r="B9" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440202</v>
+        <v>440199</v>
       </c>
       <c r="R9" t="n">
-        <v>6763032</v>
+        <v>6762979</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1483,10 +1484,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373873</v>
+        <v>128373878</v>
       </c>
       <c r="B10" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440201</v>
+        <v>440202</v>
       </c>
       <c r="R10" t="n">
-        <v>6763012</v>
+        <v>6763032</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1584,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373860</v>
+        <v>128374165</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,31 +1596,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1627,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440187</v>
+        <v>440024</v>
       </c>
       <c r="R11" t="n">
-        <v>6763085</v>
+        <v>6762784</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1665,17 +1661,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1694,10 +1686,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373899</v>
+        <v>128373481</v>
       </c>
       <c r="B12" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1732,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440199</v>
+        <v>440418</v>
       </c>
       <c r="R12" t="n">
-        <v>6762979</v>
+        <v>6763099</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1795,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374165</v>
+        <v>128373475</v>
       </c>
       <c r="B13" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440024</v>
+        <v>440406</v>
       </c>
       <c r="R13" t="n">
-        <v>6762784</v>
+        <v>6763080</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1899,7 +1891,7 @@
         <v>128374108</v>
       </c>
       <c r="B14" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,49 +1989,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128374324</v>
+        <v>128373860</v>
       </c>
       <c r="B15" t="n">
-        <v>96598</v>
+        <v>57673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440191</v>
+        <v>440187</v>
       </c>
       <c r="R15" t="n">
-        <v>6762689</v>
+        <v>6763085</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2074,13 +2070,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>128374090</v>
       </c>
       <c r="B16" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128373653</v>
+        <v>128373503</v>
       </c>
       <c r="B17" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440307</v>
+        <v>440401</v>
       </c>
       <c r="R17" t="n">
-        <v>6763084</v>
+        <v>6763097</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128373503</v>
+        <v>128373653</v>
       </c>
       <c r="B18" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440401</v>
+        <v>440307</v>
       </c>
       <c r="R18" t="n">
-        <v>6763097</v>
+        <v>6763084</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2512,7 +2512,7 @@
         <v>128373363</v>
       </c>
       <c r="B20" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>128374175</v>
       </c>
       <c r="B21" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2711,10 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128373390</v>
+        <v>128373893</v>
       </c>
       <c r="B22" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440462</v>
+        <v>440212</v>
       </c>
       <c r="R22" t="n">
-        <v>6763204</v>
+        <v>6762957</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2812,10 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128373893</v>
+        <v>128373390</v>
       </c>
       <c r="B23" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440212</v>
+        <v>440462</v>
       </c>
       <c r="R23" t="n">
-        <v>6762957</v>
+        <v>6763204</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128373743</v>
+        <v>128373738</v>
       </c>
       <c r="B24" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440346</v>
+        <v>440357</v>
       </c>
       <c r="R24" t="n">
-        <v>6763007</v>
+        <v>6763022</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3014,10 +3014,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128373797</v>
+        <v>128373743</v>
       </c>
       <c r="B25" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440232</v>
+        <v>440346</v>
       </c>
       <c r="R25" t="n">
-        <v>6763126</v>
+        <v>6763007</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3115,10 +3115,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128373738</v>
+        <v>128373797</v>
       </c>
       <c r="B26" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440357</v>
+        <v>440232</v>
       </c>
       <c r="R26" t="n">
-        <v>6763022</v>
+        <v>6763126</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128373960</v>
+        <v>128374000</v>
       </c>
       <c r="B27" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440101</v>
+        <v>440054</v>
       </c>
       <c r="R27" t="n">
-        <v>6762969</v>
+        <v>6762902</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128374000</v>
+        <v>128373960</v>
       </c>
       <c r="B28" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440054</v>
+        <v>440101</v>
       </c>
       <c r="R28" t="n">
-        <v>6762902</v>
+        <v>6762969</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128373992</v>
+        <v>128374454</v>
       </c>
       <c r="B29" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3452,14 +3452,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440043</v>
+        <v>440400</v>
       </c>
       <c r="R29" t="n">
-        <v>6762922</v>
+        <v>6762886</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128374454</v>
+        <v>128373992</v>
       </c>
       <c r="B30" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3553,14 +3553,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440400</v>
+        <v>440043</v>
       </c>
       <c r="R30" t="n">
-        <v>6762886</v>
+        <v>6762922</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3620,54 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374425</v>
+        <v>128373955</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440328</v>
+        <v>440100</v>
       </c>
       <c r="R31" t="n">
-        <v>6762829</v>
+        <v>6762947</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3727,10 +3721,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374437</v>
+        <v>128373374</v>
       </c>
       <c r="B32" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3761,14 +3755,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440322</v>
+        <v>440502</v>
       </c>
       <c r="R32" t="n">
-        <v>6762821</v>
+        <v>6763186</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3828,10 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128373955</v>
+        <v>128374114</v>
       </c>
       <c r="B33" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3866,10 +3860,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440100</v>
+        <v>439954</v>
       </c>
       <c r="R33" t="n">
-        <v>6762947</v>
+        <v>6762847</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3929,10 +3923,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373374</v>
+        <v>128374437</v>
       </c>
       <c r="B34" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3963,14 +3957,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440502</v>
+        <v>440322</v>
       </c>
       <c r="R34" t="n">
-        <v>6763186</v>
+        <v>6762821</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4030,48 +4024,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128374114</v>
+        <v>128374425</v>
       </c>
       <c r="B35" t="n">
-        <v>79031</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439954</v>
+        <v>440328</v>
       </c>
       <c r="R35" t="n">
-        <v>6762847</v>
+        <v>6762829</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4134,7 +4134,7 @@
         <v>128373433</v>
       </c>
       <c r="B36" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,31 +4243,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4275,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R37" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4313,17 +4308,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4342,10 +4333,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B38" t="n">
-        <v>79031</v>
+        <v>57673</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4353,26 +4344,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4380,10 +4376,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R38" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4418,13 +4414,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4443,48 +4443,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128373747</v>
+        <v>128374321</v>
       </c>
       <c r="B39" t="n">
-        <v>79031</v>
+        <v>96603</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440332</v>
+        <v>440185</v>
       </c>
       <c r="R39" t="n">
-        <v>6762998</v>
+        <v>6762702</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4544,32 +4545,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128373466</v>
+        <v>128374129</v>
       </c>
       <c r="B40" t="n">
-        <v>92645</v>
+        <v>79032</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4582,10 +4583,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440428</v>
+        <v>439996</v>
       </c>
       <c r="R40" t="n">
-        <v>6763185</v>
+        <v>6762772</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4618,11 +4619,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4653,7 +4649,7 @@
         <v>128373380</v>
       </c>
       <c r="B41" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4751,49 +4747,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128374321</v>
+        <v>128373747</v>
       </c>
       <c r="B42" t="n">
-        <v>96598</v>
+        <v>79032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440185</v>
+        <v>440332</v>
       </c>
       <c r="R42" t="n">
-        <v>6762702</v>
+        <v>6762998</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4853,32 +4848,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128374129</v>
+        <v>128373466</v>
       </c>
       <c r="B43" t="n">
-        <v>79031</v>
+        <v>92650</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4891,10 +4886,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439996</v>
+        <v>440428</v>
       </c>
       <c r="R43" t="n">
-        <v>6762772</v>
+        <v>6763185</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4927,6 +4922,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4954,49 +4954,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128374335</v>
+        <v>128373409</v>
       </c>
       <c r="B44" t="n">
-        <v>96598</v>
+        <v>79032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440203</v>
+        <v>440432</v>
       </c>
       <c r="R44" t="n">
-        <v>6762697</v>
+        <v>6763202</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5056,10 +5055,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373809</v>
+        <v>128373813</v>
       </c>
       <c r="B45" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5094,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440239</v>
+        <v>440218</v>
       </c>
       <c r="R45" t="n">
-        <v>6763111</v>
+        <v>6763088</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5157,10 +5156,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373813</v>
+        <v>128374120</v>
       </c>
       <c r="B46" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5195,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440218</v>
+        <v>439959</v>
       </c>
       <c r="R46" t="n">
-        <v>6763088</v>
+        <v>6762821</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5261,7 +5260,7 @@
         <v>128373868</v>
       </c>
       <c r="B47" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5359,10 +5358,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128373409</v>
+        <v>128373809</v>
       </c>
       <c r="B48" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5397,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440432</v>
+        <v>440239</v>
       </c>
       <c r="R48" t="n">
-        <v>6763202</v>
+        <v>6763111</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5460,48 +5459,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128374120</v>
+        <v>128374335</v>
       </c>
       <c r="B49" t="n">
-        <v>79031</v>
+        <v>96603</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439959</v>
+        <v>440203</v>
       </c>
       <c r="R49" t="n">
-        <v>6762821</v>
+        <v>6762697</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373593</v>
+        <v>128373782</v>
       </c>
       <c r="B50" t="n">
-        <v>79031</v>
+        <v>91380</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,24 +5572,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5599,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440325</v>
+        <v>440285</v>
       </c>
       <c r="R50" t="n">
-        <v>6763069</v>
+        <v>6762985</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5662,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373782</v>
+        <v>128373593</v>
       </c>
       <c r="B51" t="n">
-        <v>91375</v>
+        <v>79032</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5673,28 +5677,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440285</v>
+        <v>440325</v>
       </c>
       <c r="R51" t="n">
-        <v>6762985</v>
+        <v>6763069</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5770,7 +5770,7 @@
         <v>128373752</v>
       </c>
       <c r="B52" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>128373403</v>
       </c>
       <c r="B53" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5969,10 +5969,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128373544</v>
+        <v>128373986</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,31 +5980,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6012,10 +6007,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440327</v>
+        <v>440031</v>
       </c>
       <c r="R54" t="n">
-        <v>6763083</v>
+        <v>6762895</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,17 +6045,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6082,7 +6073,7 @@
         <v>128374429</v>
       </c>
       <c r="B55" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6183,7 +6174,7 @@
         <v>128374431</v>
       </c>
       <c r="B56" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6281,10 +6272,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128373986</v>
+        <v>128374197</v>
       </c>
       <c r="B57" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6319,10 +6310,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440031</v>
+        <v>440001</v>
       </c>
       <c r="R57" t="n">
-        <v>6762895</v>
+        <v>6762789</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6382,10 +6373,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128374197</v>
+        <v>128373544</v>
       </c>
       <c r="B58" t="n">
-        <v>79031</v>
+        <v>57673</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6393,26 +6384,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6420,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440001</v>
+        <v>440327</v>
       </c>
       <c r="R58" t="n">
-        <v>6762789</v>
+        <v>6763083</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6458,13 +6454,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6483,42 +6483,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128373927</v>
+        <v>128373395</v>
       </c>
       <c r="B59" t="n">
-        <v>56864</v>
+        <v>79032</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6526,10 +6521,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440114</v>
+        <v>440451</v>
       </c>
       <c r="R59" t="n">
-        <v>6763007</v>
+        <v>6763197</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6570,6 +6565,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6588,37 +6584,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128373395</v>
+        <v>128373927</v>
       </c>
       <c r="B60" t="n">
-        <v>79031</v>
+        <v>56864</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6626,10 +6627,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440451</v>
+        <v>440114</v>
       </c>
       <c r="R60" t="n">
-        <v>6763197</v>
+        <v>6763007</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6670,7 +6671,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128373428</v>
+        <v>128373803</v>
       </c>
       <c r="B61" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440418</v>
+        <v>440226</v>
       </c>
       <c r="R61" t="n">
-        <v>6763150</v>
+        <v>6763108</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128373803</v>
+        <v>128373428</v>
       </c>
       <c r="B62" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6828,10 +6828,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440226</v>
+        <v>440418</v>
       </c>
       <c r="R62" t="n">
-        <v>6763108</v>
+        <v>6763150</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373976</v>
+        <v>128373958</v>
       </c>
       <c r="B63" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440119</v>
+        <v>440085</v>
       </c>
       <c r="R63" t="n">
         <v>6762953</v>
@@ -6992,43 +6992,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373939</v>
+        <v>128373976</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7036,10 +7030,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440091</v>
+        <v>440119</v>
       </c>
       <c r="R64" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7206,37 +7200,43 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373958</v>
+        <v>128373939</v>
       </c>
       <c r="B66" t="n">
-        <v>79031</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440085</v>
+        <v>440091</v>
       </c>
       <c r="R66" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7310,7 +7310,7 @@
         <v>128373912</v>
       </c>
       <c r="B67" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>128373683</v>
       </c>
       <c r="B68" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>128373907</v>
       </c>
       <c r="B69" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>128373339</v>
       </c>
       <c r="B70" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>128373758</v>
       </c>
       <c r="B71" t="n">
-        <v>78790</v>
+        <v>78791</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,26 +4243,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4270,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R37" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4308,13 +4313,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4333,10 +4342,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B38" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4344,31 +4353,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4376,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R38" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4414,17 +4418,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4954,48 +4954,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128373409</v>
+        <v>128374335</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>96603</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440432</v>
+        <v>440203</v>
       </c>
       <c r="R44" t="n">
-        <v>6763202</v>
+        <v>6762697</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5055,7 +5056,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373813</v>
+        <v>128373409</v>
       </c>
       <c r="B45" t="n">
         <v>79032</v>
@@ -5093,10 +5094,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440218</v>
+        <v>440432</v>
       </c>
       <c r="R45" t="n">
-        <v>6763088</v>
+        <v>6763202</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5156,7 +5157,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128374120</v>
+        <v>128373813</v>
       </c>
       <c r="B46" t="n">
         <v>79032</v>
@@ -5194,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439959</v>
+        <v>440218</v>
       </c>
       <c r="R46" t="n">
-        <v>6762821</v>
+        <v>6763088</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5257,7 +5258,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128373868</v>
+        <v>128374120</v>
       </c>
       <c r="B47" t="n">
         <v>79032</v>
@@ -5295,10 +5296,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440225</v>
+        <v>439959</v>
       </c>
       <c r="R47" t="n">
-        <v>6763025</v>
+        <v>6762821</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5358,7 +5359,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128373809</v>
+        <v>128373868</v>
       </c>
       <c r="B48" t="n">
         <v>79032</v>
@@ -5396,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440239</v>
+        <v>440225</v>
       </c>
       <c r="R48" t="n">
-        <v>6763111</v>
+        <v>6763025</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5459,49 +5460,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128374335</v>
+        <v>128373809</v>
       </c>
       <c r="B49" t="n">
-        <v>96603</v>
+        <v>79032</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440203</v>
+        <v>440239</v>
       </c>
       <c r="R49" t="n">
-        <v>6762697</v>
+        <v>6763111</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373419</v>
+        <v>128374441</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440412</v>
+        <v>440344</v>
       </c>
       <c r="R2" t="n">
-        <v>6763165</v>
+        <v>6762829</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373617</v>
+        <v>128373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440313</v>
+        <v>440412</v>
       </c>
       <c r="R3" t="n">
-        <v>6763067</v>
+        <v>6763165</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128374441</v>
+        <v>128373617</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440344</v>
+        <v>440313</v>
       </c>
       <c r="R4" t="n">
-        <v>6762829</v>
+        <v>6763067</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
         <v>128373817</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,49 +1079,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374324</v>
+        <v>128373475</v>
       </c>
       <c r="B6" t="n">
-        <v>96603</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440191</v>
+        <v>440406</v>
       </c>
       <c r="R6" t="n">
-        <v>6762689</v>
+        <v>6763080</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1181,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373673</v>
+        <v>128373860</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,26 +1191,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1219,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440297</v>
+        <v>440187</v>
       </c>
       <c r="R7" t="n">
-        <v>6763071</v>
+        <v>6763085</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,13 +1261,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1282,48 +1290,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373873</v>
+        <v>128374324</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>96696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440201</v>
+        <v>440191</v>
       </c>
       <c r="R8" t="n">
-        <v>6763012</v>
+        <v>6762689</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1386,7 +1395,7 @@
         <v>128373899</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373878</v>
+        <v>128373673</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440202</v>
+        <v>440297</v>
       </c>
       <c r="R10" t="n">
-        <v>6763032</v>
+        <v>6763071</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128374165</v>
+        <v>128373873</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440024</v>
+        <v>440201</v>
       </c>
       <c r="R11" t="n">
-        <v>6762784</v>
+        <v>6763012</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1686,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373481</v>
+        <v>128373878</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1724,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440418</v>
+        <v>440202</v>
       </c>
       <c r="R12" t="n">
-        <v>6763099</v>
+        <v>6763032</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1787,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128373475</v>
+        <v>128374165</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440406</v>
+        <v>440024</v>
       </c>
       <c r="R13" t="n">
-        <v>6763080</v>
+        <v>6762784</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374108</v>
+        <v>128373481</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439941</v>
+        <v>440418</v>
       </c>
       <c r="R14" t="n">
-        <v>6762833</v>
+        <v>6763099</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1989,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128373860</v>
+        <v>128374108</v>
       </c>
       <c r="B15" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,31 +2009,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2032,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440187</v>
+        <v>439941</v>
       </c>
       <c r="R15" t="n">
-        <v>6763085</v>
+        <v>6762833</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2070,17 +2074,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>128374090</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>128373503</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128373653</v>
       </c>
       <c r="B18" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128373363</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>128374175</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128373893</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>128373390</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128373738</v>
+        <v>128373797</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440357</v>
+        <v>440232</v>
       </c>
       <c r="R24" t="n">
-        <v>6763022</v>
+        <v>6763126</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3014,10 +3014,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128373743</v>
+        <v>128373738</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440346</v>
+        <v>440357</v>
       </c>
       <c r="R25" t="n">
-        <v>6763007</v>
+        <v>6763022</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3115,10 +3115,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128373797</v>
+        <v>128373743</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440232</v>
+        <v>440346</v>
       </c>
       <c r="R26" t="n">
-        <v>6763126</v>
+        <v>6763007</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128374000</v>
+        <v>128373960</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440054</v>
+        <v>440101</v>
       </c>
       <c r="R27" t="n">
-        <v>6762902</v>
+        <v>6762969</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128373960</v>
+        <v>128374000</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440101</v>
+        <v>440054</v>
       </c>
       <c r="R28" t="n">
-        <v>6762969</v>
+        <v>6762902</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3421,7 +3421,7 @@
         <v>128374454</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>128373992</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3620,48 +3620,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128373955</v>
+        <v>128374425</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440100</v>
+        <v>440328</v>
       </c>
       <c r="R31" t="n">
-        <v>6762947</v>
+        <v>6762829</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3721,10 +3727,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128373374</v>
+        <v>128374114</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3759,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440502</v>
+        <v>439954</v>
       </c>
       <c r="R32" t="n">
-        <v>6763186</v>
+        <v>6762847</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3822,10 +3828,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128374114</v>
+        <v>128374437</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,14 +3862,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439954</v>
+        <v>440322</v>
       </c>
       <c r="R33" t="n">
-        <v>6762847</v>
+        <v>6762821</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3923,10 +3929,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128374437</v>
+        <v>128373955</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3957,14 +3963,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440322</v>
+        <v>440100</v>
       </c>
       <c r="R34" t="n">
-        <v>6762821</v>
+        <v>6762947</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4024,54 +4030,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128374425</v>
+        <v>128373374</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440328</v>
+        <v>440502</v>
       </c>
       <c r="R35" t="n">
-        <v>6762829</v>
+        <v>6763186</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4134,7 +4134,7 @@
         <v>128373433</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B37" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,31 +4243,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4275,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R37" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4313,17 +4308,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4342,10 +4333,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4353,26 +4344,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4380,10 +4376,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R38" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4418,13 +4414,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4443,49 +4443,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128374321</v>
+        <v>128373747</v>
       </c>
       <c r="B39" t="n">
-        <v>96603</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440185</v>
+        <v>440332</v>
       </c>
       <c r="R39" t="n">
-        <v>6762702</v>
+        <v>6762998</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4545,48 +4544,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374129</v>
+        <v>128374321</v>
       </c>
       <c r="B40" t="n">
-        <v>79032</v>
+        <v>96696</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439996</v>
+        <v>440185</v>
       </c>
       <c r="R40" t="n">
-        <v>6762772</v>
+        <v>6762702</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4646,32 +4646,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128373380</v>
+        <v>128373466</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>92742</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440499</v>
+        <v>440428</v>
       </c>
       <c r="R41" t="n">
-        <v>6763177</v>
+        <v>6763185</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4720,6 +4720,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4747,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373747</v>
+        <v>128374129</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4785,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440332</v>
+        <v>439996</v>
       </c>
       <c r="R42" t="n">
-        <v>6762998</v>
+        <v>6762772</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4848,32 +4853,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128373466</v>
+        <v>128373380</v>
       </c>
       <c r="B43" t="n">
-        <v>92650</v>
+        <v>79083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4886,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440428</v>
+        <v>440499</v>
       </c>
       <c r="R43" t="n">
-        <v>6763185</v>
+        <v>6763177</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4922,11 +4927,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4954,49 +4954,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128374335</v>
+        <v>128373809</v>
       </c>
       <c r="B44" t="n">
-        <v>96603</v>
+        <v>79083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440203</v>
+        <v>440239</v>
       </c>
       <c r="R44" t="n">
-        <v>6762697</v>
+        <v>6763111</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5056,48 +5055,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373409</v>
+        <v>128374335</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>96696</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440432</v>
+        <v>440203</v>
       </c>
       <c r="R45" t="n">
-        <v>6763202</v>
+        <v>6762697</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373813</v>
+        <v>128373409</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440218</v>
+        <v>440432</v>
       </c>
       <c r="R46" t="n">
-        <v>6763088</v>
+        <v>6763202</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5258,10 +5258,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128374120</v>
+        <v>128373813</v>
       </c>
       <c r="B47" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439959</v>
+        <v>440218</v>
       </c>
       <c r="R47" t="n">
-        <v>6762821</v>
+        <v>6763088</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5362,7 +5362,7 @@
         <v>128373868</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5460,10 +5460,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128373809</v>
+        <v>128374120</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440239</v>
+        <v>439959</v>
       </c>
       <c r="R49" t="n">
-        <v>6763111</v>
+        <v>6762821</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5564,7 +5564,7 @@
         <v>128373782</v>
       </c>
       <c r="B50" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>128373593</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>128373752</v>
       </c>
       <c r="B52" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>128373403</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5969,10 +5969,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128373986</v>
+        <v>128373544</v>
       </c>
       <c r="B54" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,26 +5980,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6007,10 +6012,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440031</v>
+        <v>440327</v>
       </c>
       <c r="R54" t="n">
-        <v>6762895</v>
+        <v>6763083</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6045,13 +6050,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6070,10 +6079,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128374429</v>
+        <v>128374431</v>
       </c>
       <c r="B55" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6108,10 +6117,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440338</v>
+        <v>440332</v>
       </c>
       <c r="R55" t="n">
-        <v>6762836</v>
+        <v>6762821</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6171,10 +6180,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128374431</v>
+        <v>128374197</v>
       </c>
       <c r="B56" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6205,14 +6214,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440332</v>
+        <v>440001</v>
       </c>
       <c r="R56" t="n">
-        <v>6762821</v>
+        <v>6762789</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6272,10 +6281,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128374197</v>
+        <v>128373986</v>
       </c>
       <c r="B57" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6310,10 +6319,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440001</v>
+        <v>440031</v>
       </c>
       <c r="R57" t="n">
-        <v>6762789</v>
+        <v>6762895</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6373,10 +6382,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128373544</v>
+        <v>128374429</v>
       </c>
       <c r="B58" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6384,42 +6393,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440327</v>
+        <v>440338</v>
       </c>
       <c r="R58" t="n">
-        <v>6763083</v>
+        <v>6762836</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6454,17 +6458,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>128373395</v>
       </c>
       <c r="B59" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>128373927</v>
       </c>
       <c r="B60" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128373803</v>
+        <v>128373428</v>
       </c>
       <c r="B61" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440226</v>
+        <v>440418</v>
       </c>
       <c r="R61" t="n">
-        <v>6763108</v>
+        <v>6763150</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128373428</v>
+        <v>128373803</v>
       </c>
       <c r="B62" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6828,10 +6828,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440418</v>
+        <v>440226</v>
       </c>
       <c r="R62" t="n">
-        <v>6763150</v>
+        <v>6763108</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6891,37 +6891,43 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373958</v>
+        <v>128373935</v>
       </c>
       <c r="B63" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6929,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440085</v>
+        <v>440107</v>
       </c>
       <c r="R63" t="n">
-        <v>6762953</v>
+        <v>6762932</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6992,37 +6998,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373976</v>
+        <v>128373939</v>
       </c>
       <c r="B64" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7030,10 +7042,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440119</v>
+        <v>440091</v>
       </c>
       <c r="R64" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7093,43 +7105,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373935</v>
+        <v>128373958</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7137,10 +7143,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440107</v>
+        <v>440085</v>
       </c>
       <c r="R65" t="n">
-        <v>6762932</v>
+        <v>6762953</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7200,43 +7206,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373939</v>
+        <v>128373976</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440091</v>
+        <v>440119</v>
       </c>
       <c r="R66" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7310,7 +7310,7 @@
         <v>128373912</v>
       </c>
       <c r="B67" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128373683</v>
+        <v>128373907</v>
       </c>
       <c r="B68" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440312</v>
+        <v>440185</v>
       </c>
       <c r="R68" t="n">
-        <v>6763096</v>
+        <v>6762972</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128373907</v>
+        <v>128373683</v>
       </c>
       <c r="B69" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440185</v>
+        <v>440312</v>
       </c>
       <c r="R69" t="n">
-        <v>6762972</v>
+        <v>6763096</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7613,7 +7613,7 @@
         <v>128373339</v>
       </c>
       <c r="B70" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>128373758</v>
       </c>
       <c r="B71" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>128464117</v>
       </c>
       <c r="B72" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>128463867</v>
       </c>
       <c r="B73" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8043,6 +8043,355 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128532195</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Skarpmyrbäcken, Skarpmyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>440078</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6762917</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128463474</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Skarpmyrbäcken, Skarpmyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>440318</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6763131</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128535275</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>440421</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6762924</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -1079,48 +1079,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373475</v>
+        <v>128374324</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>96696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440406</v>
+        <v>440191</v>
       </c>
       <c r="R6" t="n">
-        <v>6763080</v>
+        <v>6762689</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373860</v>
+        <v>128373899</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,31 +1192,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1223,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440187</v>
+        <v>440199</v>
       </c>
       <c r="R7" t="n">
-        <v>6763085</v>
+        <v>6762979</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1261,17 +1257,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,49 +1282,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374324</v>
+        <v>128373673</v>
       </c>
       <c r="B8" t="n">
-        <v>96696</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440191</v>
+        <v>440297</v>
       </c>
       <c r="R8" t="n">
-        <v>6762689</v>
+        <v>6763071</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1392,7 +1383,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373899</v>
+        <v>128373873</v>
       </c>
       <c r="B9" t="n">
         <v>79083</v>
@@ -1430,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440199</v>
+        <v>440201</v>
       </c>
       <c r="R9" t="n">
-        <v>6762979</v>
+        <v>6763012</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1493,7 +1484,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373673</v>
+        <v>128373878</v>
       </c>
       <c r="B10" t="n">
         <v>79083</v>
@@ -1531,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440297</v>
+        <v>440202</v>
       </c>
       <c r="R10" t="n">
-        <v>6763071</v>
+        <v>6763032</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1594,7 +1585,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373873</v>
+        <v>128374165</v>
       </c>
       <c r="B11" t="n">
         <v>79083</v>
@@ -1632,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440201</v>
+        <v>440024</v>
       </c>
       <c r="R11" t="n">
-        <v>6763012</v>
+        <v>6762784</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1695,7 +1686,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373878</v>
+        <v>128373481</v>
       </c>
       <c r="B12" t="n">
         <v>79083</v>
@@ -1733,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440202</v>
+        <v>440418</v>
       </c>
       <c r="R12" t="n">
-        <v>6763032</v>
+        <v>6763099</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1796,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374165</v>
+        <v>128373475</v>
       </c>
       <c r="B13" t="n">
         <v>79083</v>
@@ -1834,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440024</v>
+        <v>440406</v>
       </c>
       <c r="R13" t="n">
-        <v>6762784</v>
+        <v>6763080</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1897,7 +1888,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128373481</v>
+        <v>128374108</v>
       </c>
       <c r="B14" t="n">
         <v>79083</v>
@@ -1935,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440418</v>
+        <v>439941</v>
       </c>
       <c r="R14" t="n">
-        <v>6763099</v>
+        <v>6762833</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1998,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128374108</v>
+        <v>128373860</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,26 +2000,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2036,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439941</v>
+        <v>440187</v>
       </c>
       <c r="R15" t="n">
-        <v>6762833</v>
+        <v>6763085</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2074,13 +2070,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2200,37 +2200,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128373503</v>
+        <v>128373765</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2238,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440401</v>
+        <v>440300</v>
       </c>
       <c r="R17" t="n">
-        <v>6763097</v>
+        <v>6762994</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2301,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128373653</v>
+        <v>128373503</v>
       </c>
       <c r="B18" t="n">
         <v>79083</v>
@@ -2339,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440307</v>
+        <v>440401</v>
       </c>
       <c r="R18" t="n">
-        <v>6763084</v>
+        <v>6763097</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2402,43 +2408,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128373765</v>
+        <v>128373653</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440300</v>
+        <v>440307</v>
       </c>
       <c r="R19" t="n">
-        <v>6762994</v>
+        <v>6763084</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128373960</v>
+        <v>128374000</v>
       </c>
       <c r="B27" t="n">
         <v>79083</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440101</v>
+        <v>440054</v>
       </c>
       <c r="R27" t="n">
-        <v>6762969</v>
+        <v>6762902</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3317,7 +3317,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128374000</v>
+        <v>128373960</v>
       </c>
       <c r="B28" t="n">
         <v>79083</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440054</v>
+        <v>440101</v>
       </c>
       <c r="R28" t="n">
-        <v>6762902</v>
+        <v>6762969</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3620,54 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374425</v>
+        <v>128374114</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440328</v>
+        <v>439954</v>
       </c>
       <c r="R31" t="n">
-        <v>6762829</v>
+        <v>6762847</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3727,7 +3721,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374114</v>
+        <v>128374437</v>
       </c>
       <c r="B32" t="n">
         <v>79083</v>
@@ -3761,14 +3755,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439954</v>
+        <v>440322</v>
       </c>
       <c r="R32" t="n">
-        <v>6762847</v>
+        <v>6762821</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3828,7 +3822,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128374437</v>
+        <v>128373955</v>
       </c>
       <c r="B33" t="n">
         <v>79083</v>
@@ -3862,14 +3856,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440322</v>
+        <v>440100</v>
       </c>
       <c r="R33" t="n">
-        <v>6762821</v>
+        <v>6762947</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3929,7 +3923,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373955</v>
+        <v>128373374</v>
       </c>
       <c r="B34" t="n">
         <v>79083</v>
@@ -3967,10 +3961,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440100</v>
+        <v>440502</v>
       </c>
       <c r="R34" t="n">
-        <v>6762947</v>
+        <v>6763186</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4030,48 +4024,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128373374</v>
+        <v>128374425</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440502</v>
+        <v>440328</v>
       </c>
       <c r="R35" t="n">
-        <v>6763186</v>
+        <v>6762829</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4443,32 +4443,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128373747</v>
+        <v>128373466</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440332</v>
+        <v>440428</v>
       </c>
       <c r="R39" t="n">
-        <v>6762998</v>
+        <v>6763185</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4517,6 +4517,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4544,49 +4549,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374321</v>
+        <v>128374129</v>
       </c>
       <c r="B40" t="n">
-        <v>96696</v>
+        <v>79083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440185</v>
+        <v>439996</v>
       </c>
       <c r="R40" t="n">
-        <v>6762702</v>
+        <v>6762772</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4646,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128373466</v>
+        <v>128373380</v>
       </c>
       <c r="B41" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4684,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440428</v>
+        <v>440499</v>
       </c>
       <c r="R41" t="n">
-        <v>6763185</v>
+        <v>6763177</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4720,11 +4724,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4752,7 +4751,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128374129</v>
+        <v>128373747</v>
       </c>
       <c r="B42" t="n">
         <v>79083</v>
@@ -4790,10 +4789,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439996</v>
+        <v>440332</v>
       </c>
       <c r="R42" t="n">
-        <v>6762772</v>
+        <v>6762998</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4853,48 +4852,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128373380</v>
+        <v>128374321</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>96696</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440499</v>
+        <v>440185</v>
       </c>
       <c r="R43" t="n">
-        <v>6763177</v>
+        <v>6762702</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4954,48 +4954,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128373809</v>
+        <v>128374335</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>96696</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440239</v>
+        <v>440203</v>
       </c>
       <c r="R44" t="n">
-        <v>6763111</v>
+        <v>6762697</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5055,49 +5056,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128374335</v>
+        <v>128373409</v>
       </c>
       <c r="B45" t="n">
-        <v>96696</v>
+        <v>79083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440203</v>
+        <v>440432</v>
       </c>
       <c r="R45" t="n">
-        <v>6762697</v>
+        <v>6763202</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5157,7 +5157,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373409</v>
+        <v>128373813</v>
       </c>
       <c r="B46" t="n">
         <v>79083</v>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440432</v>
+        <v>440218</v>
       </c>
       <c r="R46" t="n">
-        <v>6763202</v>
+        <v>6763088</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5258,7 +5258,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128373813</v>
+        <v>128373868</v>
       </c>
       <c r="B47" t="n">
         <v>79083</v>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440218</v>
+        <v>440225</v>
       </c>
       <c r="R47" t="n">
-        <v>6763088</v>
+        <v>6763025</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5359,7 +5359,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128373868</v>
+        <v>128374120</v>
       </c>
       <c r="B48" t="n">
         <v>79083</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440225</v>
+        <v>439959</v>
       </c>
       <c r="R48" t="n">
-        <v>6763025</v>
+        <v>6762821</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5460,7 +5460,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128374120</v>
+        <v>128373809</v>
       </c>
       <c r="B49" t="n">
         <v>79083</v>
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439959</v>
+        <v>440239</v>
       </c>
       <c r="R49" t="n">
-        <v>6762821</v>
+        <v>6763111</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373782</v>
+        <v>128373593</v>
       </c>
       <c r="B50" t="n">
-        <v>91472</v>
+        <v>79083</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,28 +5572,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5603,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440285</v>
+        <v>440325</v>
       </c>
       <c r="R50" t="n">
-        <v>6762985</v>
+        <v>6763069</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5666,7 +5662,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373593</v>
+        <v>128373752</v>
       </c>
       <c r="B51" t="n">
         <v>79083</v>
@@ -5704,10 +5700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440325</v>
+        <v>440310</v>
       </c>
       <c r="R51" t="n">
-        <v>6763069</v>
+        <v>6762992</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5767,7 +5763,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373752</v>
+        <v>128373403</v>
       </c>
       <c r="B52" t="n">
         <v>79083</v>
@@ -5805,10 +5801,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440310</v>
+        <v>440444</v>
       </c>
       <c r="R52" t="n">
-        <v>6762992</v>
+        <v>6763182</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5868,10 +5864,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373403</v>
+        <v>128373782</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>91472</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5879,24 +5875,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440444</v>
+        <v>440285</v>
       </c>
       <c r="R53" t="n">
-        <v>6763182</v>
+        <v>6762985</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5969,10 +5969,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128373544</v>
+        <v>128374431</v>
       </c>
       <c r="B54" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,42 +5980,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440327</v>
+        <v>440332</v>
       </c>
       <c r="R54" t="n">
-        <v>6763083</v>
+        <v>6762821</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,17 +6045,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6079,7 +6070,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128374431</v>
+        <v>128374197</v>
       </c>
       <c r="B55" t="n">
         <v>79083</v>
@@ -6113,14 +6104,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440332</v>
+        <v>440001</v>
       </c>
       <c r="R55" t="n">
-        <v>6762821</v>
+        <v>6762789</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6180,7 +6171,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128374197</v>
+        <v>128373986</v>
       </c>
       <c r="B56" t="n">
         <v>79083</v>
@@ -6218,10 +6209,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440001</v>
+        <v>440031</v>
       </c>
       <c r="R56" t="n">
-        <v>6762789</v>
+        <v>6762895</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6281,7 +6272,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128373986</v>
+        <v>128374429</v>
       </c>
       <c r="B57" t="n">
         <v>79083</v>
@@ -6315,14 +6306,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440031</v>
+        <v>440338</v>
       </c>
       <c r="R57" t="n">
-        <v>6762895</v>
+        <v>6762836</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6382,10 +6373,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128374429</v>
+        <v>128373544</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6393,37 +6384,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440338</v>
+        <v>440327</v>
       </c>
       <c r="R58" t="n">
-        <v>6762836</v>
+        <v>6763083</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6458,13 +6454,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6483,37 +6483,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128373395</v>
+        <v>128373927</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>56876</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6521,10 +6526,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440451</v>
+        <v>440114</v>
       </c>
       <c r="R59" t="n">
-        <v>6763197</v>
+        <v>6763007</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6565,7 +6570,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6584,42 +6588,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128373927</v>
+        <v>128373395</v>
       </c>
       <c r="B60" t="n">
-        <v>56876</v>
+        <v>79083</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6627,10 +6626,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440114</v>
+        <v>440451</v>
       </c>
       <c r="R60" t="n">
-        <v>6763007</v>
+        <v>6763197</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6671,6 +6670,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6689,7 +6689,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128373428</v>
+        <v>128373803</v>
       </c>
       <c r="B61" t="n">
         <v>79083</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440418</v>
+        <v>440226</v>
       </c>
       <c r="R61" t="n">
-        <v>6763150</v>
+        <v>6763108</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128373803</v>
+        <v>128373428</v>
       </c>
       <c r="B62" t="n">
         <v>79083</v>
@@ -6828,10 +6828,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440226</v>
+        <v>440418</v>
       </c>
       <c r="R62" t="n">
-        <v>6763108</v>
+        <v>6763150</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6891,43 +6891,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373935</v>
+        <v>128373958</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6935,10 +6929,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440107</v>
+        <v>440085</v>
       </c>
       <c r="R63" t="n">
-        <v>6762932</v>
+        <v>6762953</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6998,43 +6992,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373939</v>
+        <v>128373976</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7042,10 +7030,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440091</v>
+        <v>440119</v>
       </c>
       <c r="R64" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7105,37 +7093,43 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373958</v>
+        <v>128373935</v>
       </c>
       <c r="B65" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7143,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440085</v>
+        <v>440107</v>
       </c>
       <c r="R65" t="n">
-        <v>6762953</v>
+        <v>6762932</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7206,37 +7200,43 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373976</v>
+        <v>128373939</v>
       </c>
       <c r="B66" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440119</v>
+        <v>440091</v>
       </c>
       <c r="R66" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7408,7 +7408,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128373907</v>
+        <v>128373683</v>
       </c>
       <c r="B68" t="n">
         <v>79083</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440185</v>
+        <v>440312</v>
       </c>
       <c r="R68" t="n">
-        <v>6762972</v>
+        <v>6763096</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7509,7 +7509,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128373683</v>
+        <v>128373907</v>
       </c>
       <c r="B69" t="n">
         <v>79083</v>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440312</v>
+        <v>440185</v>
       </c>
       <c r="R69" t="n">
-        <v>6763096</v>
+        <v>6762972</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -1079,49 +1079,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374324</v>
+        <v>128373860</v>
       </c>
       <c r="B6" t="n">
-        <v>96696</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440191</v>
+        <v>440187</v>
       </c>
       <c r="R6" t="n">
-        <v>6762689</v>
+        <v>6763085</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1156,13 +1160,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1989,53 +1997,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128373860</v>
+        <v>128374324</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>96696</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440187</v>
+        <v>440191</v>
       </c>
       <c r="R15" t="n">
-        <v>6763085</v>
+        <v>6762689</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2070,17 +2074,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2200,43 +2200,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128373765</v>
+        <v>128373503</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2244,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440300</v>
+        <v>440401</v>
       </c>
       <c r="R17" t="n">
-        <v>6762994</v>
+        <v>6763097</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2307,7 +2301,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128373503</v>
+        <v>128373653</v>
       </c>
       <c r="B18" t="n">
         <v>79083</v>
@@ -2345,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440401</v>
+        <v>440307</v>
       </c>
       <c r="R18" t="n">
-        <v>6763097</v>
+        <v>6763084</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2408,37 +2402,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128373653</v>
+        <v>128373765</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440307</v>
+        <v>440300</v>
       </c>
       <c r="R19" t="n">
-        <v>6763084</v>
+        <v>6762994</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2711,7 +2711,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128373893</v>
+        <v>128373390</v>
       </c>
       <c r="B22" t="n">
         <v>79083</v>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440212</v>
+        <v>440462</v>
       </c>
       <c r="R22" t="n">
-        <v>6762957</v>
+        <v>6763204</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128373390</v>
+        <v>128373893</v>
       </c>
       <c r="B23" t="n">
         <v>79083</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440462</v>
+        <v>440212</v>
       </c>
       <c r="R23" t="n">
-        <v>6763204</v>
+        <v>6762957</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3620,48 +3620,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374114</v>
+        <v>128374425</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439954</v>
+        <v>440328</v>
       </c>
       <c r="R31" t="n">
-        <v>6762847</v>
+        <v>6762829</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3721,7 +3727,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374437</v>
+        <v>128374114</v>
       </c>
       <c r="B32" t="n">
         <v>79083</v>
@@ -3755,14 +3761,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440322</v>
+        <v>439954</v>
       </c>
       <c r="R32" t="n">
-        <v>6762821</v>
+        <v>6762847</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3822,7 +3828,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128373955</v>
+        <v>128374437</v>
       </c>
       <c r="B33" t="n">
         <v>79083</v>
@@ -3856,14 +3862,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440100</v>
+        <v>440322</v>
       </c>
       <c r="R33" t="n">
-        <v>6762947</v>
+        <v>6762821</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3923,7 +3929,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373374</v>
+        <v>128373955</v>
       </c>
       <c r="B34" t="n">
         <v>79083</v>
@@ -3961,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440502</v>
+        <v>440100</v>
       </c>
       <c r="R34" t="n">
-        <v>6763186</v>
+        <v>6762947</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4024,54 +4030,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128374425</v>
+        <v>128373374</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440328</v>
+        <v>440502</v>
       </c>
       <c r="R35" t="n">
-        <v>6762829</v>
+        <v>6763186</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,26 +4243,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4270,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R37" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4308,13 +4313,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4333,10 +4342,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B38" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4344,31 +4353,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4376,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R38" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4414,17 +4418,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4954,49 +4954,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128374335</v>
+        <v>128373409</v>
       </c>
       <c r="B44" t="n">
-        <v>96696</v>
+        <v>79083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440203</v>
+        <v>440432</v>
       </c>
       <c r="R44" t="n">
-        <v>6762697</v>
+        <v>6763202</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5056,7 +5055,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373409</v>
+        <v>128373813</v>
       </c>
       <c r="B45" t="n">
         <v>79083</v>
@@ -5094,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440432</v>
+        <v>440218</v>
       </c>
       <c r="R45" t="n">
-        <v>6763202</v>
+        <v>6763088</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5157,7 +5156,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373813</v>
+        <v>128373809</v>
       </c>
       <c r="B46" t="n">
         <v>79083</v>
@@ -5195,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440218</v>
+        <v>440239</v>
       </c>
       <c r="R46" t="n">
-        <v>6763088</v>
+        <v>6763111</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5258,48 +5257,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128373868</v>
+        <v>128374335</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>96696</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440225</v>
+        <v>440203</v>
       </c>
       <c r="R47" t="n">
-        <v>6763025</v>
+        <v>6762697</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5359,7 +5359,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128374120</v>
+        <v>128373868</v>
       </c>
       <c r="B48" t="n">
         <v>79083</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439959</v>
+        <v>440225</v>
       </c>
       <c r="R48" t="n">
-        <v>6762821</v>
+        <v>6763025</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5460,7 +5460,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128373809</v>
+        <v>128374120</v>
       </c>
       <c r="B49" t="n">
         <v>79083</v>
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440239</v>
+        <v>439959</v>
       </c>
       <c r="R49" t="n">
-        <v>6763111</v>
+        <v>6762821</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373593</v>
+        <v>128373782</v>
       </c>
       <c r="B50" t="n">
-        <v>79083</v>
+        <v>91472</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,24 +5572,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5599,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440325</v>
+        <v>440285</v>
       </c>
       <c r="R50" t="n">
-        <v>6763069</v>
+        <v>6762985</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5662,7 +5666,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373752</v>
+        <v>128373593</v>
       </c>
       <c r="B51" t="n">
         <v>79083</v>
@@ -5700,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440310</v>
+        <v>440325</v>
       </c>
       <c r="R51" t="n">
-        <v>6762992</v>
+        <v>6763069</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,7 +5767,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373403</v>
+        <v>128373752</v>
       </c>
       <c r="B52" t="n">
         <v>79083</v>
@@ -5801,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440444</v>
+        <v>440310</v>
       </c>
       <c r="R52" t="n">
-        <v>6763182</v>
+        <v>6762992</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5864,10 +5868,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373782</v>
+        <v>128373403</v>
       </c>
       <c r="B53" t="n">
-        <v>91472</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5875,28 +5879,24 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440285</v>
+        <v>440444</v>
       </c>
       <c r="R53" t="n">
-        <v>6762985</v>
+        <v>6763182</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6483,42 +6483,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128373927</v>
+        <v>128373395</v>
       </c>
       <c r="B59" t="n">
-        <v>56876</v>
+        <v>79083</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6526,10 +6521,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440114</v>
+        <v>440451</v>
       </c>
       <c r="R59" t="n">
-        <v>6763007</v>
+        <v>6763197</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6570,6 +6565,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6588,37 +6584,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128373395</v>
+        <v>128373927</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>56876</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6626,10 +6627,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440451</v>
+        <v>440114</v>
       </c>
       <c r="R60" t="n">
-        <v>6763197</v>
+        <v>6763007</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6670,7 +6671,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -2711,7 +2711,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128373390</v>
+        <v>128373893</v>
       </c>
       <c r="B22" t="n">
         <v>79083</v>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440462</v>
+        <v>440212</v>
       </c>
       <c r="R22" t="n">
-        <v>6763204</v>
+        <v>6762957</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128373893</v>
+        <v>128373390</v>
       </c>
       <c r="B23" t="n">
         <v>79083</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440212</v>
+        <v>440462</v>
       </c>
       <c r="R23" t="n">
-        <v>6762957</v>
+        <v>6763204</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128373683</v>
+        <v>128373758</v>
       </c>
       <c r="B68" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7419,21 +7419,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440312</v>
+        <v>440315</v>
       </c>
       <c r="R68" t="n">
-        <v>6763096</v>
+        <v>6763002</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7509,7 +7509,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128373907</v>
+        <v>128373683</v>
       </c>
       <c r="B69" t="n">
         <v>79083</v>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440185</v>
+        <v>440312</v>
       </c>
       <c r="R69" t="n">
-        <v>6762972</v>
+        <v>6763096</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7610,7 +7610,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128373339</v>
+        <v>128373907</v>
       </c>
       <c r="B70" t="n">
         <v>79083</v>
@@ -7648,10 +7648,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440512</v>
+        <v>440185</v>
       </c>
       <c r="R70" t="n">
-        <v>6763195</v>
+        <v>6762972</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128373758</v>
+        <v>128373339</v>
       </c>
       <c r="B71" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7722,21 +7722,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440315</v>
+        <v>440512</v>
       </c>
       <c r="R71" t="n">
-        <v>6763002</v>
+        <v>6763195</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7815,7 +7815,7 @@
         <v>128464117</v>
       </c>
       <c r="B72" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>128463867</v>
       </c>
       <c r="B73" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>128532195</v>
       </c>
       <c r="B74" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>128463474</v>
       </c>
       <c r="B75" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>128535275</v>
       </c>
       <c r="B76" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128374441</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128373617</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>128373817</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373860</v>
+        <v>128373899</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,31 +1090,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1122,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440187</v>
+        <v>440199</v>
       </c>
       <c r="R6" t="n">
-        <v>6763085</v>
+        <v>6762979</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,17 +1155,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373899</v>
+        <v>128373673</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440199</v>
+        <v>440297</v>
       </c>
       <c r="R7" t="n">
-        <v>6762979</v>
+        <v>6763071</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1290,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373673</v>
+        <v>128373873</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440297</v>
+        <v>440201</v>
       </c>
       <c r="R8" t="n">
-        <v>6763071</v>
+        <v>6763012</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1391,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373873</v>
+        <v>128373878</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440201</v>
+        <v>440202</v>
       </c>
       <c r="R9" t="n">
-        <v>6763012</v>
+        <v>6763032</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1492,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373878</v>
+        <v>128374165</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440202</v>
+        <v>440024</v>
       </c>
       <c r="R10" t="n">
-        <v>6763032</v>
+        <v>6762784</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128374165</v>
+        <v>128373481</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440024</v>
+        <v>440418</v>
       </c>
       <c r="R11" t="n">
-        <v>6762784</v>
+        <v>6763099</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1694,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373481</v>
+        <v>128373475</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1732,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440418</v>
+        <v>440406</v>
       </c>
       <c r="R12" t="n">
-        <v>6763099</v>
+        <v>6763080</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1795,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128373475</v>
+        <v>128374108</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440406</v>
+        <v>439941</v>
       </c>
       <c r="R13" t="n">
-        <v>6763080</v>
+        <v>6762833</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1896,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374108</v>
+        <v>128373860</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1907,26 +1898,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1934,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439941</v>
+        <v>440187</v>
       </c>
       <c r="R14" t="n">
-        <v>6762833</v>
+        <v>6763085</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1972,13 +1968,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>128374324</v>
       </c>
       <c r="B15" t="n">
-        <v>96696</v>
+        <v>96708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>128374090</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>128373503</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128373653</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128373363</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>128374175</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128373893</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>128373390</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>128373797</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128373738</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>128373743</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>128374000</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>128373960</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>128374454</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>128373992</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3620,54 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374425</v>
+        <v>128374114</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440328</v>
+        <v>439954</v>
       </c>
       <c r="R31" t="n">
-        <v>6762829</v>
+        <v>6762847</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3727,10 +3721,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374114</v>
+        <v>128374437</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3761,14 +3755,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439954</v>
+        <v>440322</v>
       </c>
       <c r="R32" t="n">
-        <v>6762847</v>
+        <v>6762821</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3828,10 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128374437</v>
+        <v>128373955</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,14 +3856,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440322</v>
+        <v>440100</v>
       </c>
       <c r="R33" t="n">
-        <v>6762821</v>
+        <v>6762947</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3929,10 +3923,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373955</v>
+        <v>128373374</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3967,10 +3961,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440100</v>
+        <v>440502</v>
       </c>
       <c r="R34" t="n">
-        <v>6762947</v>
+        <v>6763186</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4030,48 +4024,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128373374</v>
+        <v>128374425</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440502</v>
+        <v>440328</v>
       </c>
       <c r="R35" t="n">
-        <v>6763186</v>
+        <v>6762829</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4134,7 +4134,7 @@
         <v>128373433</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B37" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,31 +4243,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4275,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R37" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4313,17 +4308,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4342,10 +4333,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4353,26 +4344,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4380,10 +4376,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R38" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4418,13 +4414,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128373466</v>
+        <v>128374321</v>
       </c>
       <c r="B39" t="n">
-        <v>92742</v>
+        <v>96708</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4454,37 +4454,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440428</v>
+        <v>440185</v>
       </c>
       <c r="R39" t="n">
-        <v>6763185</v>
+        <v>6762702</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4517,11 +4518,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4549,10 +4545,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374129</v>
+        <v>128373747</v>
       </c>
       <c r="B40" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4587,10 +4583,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439996</v>
+        <v>440332</v>
       </c>
       <c r="R40" t="n">
-        <v>6762772</v>
+        <v>6762998</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4646,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128373380</v>
+        <v>128373466</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>92754</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,10 +4684,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440499</v>
+        <v>440428</v>
       </c>
       <c r="R41" t="n">
-        <v>6763177</v>
+        <v>6763185</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4724,6 +4720,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4751,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373747</v>
+        <v>128374129</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4789,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440332</v>
+        <v>439996</v>
       </c>
       <c r="R42" t="n">
-        <v>6762998</v>
+        <v>6762772</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4852,49 +4853,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128374321</v>
+        <v>128373380</v>
       </c>
       <c r="B43" t="n">
-        <v>96696</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440185</v>
+        <v>440499</v>
       </c>
       <c r="R43" t="n">
-        <v>6762702</v>
+        <v>6763177</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4957,7 +4957,7 @@
         <v>128373409</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>128373813</v>
       </c>
       <c r="B45" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373809</v>
+        <v>128373868</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440239</v>
+        <v>440225</v>
       </c>
       <c r="R46" t="n">
-        <v>6763111</v>
+        <v>6763025</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5257,49 +5257,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128374335</v>
+        <v>128374120</v>
       </c>
       <c r="B47" t="n">
-        <v>96696</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440203</v>
+        <v>439959</v>
       </c>
       <c r="R47" t="n">
-        <v>6762697</v>
+        <v>6762821</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5359,10 +5358,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128373868</v>
+        <v>128373809</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5397,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440225</v>
+        <v>440239</v>
       </c>
       <c r="R48" t="n">
-        <v>6763025</v>
+        <v>6763111</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5460,48 +5459,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128374120</v>
+        <v>128374335</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>96708</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439959</v>
+        <v>440203</v>
       </c>
       <c r="R49" t="n">
-        <v>6762821</v>
+        <v>6762697</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373782</v>
+        <v>128373593</v>
       </c>
       <c r="B50" t="n">
-        <v>91472</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,28 +5572,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5603,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440285</v>
+        <v>440325</v>
       </c>
       <c r="R50" t="n">
-        <v>6762985</v>
+        <v>6763069</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5666,10 +5662,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373593</v>
+        <v>128373752</v>
       </c>
       <c r="B51" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5704,10 +5700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440325</v>
+        <v>440310</v>
       </c>
       <c r="R51" t="n">
-        <v>6763069</v>
+        <v>6762992</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5767,10 +5763,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373752</v>
+        <v>128373403</v>
       </c>
       <c r="B52" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5805,10 +5801,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440310</v>
+        <v>440444</v>
       </c>
       <c r="R52" t="n">
-        <v>6762992</v>
+        <v>6763182</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5868,10 +5864,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373403</v>
+        <v>128373782</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>91484</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5879,24 +5875,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440444</v>
+        <v>440285</v>
       </c>
       <c r="R53" t="n">
-        <v>6763182</v>
+        <v>6762985</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5972,7 +5972,7 @@
         <v>128374431</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>128374197</v>
       </c>
       <c r="B55" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>128373986</v>
       </c>
       <c r="B56" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>128374429</v>
       </c>
       <c r="B57" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>128373544</v>
       </c>
       <c r="B58" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>128373395</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>128373927</v>
       </c>
       <c r="B60" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>128373803</v>
       </c>
       <c r="B61" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>128373428</v>
       </c>
       <c r="B62" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373958</v>
+        <v>128373976</v>
       </c>
       <c r="B63" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440085</v>
+        <v>440119</v>
       </c>
       <c r="R63" t="n">
         <v>6762953</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373976</v>
+        <v>128373958</v>
       </c>
       <c r="B64" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440119</v>
+        <v>440085</v>
       </c>
       <c r="R64" t="n">
         <v>6762953</v>
@@ -7310,7 +7310,7 @@
         <v>128373912</v>
       </c>
       <c r="B67" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128373758</v>
+        <v>128373683</v>
       </c>
       <c r="B68" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7419,21 +7419,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440315</v>
+        <v>440312</v>
       </c>
       <c r="R68" t="n">
-        <v>6763002</v>
+        <v>6763096</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128373683</v>
+        <v>128373907</v>
       </c>
       <c r="B69" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440312</v>
+        <v>440185</v>
       </c>
       <c r="R69" t="n">
-        <v>6763096</v>
+        <v>6762972</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7610,10 +7610,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128373907</v>
+        <v>128373339</v>
       </c>
       <c r="B70" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7648,10 +7648,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440185</v>
+        <v>440512</v>
       </c>
       <c r="R70" t="n">
-        <v>6762972</v>
+        <v>6763195</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128373339</v>
+        <v>128373758</v>
       </c>
       <c r="B71" t="n">
-        <v>79083</v>
+        <v>78845</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7722,21 +7722,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440512</v>
+        <v>440315</v>
       </c>
       <c r="R71" t="n">
-        <v>6763195</v>
+        <v>6763002</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -1079,48 +1079,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373899</v>
+        <v>128374324</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440199</v>
+        <v>440191</v>
       </c>
       <c r="R6" t="n">
-        <v>6762979</v>
+        <v>6762689</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,7 +1181,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373673</v>
+        <v>128373899</v>
       </c>
       <c r="B7" t="n">
         <v>79087</v>
@@ -1218,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440297</v>
+        <v>440199</v>
       </c>
       <c r="R7" t="n">
-        <v>6763071</v>
+        <v>6762979</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,7 +1282,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373873</v>
+        <v>128373673</v>
       </c>
       <c r="B8" t="n">
         <v>79087</v>
@@ -1319,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440201</v>
+        <v>440297</v>
       </c>
       <c r="R8" t="n">
-        <v>6763012</v>
+        <v>6763071</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,7 +1383,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373878</v>
+        <v>128373873</v>
       </c>
       <c r="B9" t="n">
         <v>79087</v>
@@ -1420,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440202</v>
+        <v>440201</v>
       </c>
       <c r="R9" t="n">
-        <v>6763032</v>
+        <v>6763012</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1483,7 +1484,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128374165</v>
+        <v>128373878</v>
       </c>
       <c r="B10" t="n">
         <v>79087</v>
@@ -1521,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440024</v>
+        <v>440202</v>
       </c>
       <c r="R10" t="n">
-        <v>6762784</v>
+        <v>6763032</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1584,7 +1585,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373481</v>
+        <v>128374165</v>
       </c>
       <c r="B11" t="n">
         <v>79087</v>
@@ -1622,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440418</v>
+        <v>440024</v>
       </c>
       <c r="R11" t="n">
-        <v>6763099</v>
+        <v>6762784</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1685,7 +1686,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373475</v>
+        <v>128373481</v>
       </c>
       <c r="B12" t="n">
         <v>79087</v>
@@ -1723,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440406</v>
+        <v>440418</v>
       </c>
       <c r="R12" t="n">
-        <v>6763080</v>
+        <v>6763099</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1786,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374108</v>
+        <v>128373475</v>
       </c>
       <c r="B13" t="n">
         <v>79087</v>
@@ -1824,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439941</v>
+        <v>440406</v>
       </c>
       <c r="R13" t="n">
-        <v>6762833</v>
+        <v>6763080</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1887,10 +1888,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128373860</v>
+        <v>128374108</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,31 +1899,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1930,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440187</v>
+        <v>439941</v>
       </c>
       <c r="R14" t="n">
-        <v>6763085</v>
+        <v>6762833</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1968,17 +1964,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1997,49 +1989,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128374324</v>
+        <v>128373860</v>
       </c>
       <c r="B15" t="n">
-        <v>96708</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440191</v>
+        <v>440187</v>
       </c>
       <c r="R15" t="n">
-        <v>6762689</v>
+        <v>6763085</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2074,13 +2070,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128374441</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128373617</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>128373817</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,49 +1079,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374324</v>
+        <v>128373899</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440191</v>
+        <v>440199</v>
       </c>
       <c r="R6" t="n">
-        <v>6762689</v>
+        <v>6762979</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1181,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373899</v>
+        <v>128373673</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440199</v>
+        <v>440297</v>
       </c>
       <c r="R7" t="n">
-        <v>6762979</v>
+        <v>6763071</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1282,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373673</v>
+        <v>128373873</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440297</v>
+        <v>440201</v>
       </c>
       <c r="R8" t="n">
-        <v>6763071</v>
+        <v>6763012</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1383,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373873</v>
+        <v>128373878</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440201</v>
+        <v>440202</v>
       </c>
       <c r="R9" t="n">
-        <v>6763012</v>
+        <v>6763032</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373878</v>
+        <v>128374165</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440202</v>
+        <v>440024</v>
       </c>
       <c r="R10" t="n">
-        <v>6763032</v>
+        <v>6762784</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128374165</v>
+        <v>128373481</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440024</v>
+        <v>440418</v>
       </c>
       <c r="R11" t="n">
-        <v>6762784</v>
+        <v>6763099</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1686,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373481</v>
+        <v>128373475</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1724,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440418</v>
+        <v>440406</v>
       </c>
       <c r="R12" t="n">
-        <v>6763099</v>
+        <v>6763080</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1787,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128373475</v>
+        <v>128374108</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440406</v>
+        <v>439941</v>
       </c>
       <c r="R13" t="n">
-        <v>6763080</v>
+        <v>6762833</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,48 +1887,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374108</v>
+        <v>128374324</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>96710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439941</v>
+        <v>440191</v>
       </c>
       <c r="R14" t="n">
-        <v>6762833</v>
+        <v>6762689</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2102,7 +2102,7 @@
         <v>128374090</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>128373503</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128373653</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128373363</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>128374175</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128373893</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>128373390</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>128373797</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128373738</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>128373743</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>128374000</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>128373960</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>128374454</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>128373992</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3620,48 +3620,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374114</v>
+        <v>128374425</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439954</v>
+        <v>440328</v>
       </c>
       <c r="R31" t="n">
-        <v>6762847</v>
+        <v>6762829</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3721,10 +3727,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374437</v>
+        <v>128374114</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3755,14 +3761,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440322</v>
+        <v>439954</v>
       </c>
       <c r="R32" t="n">
-        <v>6762821</v>
+        <v>6762847</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3822,10 +3828,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128373955</v>
+        <v>128374437</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,14 +3862,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440100</v>
+        <v>440322</v>
       </c>
       <c r="R33" t="n">
-        <v>6762947</v>
+        <v>6762821</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3923,10 +3929,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373374</v>
+        <v>128373955</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3961,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440502</v>
+        <v>440100</v>
       </c>
       <c r="R34" t="n">
-        <v>6763186</v>
+        <v>6762947</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4024,54 +4030,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128374425</v>
+        <v>128373374</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440328</v>
+        <v>440502</v>
       </c>
       <c r="R35" t="n">
-        <v>6762829</v>
+        <v>6763186</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4134,7 +4134,7 @@
         <v>128373433</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,26 +4243,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4270,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R37" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4308,13 +4313,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4333,10 +4342,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B38" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4344,31 +4353,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4376,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R38" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4414,17 +4418,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128374321</v>
+        <v>128373466</v>
       </c>
       <c r="B39" t="n">
-        <v>96708</v>
+        <v>92756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4454,38 +4454,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440185</v>
+        <v>440428</v>
       </c>
       <c r="R39" t="n">
-        <v>6762702</v>
+        <v>6763185</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4518,6 +4517,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4545,48 +4549,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128373747</v>
+        <v>128374321</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>96710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440332</v>
+        <v>440185</v>
       </c>
       <c r="R40" t="n">
-        <v>6762998</v>
+        <v>6762702</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4646,32 +4651,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128373466</v>
+        <v>128374129</v>
       </c>
       <c r="B41" t="n">
-        <v>92754</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4684,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440428</v>
+        <v>439996</v>
       </c>
       <c r="R41" t="n">
-        <v>6763185</v>
+        <v>6762772</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4720,11 +4725,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4752,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128374129</v>
+        <v>128373380</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439996</v>
+        <v>440499</v>
       </c>
       <c r="R42" t="n">
-        <v>6762772</v>
+        <v>6763177</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128373380</v>
+        <v>128373747</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440499</v>
+        <v>440332</v>
       </c>
       <c r="R43" t="n">
-        <v>6763177</v>
+        <v>6762998</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4954,48 +4954,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128373409</v>
+        <v>128374335</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>96710</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440432</v>
+        <v>440203</v>
       </c>
       <c r="R44" t="n">
-        <v>6763202</v>
+        <v>6762697</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5055,10 +5056,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373813</v>
+        <v>128373409</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5093,10 +5094,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440218</v>
+        <v>440432</v>
       </c>
       <c r="R45" t="n">
-        <v>6763088</v>
+        <v>6763202</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5156,10 +5157,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373868</v>
+        <v>128373813</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5194,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440225</v>
+        <v>440218</v>
       </c>
       <c r="R46" t="n">
-        <v>6763025</v>
+        <v>6763088</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5257,10 +5258,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128374120</v>
+        <v>128373868</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5295,10 +5296,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439959</v>
+        <v>440225</v>
       </c>
       <c r="R47" t="n">
-        <v>6762821</v>
+        <v>6763025</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5358,10 +5359,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128373809</v>
+        <v>128374120</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5396,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440239</v>
+        <v>439959</v>
       </c>
       <c r="R48" t="n">
-        <v>6763111</v>
+        <v>6762821</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5459,49 +5460,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128374335</v>
+        <v>128373809</v>
       </c>
       <c r="B49" t="n">
-        <v>96708</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440203</v>
+        <v>440239</v>
       </c>
       <c r="R49" t="n">
-        <v>6762697</v>
+        <v>6763111</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373593</v>
+        <v>128373782</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>91486</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,24 +5572,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5599,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440325</v>
+        <v>440285</v>
       </c>
       <c r="R50" t="n">
-        <v>6763069</v>
+        <v>6762985</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5662,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373752</v>
+        <v>128373403</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5700,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440310</v>
+        <v>440444</v>
       </c>
       <c r="R51" t="n">
-        <v>6762992</v>
+        <v>6763182</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,10 +5767,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373403</v>
+        <v>128373593</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5801,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440444</v>
+        <v>440325</v>
       </c>
       <c r="R52" t="n">
-        <v>6763182</v>
+        <v>6763069</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5864,10 +5868,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373782</v>
+        <v>128373752</v>
       </c>
       <c r="B53" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5875,28 +5879,24 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440285</v>
+        <v>440310</v>
       </c>
       <c r="R53" t="n">
-        <v>6762985</v>
+        <v>6762992</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5972,7 +5972,7 @@
         <v>128374431</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>128374197</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>128373986</v>
       </c>
       <c r="B56" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>128374429</v>
       </c>
       <c r="B57" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>128373395</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>128373803</v>
       </c>
       <c r="B61" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>128373428</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6891,37 +6891,43 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373976</v>
+        <v>128373935</v>
       </c>
       <c r="B63" t="n">
-        <v>79087</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6929,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440119</v>
+        <v>440107</v>
       </c>
       <c r="R63" t="n">
-        <v>6762953</v>
+        <v>6762932</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6992,37 +6998,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373958</v>
+        <v>128373939</v>
       </c>
       <c r="B64" t="n">
-        <v>79087</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7030,10 +7042,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440085</v>
+        <v>440091</v>
       </c>
       <c r="R64" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7093,43 +7105,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373935</v>
+        <v>128373958</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7137,10 +7143,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440107</v>
+        <v>440085</v>
       </c>
       <c r="R65" t="n">
-        <v>6762932</v>
+        <v>6762953</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7200,43 +7206,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373939</v>
+        <v>128373976</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440091</v>
+        <v>440119</v>
       </c>
       <c r="R66" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7310,7 +7310,7 @@
         <v>128373912</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>128373683</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>128373907</v>
       </c>
       <c r="B69" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>128373339</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>128373758</v>
       </c>
       <c r="B71" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373899</v>
+        <v>128373860</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,26 +1090,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1117,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440199</v>
+        <v>440187</v>
       </c>
       <c r="R6" t="n">
-        <v>6762979</v>
+        <v>6763085</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1155,13 +1160,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,48 +1189,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373673</v>
+        <v>128374324</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>96710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440297</v>
+        <v>440191</v>
       </c>
       <c r="R7" t="n">
-        <v>6763071</v>
+        <v>6762689</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373873</v>
+        <v>128373899</v>
       </c>
       <c r="B8" t="n">
         <v>79089</v>
@@ -1319,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440201</v>
+        <v>440199</v>
       </c>
       <c r="R8" t="n">
-        <v>6763012</v>
+        <v>6762979</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,7 +1392,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373878</v>
+        <v>128373673</v>
       </c>
       <c r="B9" t="n">
         <v>79089</v>
@@ -1420,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440202</v>
+        <v>440297</v>
       </c>
       <c r="R9" t="n">
-        <v>6763032</v>
+        <v>6763071</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1483,7 +1493,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128374165</v>
+        <v>128373873</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1521,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440024</v>
+        <v>440201</v>
       </c>
       <c r="R10" t="n">
-        <v>6762784</v>
+        <v>6763012</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1584,7 +1594,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373481</v>
+        <v>128373878</v>
       </c>
       <c r="B11" t="n">
         <v>79089</v>
@@ -1622,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440418</v>
+        <v>440202</v>
       </c>
       <c r="R11" t="n">
-        <v>6763099</v>
+        <v>6763032</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1685,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373475</v>
+        <v>128374165</v>
       </c>
       <c r="B12" t="n">
         <v>79089</v>
@@ -1723,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440406</v>
+        <v>440024</v>
       </c>
       <c r="R12" t="n">
-        <v>6763080</v>
+        <v>6762784</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1786,7 +1796,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374108</v>
+        <v>128373481</v>
       </c>
       <c r="B13" t="n">
         <v>79089</v>
@@ -1824,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439941</v>
+        <v>440418</v>
       </c>
       <c r="R13" t="n">
-        <v>6762833</v>
+        <v>6763099</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1887,49 +1897,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374324</v>
+        <v>128373475</v>
       </c>
       <c r="B14" t="n">
-        <v>96710</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440191</v>
+        <v>440406</v>
       </c>
       <c r="R14" t="n">
-        <v>6762689</v>
+        <v>6763080</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1989,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128373860</v>
+        <v>128374108</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,31 +2009,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2032,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440187</v>
+        <v>439941</v>
       </c>
       <c r="R15" t="n">
-        <v>6763085</v>
+        <v>6762833</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2070,17 +2074,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2200,37 +2200,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128373503</v>
+        <v>128373765</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2238,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440401</v>
+        <v>440300</v>
       </c>
       <c r="R17" t="n">
-        <v>6763097</v>
+        <v>6762994</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2301,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128373653</v>
+        <v>128373503</v>
       </c>
       <c r="B18" t="n">
         <v>79089</v>
@@ -2339,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440307</v>
+        <v>440401</v>
       </c>
       <c r="R18" t="n">
-        <v>6763084</v>
+        <v>6763097</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2402,43 +2408,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128373765</v>
+        <v>128373653</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440300</v>
+        <v>440307</v>
       </c>
       <c r="R19" t="n">
-        <v>6762994</v>
+        <v>6763084</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B37" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,31 +4243,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4275,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R37" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4313,17 +4308,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4342,10 +4333,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4353,26 +4344,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4380,10 +4376,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R38" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4418,13 +4414,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4443,32 +4443,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128373466</v>
+        <v>128374129</v>
       </c>
       <c r="B39" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440428</v>
+        <v>439996</v>
       </c>
       <c r="R39" t="n">
-        <v>6763185</v>
+        <v>6762772</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4517,11 +4517,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4549,49 +4544,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374321</v>
+        <v>128373380</v>
       </c>
       <c r="B40" t="n">
-        <v>96710</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440185</v>
+        <v>440499</v>
       </c>
       <c r="R40" t="n">
-        <v>6762702</v>
+        <v>6763177</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4651,7 +4645,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128374129</v>
+        <v>128373747</v>
       </c>
       <c r="B41" t="n">
         <v>79089</v>
@@ -4689,10 +4683,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439996</v>
+        <v>440332</v>
       </c>
       <c r="R41" t="n">
-        <v>6762772</v>
+        <v>6762998</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4752,32 +4746,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373380</v>
+        <v>128373466</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>92756</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4790,10 +4784,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440499</v>
+        <v>440428</v>
       </c>
       <c r="R42" t="n">
-        <v>6763177</v>
+        <v>6763185</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4826,6 +4820,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4853,48 +4852,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128373747</v>
+        <v>128374321</v>
       </c>
       <c r="B43" t="n">
-        <v>79089</v>
+        <v>96710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440332</v>
+        <v>440185</v>
       </c>
       <c r="R43" t="n">
-        <v>6762998</v>
+        <v>6762702</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373782</v>
+        <v>128373593</v>
       </c>
       <c r="B50" t="n">
-        <v>91486</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,28 +5572,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5603,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440285</v>
+        <v>440325</v>
       </c>
       <c r="R50" t="n">
-        <v>6762985</v>
+        <v>6763069</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5666,7 +5662,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373403</v>
+        <v>128373752</v>
       </c>
       <c r="B51" t="n">
         <v>79089</v>
@@ -5704,10 +5700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440444</v>
+        <v>440310</v>
       </c>
       <c r="R51" t="n">
-        <v>6763182</v>
+        <v>6762992</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5767,7 +5763,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373593</v>
+        <v>128373403</v>
       </c>
       <c r="B52" t="n">
         <v>79089</v>
@@ -5805,10 +5801,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440325</v>
+        <v>440444</v>
       </c>
       <c r="R52" t="n">
-        <v>6763069</v>
+        <v>6763182</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5868,10 +5864,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373752</v>
+        <v>128373782</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>91486</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5879,24 +5875,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440310</v>
+        <v>440285</v>
       </c>
       <c r="R53" t="n">
-        <v>6762992</v>
+        <v>6762985</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -1079,53 +1079,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373860</v>
+        <v>128374324</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>96710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440187</v>
+        <v>440191</v>
       </c>
       <c r="R6" t="n">
-        <v>6763085</v>
+        <v>6762689</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,17 +1156,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,49 +1181,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128374324</v>
+        <v>128373899</v>
       </c>
       <c r="B7" t="n">
-        <v>96710</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440191</v>
+        <v>440199</v>
       </c>
       <c r="R7" t="n">
-        <v>6762689</v>
+        <v>6762979</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1291,7 +1282,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373899</v>
+        <v>128373673</v>
       </c>
       <c r="B8" t="n">
         <v>79089</v>
@@ -1329,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440199</v>
+        <v>440297</v>
       </c>
       <c r="R8" t="n">
-        <v>6762979</v>
+        <v>6763071</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1392,7 +1383,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373673</v>
+        <v>128373873</v>
       </c>
       <c r="B9" t="n">
         <v>79089</v>
@@ -1430,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440297</v>
+        <v>440201</v>
       </c>
       <c r="R9" t="n">
-        <v>6763071</v>
+        <v>6763012</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1493,7 +1484,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373873</v>
+        <v>128373878</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1531,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440201</v>
+        <v>440202</v>
       </c>
       <c r="R10" t="n">
-        <v>6763012</v>
+        <v>6763032</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1594,7 +1585,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373878</v>
+        <v>128374165</v>
       </c>
       <c r="B11" t="n">
         <v>79089</v>
@@ -1632,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440202</v>
+        <v>440024</v>
       </c>
       <c r="R11" t="n">
-        <v>6763032</v>
+        <v>6762784</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1695,7 +1686,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128374165</v>
+        <v>128373481</v>
       </c>
       <c r="B12" t="n">
         <v>79089</v>
@@ -1733,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440024</v>
+        <v>440418</v>
       </c>
       <c r="R12" t="n">
-        <v>6762784</v>
+        <v>6763099</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1796,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128373481</v>
+        <v>128373475</v>
       </c>
       <c r="B13" t="n">
         <v>79089</v>
@@ -1834,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440418</v>
+        <v>440406</v>
       </c>
       <c r="R13" t="n">
-        <v>6763099</v>
+        <v>6763080</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1897,7 +1888,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128373475</v>
+        <v>128374108</v>
       </c>
       <c r="B14" t="n">
         <v>79089</v>
@@ -1935,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440406</v>
+        <v>439941</v>
       </c>
       <c r="R14" t="n">
-        <v>6763080</v>
+        <v>6762833</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1998,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128374108</v>
+        <v>128373860</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,26 +2000,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2036,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439941</v>
+        <v>440187</v>
       </c>
       <c r="R15" t="n">
-        <v>6762833</v>
+        <v>6763085</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2074,13 +2070,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -4443,32 +4443,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128374129</v>
+        <v>128373466</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>92756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439996</v>
+        <v>440428</v>
       </c>
       <c r="R39" t="n">
-        <v>6762772</v>
+        <v>6763185</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4517,6 +4517,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4544,7 +4549,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128373380</v>
+        <v>128374129</v>
       </c>
       <c r="B40" t="n">
         <v>79089</v>
@@ -4582,10 +4587,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440499</v>
+        <v>439996</v>
       </c>
       <c r="R40" t="n">
-        <v>6763177</v>
+        <v>6762772</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4645,7 +4650,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128373747</v>
+        <v>128373380</v>
       </c>
       <c r="B41" t="n">
         <v>79089</v>
@@ -4683,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440332</v>
+        <v>440499</v>
       </c>
       <c r="R41" t="n">
-        <v>6762998</v>
+        <v>6763177</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4746,32 +4751,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373466</v>
+        <v>128373747</v>
       </c>
       <c r="B42" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4784,10 +4789,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440428</v>
+        <v>440332</v>
       </c>
       <c r="R42" t="n">
-        <v>6763185</v>
+        <v>6762998</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4820,11 +4825,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5969,10 +5969,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128374431</v>
+        <v>128373544</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,37 +5980,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440332</v>
+        <v>440327</v>
       </c>
       <c r="R54" t="n">
-        <v>6762821</v>
+        <v>6763083</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6045,13 +6050,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6070,7 +6079,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128374197</v>
+        <v>128374431</v>
       </c>
       <c r="B55" t="n">
         <v>79089</v>
@@ -6104,14 +6113,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440001</v>
+        <v>440332</v>
       </c>
       <c r="R55" t="n">
-        <v>6762789</v>
+        <v>6762821</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6171,7 +6180,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128373986</v>
+        <v>128374197</v>
       </c>
       <c r="B56" t="n">
         <v>79089</v>
@@ -6209,10 +6218,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440031</v>
+        <v>440001</v>
       </c>
       <c r="R56" t="n">
-        <v>6762895</v>
+        <v>6762789</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6272,7 +6281,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128374429</v>
+        <v>128373986</v>
       </c>
       <c r="B57" t="n">
         <v>79089</v>
@@ -6306,14 +6315,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440338</v>
+        <v>440031</v>
       </c>
       <c r="R57" t="n">
-        <v>6762836</v>
+        <v>6762895</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6373,10 +6382,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128373544</v>
+        <v>128374429</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6384,42 +6393,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440327</v>
+        <v>440338</v>
       </c>
       <c r="R58" t="n">
-        <v>6763083</v>
+        <v>6762836</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6454,17 +6458,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6891,43 +6891,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373935</v>
+        <v>128373958</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6935,10 +6929,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440107</v>
+        <v>440085</v>
       </c>
       <c r="R63" t="n">
-        <v>6762932</v>
+        <v>6762953</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6998,43 +6992,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373939</v>
+        <v>128373976</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7042,10 +7030,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440091</v>
+        <v>440119</v>
       </c>
       <c r="R64" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7105,37 +7093,43 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373958</v>
+        <v>128373935</v>
       </c>
       <c r="B65" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7143,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440085</v>
+        <v>440107</v>
       </c>
       <c r="R65" t="n">
-        <v>6762953</v>
+        <v>6762932</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7206,37 +7200,43 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373976</v>
+        <v>128373939</v>
       </c>
       <c r="B66" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440119</v>
+        <v>440091</v>
       </c>
       <c r="R66" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128374441</v>
+        <v>128373817</v>
       </c>
       <c r="B2" t="n">
         <v>79089</v>
@@ -709,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440344</v>
+        <v>440235</v>
       </c>
       <c r="R2" t="n">
-        <v>6762829</v>
+        <v>6763090</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373419</v>
+        <v>128373617</v>
       </c>
       <c r="B3" t="n">
         <v>79089</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440412</v>
+        <v>440313</v>
       </c>
       <c r="R3" t="n">
-        <v>6763165</v>
+        <v>6763067</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128373617</v>
+        <v>128374441</v>
       </c>
       <c r="B4" t="n">
         <v>79089</v>
@@ -911,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440313</v>
+        <v>440344</v>
       </c>
       <c r="R4" t="n">
-        <v>6763067</v>
+        <v>6762829</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373817</v>
+        <v>128373419</v>
       </c>
       <c r="B5" t="n">
         <v>79089</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440235</v>
+        <v>440412</v>
       </c>
       <c r="R5" t="n">
-        <v>6763090</v>
+        <v>6763165</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1082,7 +1082,7 @@
         <v>128374324</v>
       </c>
       <c r="B6" t="n">
-        <v>96710</v>
+        <v>96711</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373899</v>
+        <v>128373873</v>
       </c>
       <c r="B7" t="n">
         <v>79089</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440199</v>
+        <v>440201</v>
       </c>
       <c r="R7" t="n">
-        <v>6762979</v>
+        <v>6763012</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373673</v>
+        <v>128373878</v>
       </c>
       <c r="B8" t="n">
         <v>79089</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440297</v>
+        <v>440202</v>
       </c>
       <c r="R8" t="n">
-        <v>6763071</v>
+        <v>6763032</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1383,7 +1383,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373873</v>
+        <v>128373673</v>
       </c>
       <c r="B9" t="n">
         <v>79089</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440201</v>
+        <v>440297</v>
       </c>
       <c r="R9" t="n">
-        <v>6763012</v>
+        <v>6763071</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373878</v>
+        <v>128374165</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440202</v>
+        <v>440024</v>
       </c>
       <c r="R10" t="n">
-        <v>6763032</v>
+        <v>6762784</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128374165</v>
+        <v>128373475</v>
       </c>
       <c r="B11" t="n">
         <v>79089</v>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440024</v>
+        <v>440406</v>
       </c>
       <c r="R11" t="n">
-        <v>6762784</v>
+        <v>6763080</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373481</v>
+        <v>128373899</v>
       </c>
       <c r="B12" t="n">
         <v>79089</v>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440418</v>
+        <v>440199</v>
       </c>
       <c r="R12" t="n">
-        <v>6763099</v>
+        <v>6762979</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128373475</v>
+        <v>128374108</v>
       </c>
       <c r="B13" t="n">
         <v>79089</v>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440406</v>
+        <v>439941</v>
       </c>
       <c r="R13" t="n">
-        <v>6763080</v>
+        <v>6762833</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,7 +1888,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374108</v>
+        <v>128373481</v>
       </c>
       <c r="B14" t="n">
         <v>79089</v>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439941</v>
+        <v>440418</v>
       </c>
       <c r="R14" t="n">
-        <v>6762833</v>
+        <v>6763099</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2200,43 +2200,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128373765</v>
+        <v>128373503</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2244,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440300</v>
+        <v>440401</v>
       </c>
       <c r="R17" t="n">
-        <v>6762994</v>
+        <v>6763097</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2307,7 +2301,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128373503</v>
+        <v>128373653</v>
       </c>
       <c r="B18" t="n">
         <v>79089</v>
@@ -2345,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440401</v>
+        <v>440307</v>
       </c>
       <c r="R18" t="n">
-        <v>6763097</v>
+        <v>6763084</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2408,37 +2402,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128373653</v>
+        <v>128373765</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440307</v>
+        <v>440300</v>
       </c>
       <c r="R19" t="n">
-        <v>6763084</v>
+        <v>6762994</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2509,7 +2509,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128373363</v>
+        <v>128374175</v>
       </c>
       <c r="B20" t="n">
         <v>79089</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440512</v>
+        <v>439993</v>
       </c>
       <c r="R20" t="n">
-        <v>6763183</v>
+        <v>6762757</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128374175</v>
+        <v>128373363</v>
       </c>
       <c r="B21" t="n">
         <v>79089</v>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439993</v>
+        <v>440512</v>
       </c>
       <c r="R21" t="n">
-        <v>6762757</v>
+        <v>6763183</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2711,7 +2711,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128373893</v>
+        <v>128373390</v>
       </c>
       <c r="B22" t="n">
         <v>79089</v>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440212</v>
+        <v>440462</v>
       </c>
       <c r="R22" t="n">
-        <v>6762957</v>
+        <v>6763204</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128373390</v>
+        <v>128373893</v>
       </c>
       <c r="B23" t="n">
         <v>79089</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440462</v>
+        <v>440212</v>
       </c>
       <c r="R23" t="n">
-        <v>6763204</v>
+        <v>6762957</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128373797</v>
+        <v>128373738</v>
       </c>
       <c r="B24" t="n">
         <v>79089</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440232</v>
+        <v>440357</v>
       </c>
       <c r="R24" t="n">
-        <v>6763126</v>
+        <v>6763022</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128373738</v>
+        <v>128373797</v>
       </c>
       <c r="B25" t="n">
         <v>79089</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440357</v>
+        <v>440232</v>
       </c>
       <c r="R25" t="n">
-        <v>6763022</v>
+        <v>6763126</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128374000</v>
+        <v>128373960</v>
       </c>
       <c r="B27" t="n">
         <v>79089</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440054</v>
+        <v>440101</v>
       </c>
       <c r="R27" t="n">
-        <v>6762902</v>
+        <v>6762969</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3317,7 +3317,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128373960</v>
+        <v>128373992</v>
       </c>
       <c r="B28" t="n">
         <v>79089</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440101</v>
+        <v>440043</v>
       </c>
       <c r="R28" t="n">
-        <v>6762969</v>
+        <v>6762922</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128373992</v>
+        <v>128374000</v>
       </c>
       <c r="B30" t="n">
         <v>79089</v>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440043</v>
+        <v>440054</v>
       </c>
       <c r="R30" t="n">
-        <v>6762922</v>
+        <v>6762902</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374114</v>
+        <v>128374437</v>
       </c>
       <c r="B32" t="n">
         <v>79089</v>
@@ -3761,14 +3761,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439954</v>
+        <v>440322</v>
       </c>
       <c r="R32" t="n">
-        <v>6762847</v>
+        <v>6762821</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128374437</v>
+        <v>128374114</v>
       </c>
       <c r="B33" t="n">
         <v>79089</v>
@@ -3862,14 +3862,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440322</v>
+        <v>439954</v>
       </c>
       <c r="R33" t="n">
-        <v>6762821</v>
+        <v>6762847</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4443,32 +4443,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128373466</v>
+        <v>128373380</v>
       </c>
       <c r="B39" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440428</v>
+        <v>440499</v>
       </c>
       <c r="R39" t="n">
-        <v>6763185</v>
+        <v>6763177</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4517,11 +4517,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4549,7 +4544,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374129</v>
+        <v>128373747</v>
       </c>
       <c r="B40" t="n">
         <v>79089</v>
@@ -4587,10 +4582,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439996</v>
+        <v>440332</v>
       </c>
       <c r="R40" t="n">
-        <v>6762772</v>
+        <v>6762998</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,7 +4645,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128373380</v>
+        <v>128374129</v>
       </c>
       <c r="B41" t="n">
         <v>79089</v>
@@ -4688,10 +4683,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440499</v>
+        <v>439996</v>
       </c>
       <c r="R41" t="n">
-        <v>6763177</v>
+        <v>6762772</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4751,32 +4746,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373747</v>
+        <v>128373466</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>92757</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4789,10 +4784,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440332</v>
+        <v>440428</v>
       </c>
       <c r="R42" t="n">
-        <v>6762998</v>
+        <v>6763185</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4825,6 +4820,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4855,7 +4855,7 @@
         <v>128374321</v>
       </c>
       <c r="B43" t="n">
-        <v>96710</v>
+        <v>96711</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4954,49 +4954,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128374335</v>
+        <v>128373813</v>
       </c>
       <c r="B44" t="n">
-        <v>96710</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440203</v>
+        <v>440218</v>
       </c>
       <c r="R44" t="n">
-        <v>6762697</v>
+        <v>6763088</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5056,7 +5055,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373409</v>
+        <v>128374120</v>
       </c>
       <c r="B45" t="n">
         <v>79089</v>
@@ -5094,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440432</v>
+        <v>439959</v>
       </c>
       <c r="R45" t="n">
-        <v>6763202</v>
+        <v>6762821</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5157,7 +5156,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373813</v>
+        <v>128373809</v>
       </c>
       <c r="B46" t="n">
         <v>79089</v>
@@ -5195,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440218</v>
+        <v>440239</v>
       </c>
       <c r="R46" t="n">
-        <v>6763088</v>
+        <v>6763111</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5258,7 +5257,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128373868</v>
+        <v>128373409</v>
       </c>
       <c r="B47" t="n">
         <v>79089</v>
@@ -5296,10 +5295,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440225</v>
+        <v>440432</v>
       </c>
       <c r="R47" t="n">
-        <v>6763025</v>
+        <v>6763202</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5359,7 +5358,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128374120</v>
+        <v>128373868</v>
       </c>
       <c r="B48" t="n">
         <v>79089</v>
@@ -5397,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439959</v>
+        <v>440225</v>
       </c>
       <c r="R48" t="n">
-        <v>6762821</v>
+        <v>6763025</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5460,48 +5459,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128373809</v>
+        <v>128374335</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>96711</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440239</v>
+        <v>440203</v>
       </c>
       <c r="R49" t="n">
-        <v>6763111</v>
+        <v>6762697</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,7 +5561,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373593</v>
+        <v>128373403</v>
       </c>
       <c r="B50" t="n">
         <v>79089</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440325</v>
+        <v>440444</v>
       </c>
       <c r="R50" t="n">
-        <v>6763069</v>
+        <v>6763182</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5662,7 +5662,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373752</v>
+        <v>128373593</v>
       </c>
       <c r="B51" t="n">
         <v>79089</v>
@@ -5700,10 +5700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440310</v>
+        <v>440325</v>
       </c>
       <c r="R51" t="n">
-        <v>6762992</v>
+        <v>6763069</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,7 +5763,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373403</v>
+        <v>128373752</v>
       </c>
       <c r="B52" t="n">
         <v>79089</v>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440444</v>
+        <v>440310</v>
       </c>
       <c r="R52" t="n">
-        <v>6763182</v>
+        <v>6762992</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5867,7 +5867,7 @@
         <v>128373782</v>
       </c>
       <c r="B53" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5969,10 +5969,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128373544</v>
+        <v>128374431</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,42 +5980,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440327</v>
+        <v>440332</v>
       </c>
       <c r="R54" t="n">
-        <v>6763083</v>
+        <v>6762821</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,17 +6045,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6079,7 +6070,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128374431</v>
+        <v>128374197</v>
       </c>
       <c r="B55" t="n">
         <v>79089</v>
@@ -6113,14 +6104,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440332</v>
+        <v>440001</v>
       </c>
       <c r="R55" t="n">
-        <v>6762821</v>
+        <v>6762789</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6180,7 +6171,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128374197</v>
+        <v>128374429</v>
       </c>
       <c r="B56" t="n">
         <v>79089</v>
@@ -6214,14 +6205,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440001</v>
+        <v>440338</v>
       </c>
       <c r="R56" t="n">
-        <v>6762789</v>
+        <v>6762836</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6382,10 +6373,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128374429</v>
+        <v>128373544</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6393,37 +6384,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440338</v>
+        <v>440327</v>
       </c>
       <c r="R58" t="n">
-        <v>6762836</v>
+        <v>6763083</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6458,13 +6454,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6891,37 +6891,43 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373958</v>
+        <v>128373935</v>
       </c>
       <c r="B63" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6929,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440085</v>
+        <v>440107</v>
       </c>
       <c r="R63" t="n">
-        <v>6762953</v>
+        <v>6762932</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6992,37 +6998,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373976</v>
+        <v>128373939</v>
       </c>
       <c r="B64" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7030,10 +7042,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440119</v>
+        <v>440091</v>
       </c>
       <c r="R64" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7093,43 +7105,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373935</v>
+        <v>128373976</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7137,10 +7143,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440107</v>
+        <v>440119</v>
       </c>
       <c r="R65" t="n">
-        <v>6762932</v>
+        <v>6762953</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7200,43 +7206,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373939</v>
+        <v>128373958</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440091</v>
+        <v>440085</v>
       </c>
       <c r="R66" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7408,7 +7408,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128373683</v>
+        <v>128373339</v>
       </c>
       <c r="B68" t="n">
         <v>79089</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440312</v>
+        <v>440512</v>
       </c>
       <c r="R68" t="n">
-        <v>6763096</v>
+        <v>6763195</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7509,7 +7509,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128373907</v>
+        <v>128373683</v>
       </c>
       <c r="B69" t="n">
         <v>79089</v>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440185</v>
+        <v>440312</v>
       </c>
       <c r="R69" t="n">
-        <v>6762972</v>
+        <v>6763096</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7610,7 +7610,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128373339</v>
+        <v>128373907</v>
       </c>
       <c r="B70" t="n">
         <v>79089</v>
@@ -7648,10 +7648,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440512</v>
+        <v>440185</v>
       </c>
       <c r="R70" t="n">
-        <v>6763195</v>
+        <v>6762972</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -1079,49 +1079,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374324</v>
+        <v>128373873</v>
       </c>
       <c r="B6" t="n">
-        <v>96711</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440191</v>
+        <v>440201</v>
       </c>
       <c r="R6" t="n">
-        <v>6762689</v>
+        <v>6763012</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1181,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373873</v>
+        <v>128373878</v>
       </c>
       <c r="B7" t="n">
         <v>79089</v>
@@ -1219,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440201</v>
+        <v>440202</v>
       </c>
       <c r="R7" t="n">
-        <v>6763012</v>
+        <v>6763032</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1282,7 +1281,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373878</v>
+        <v>128373673</v>
       </c>
       <c r="B8" t="n">
         <v>79089</v>
@@ -1320,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440202</v>
+        <v>440297</v>
       </c>
       <c r="R8" t="n">
-        <v>6763032</v>
+        <v>6763071</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1383,7 +1382,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373673</v>
+        <v>128374165</v>
       </c>
       <c r="B9" t="n">
         <v>79089</v>
@@ -1421,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440297</v>
+        <v>440024</v>
       </c>
       <c r="R9" t="n">
-        <v>6763071</v>
+        <v>6762784</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,7 +1483,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128374165</v>
+        <v>128373475</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1522,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440024</v>
+        <v>440406</v>
       </c>
       <c r="R10" t="n">
-        <v>6762784</v>
+        <v>6763080</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,7 +1584,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373475</v>
+        <v>128373899</v>
       </c>
       <c r="B11" t="n">
         <v>79089</v>
@@ -1623,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440406</v>
+        <v>440199</v>
       </c>
       <c r="R11" t="n">
-        <v>6763080</v>
+        <v>6762979</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1686,7 +1685,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373899</v>
+        <v>128374108</v>
       </c>
       <c r="B12" t="n">
         <v>79089</v>
@@ -1724,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440199</v>
+        <v>439941</v>
       </c>
       <c r="R12" t="n">
-        <v>6762979</v>
+        <v>6762833</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1787,7 +1786,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374108</v>
+        <v>128373481</v>
       </c>
       <c r="B13" t="n">
         <v>79089</v>
@@ -1825,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439941</v>
+        <v>440418</v>
       </c>
       <c r="R13" t="n">
-        <v>6762833</v>
+        <v>6763099</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128373481</v>
+        <v>128373860</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,26 +1898,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1926,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440418</v>
+        <v>440187</v>
       </c>
       <c r="R14" t="n">
-        <v>6763099</v>
+        <v>6763085</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1964,13 +1968,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1989,53 +1997,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128373860</v>
+        <v>128374324</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>96711</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440187</v>
+        <v>440191</v>
       </c>
       <c r="R15" t="n">
-        <v>6763085</v>
+        <v>6762689</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2070,17 +2074,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>128464117</v>
       </c>
       <c r="B72" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>128463867</v>
       </c>
       <c r="B73" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>128532195</v>
       </c>
       <c r="B74" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>128463474</v>
       </c>
       <c r="B75" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>128535275</v>
       </c>
       <c r="B76" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373817</v>
+        <v>128374441</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440235</v>
+        <v>440344</v>
       </c>
       <c r="R2" t="n">
-        <v>6763090</v>
+        <v>6762829</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373617</v>
+        <v>128373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440313</v>
+        <v>440412</v>
       </c>
       <c r="R3" t="n">
-        <v>6763067</v>
+        <v>6763165</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128374441</v>
+        <v>128373617</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440344</v>
+        <v>440313</v>
       </c>
       <c r="R4" t="n">
-        <v>6762829</v>
+        <v>6763067</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373419</v>
+        <v>128373817</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440412</v>
+        <v>440235</v>
       </c>
       <c r="R5" t="n">
-        <v>6763165</v>
+        <v>6763090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373873</v>
+        <v>128373860</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,26 +1090,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1117,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440201</v>
+        <v>440187</v>
       </c>
       <c r="R6" t="n">
-        <v>6763012</v>
+        <v>6763085</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1155,13 +1160,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,48 +1189,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373878</v>
+        <v>128374324</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>96738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440202</v>
+        <v>440191</v>
       </c>
       <c r="R7" t="n">
-        <v>6763032</v>
+        <v>6762689</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373673</v>
+        <v>128373899</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440297</v>
+        <v>440199</v>
       </c>
       <c r="R8" t="n">
-        <v>6763071</v>
+        <v>6762979</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128374165</v>
+        <v>128373673</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440024</v>
+        <v>440297</v>
       </c>
       <c r="R9" t="n">
-        <v>6762784</v>
+        <v>6763071</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1483,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373475</v>
+        <v>128373873</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440406</v>
+        <v>440201</v>
       </c>
       <c r="R10" t="n">
-        <v>6763080</v>
+        <v>6763012</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1584,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373899</v>
+        <v>128373878</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1622,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440199</v>
+        <v>440202</v>
       </c>
       <c r="R11" t="n">
-        <v>6762979</v>
+        <v>6763032</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1685,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128374108</v>
+        <v>128374165</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1723,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439941</v>
+        <v>440024</v>
       </c>
       <c r="R12" t="n">
-        <v>6762833</v>
+        <v>6762784</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1789,7 +1799,7 @@
         <v>128373481</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128373860</v>
+        <v>128373475</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,31 +1908,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1930,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440187</v>
+        <v>440406</v>
       </c>
       <c r="R14" t="n">
-        <v>6763085</v>
+        <v>6763080</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1968,17 +1973,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1997,49 +1998,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128374324</v>
+        <v>128374108</v>
       </c>
       <c r="B15" t="n">
-        <v>96711</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440191</v>
+        <v>439941</v>
       </c>
       <c r="R15" t="n">
-        <v>6762689</v>
+        <v>6762833</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2102,7 +2102,7 @@
         <v>128374090</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,37 +2200,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128373503</v>
+        <v>128373765</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2238,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440401</v>
+        <v>440300</v>
       </c>
       <c r="R17" t="n">
-        <v>6763097</v>
+        <v>6762994</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2301,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128373653</v>
+        <v>128373503</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440307</v>
+        <v>440401</v>
       </c>
       <c r="R18" t="n">
-        <v>6763084</v>
+        <v>6763097</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2402,43 +2408,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128373765</v>
+        <v>128373653</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440300</v>
+        <v>440307</v>
       </c>
       <c r="R19" t="n">
-        <v>6762994</v>
+        <v>6763084</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128374175</v>
+        <v>128373363</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439993</v>
+        <v>440512</v>
       </c>
       <c r="R20" t="n">
-        <v>6762757</v>
+        <v>6763183</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128373363</v>
+        <v>128374175</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440512</v>
+        <v>439993</v>
       </c>
       <c r="R21" t="n">
-        <v>6763183</v>
+        <v>6762757</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2711,10 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128373390</v>
+        <v>128373893</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440462</v>
+        <v>440212</v>
       </c>
       <c r="R22" t="n">
-        <v>6763204</v>
+        <v>6762957</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2812,10 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128373893</v>
+        <v>128373390</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440212</v>
+        <v>440462</v>
       </c>
       <c r="R23" t="n">
-        <v>6762957</v>
+        <v>6763204</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128373738</v>
+        <v>128373797</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440357</v>
+        <v>440232</v>
       </c>
       <c r="R24" t="n">
-        <v>6763022</v>
+        <v>6763126</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3014,10 +3014,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128373797</v>
+        <v>128373738</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440232</v>
+        <v>440357</v>
       </c>
       <c r="R25" t="n">
-        <v>6763126</v>
+        <v>6763022</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3118,7 +3118,7 @@
         <v>128373743</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128373960</v>
+        <v>128374454</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,14 +3250,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440101</v>
+        <v>440400</v>
       </c>
       <c r="R27" t="n">
-        <v>6762969</v>
+        <v>6762886</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128373992</v>
+        <v>128374000</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440043</v>
+        <v>440054</v>
       </c>
       <c r="R28" t="n">
-        <v>6762922</v>
+        <v>6762902</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128374454</v>
+        <v>128373960</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3452,14 +3452,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440400</v>
+        <v>440101</v>
       </c>
       <c r="R29" t="n">
-        <v>6762886</v>
+        <v>6762969</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128374000</v>
+        <v>128373992</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440054</v>
+        <v>440043</v>
       </c>
       <c r="R30" t="n">
-        <v>6762902</v>
+        <v>6762922</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3620,54 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374425</v>
+        <v>128373955</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440328</v>
+        <v>440100</v>
       </c>
       <c r="R31" t="n">
-        <v>6762829</v>
+        <v>6762947</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3727,10 +3721,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374437</v>
+        <v>128374114</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3761,14 +3755,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440322</v>
+        <v>439954</v>
       </c>
       <c r="R32" t="n">
-        <v>6762821</v>
+        <v>6762847</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3828,10 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128374114</v>
+        <v>128374437</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,14 +3856,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439954</v>
+        <v>440322</v>
       </c>
       <c r="R33" t="n">
-        <v>6762847</v>
+        <v>6762821</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3929,10 +3923,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373955</v>
+        <v>128373374</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3967,10 +3961,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440100</v>
+        <v>440502</v>
       </c>
       <c r="R34" t="n">
-        <v>6762947</v>
+        <v>6763186</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4030,48 +4024,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128373374</v>
+        <v>128374425</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440502</v>
+        <v>440328</v>
       </c>
       <c r="R35" t="n">
-        <v>6763186</v>
+        <v>6762829</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4134,7 +4134,7 @@
         <v>128373433</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,26 +4243,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4270,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R37" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4308,13 +4313,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4333,10 +4342,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B38" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4344,31 +4353,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4376,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R38" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4414,17 +4418,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4443,32 +4443,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128373380</v>
+        <v>128373466</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>92784</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440499</v>
+        <v>440428</v>
       </c>
       <c r="R39" t="n">
-        <v>6763177</v>
+        <v>6763185</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4517,6 +4517,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4544,48 +4549,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128373747</v>
+        <v>128374321</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>96738</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440332</v>
+        <v>440185</v>
       </c>
       <c r="R40" t="n">
-        <v>6762998</v>
+        <v>6762702</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4648,7 +4654,7 @@
         <v>128374129</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4746,32 +4752,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373466</v>
+        <v>128373380</v>
       </c>
       <c r="B42" t="n">
-        <v>92757</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4784,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440428</v>
+        <v>440499</v>
       </c>
       <c r="R42" t="n">
-        <v>6763185</v>
+        <v>6763177</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4820,11 +4826,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4852,49 +4853,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128374321</v>
+        <v>128373747</v>
       </c>
       <c r="B43" t="n">
-        <v>96711</v>
+        <v>79116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440185</v>
+        <v>440332</v>
       </c>
       <c r="R43" t="n">
-        <v>6762702</v>
+        <v>6762998</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4954,10 +4954,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128373813</v>
+        <v>128374120</v>
       </c>
       <c r="B44" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440218</v>
+        <v>439959</v>
       </c>
       <c r="R44" t="n">
-        <v>6763088</v>
+        <v>6762821</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128374120</v>
+        <v>128373809</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439959</v>
+        <v>440239</v>
       </c>
       <c r="R45" t="n">
-        <v>6762821</v>
+        <v>6763111</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5156,48 +5156,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373809</v>
+        <v>128374335</v>
       </c>
       <c r="B46" t="n">
-        <v>79089</v>
+        <v>96738</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440239</v>
+        <v>440203</v>
       </c>
       <c r="R46" t="n">
-        <v>6763111</v>
+        <v>6762697</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5260,7 +5261,7 @@
         <v>128373409</v>
       </c>
       <c r="B47" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5358,10 +5359,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128373868</v>
+        <v>128373813</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5396,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440225</v>
+        <v>440218</v>
       </c>
       <c r="R48" t="n">
-        <v>6763025</v>
+        <v>6763088</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5459,49 +5460,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128374335</v>
+        <v>128373868</v>
       </c>
       <c r="B49" t="n">
-        <v>96711</v>
+        <v>79116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440203</v>
+        <v>440225</v>
       </c>
       <c r="R49" t="n">
-        <v>6762697</v>
+        <v>6763025</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373403</v>
+        <v>128373593</v>
       </c>
       <c r="B50" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440444</v>
+        <v>440325</v>
       </c>
       <c r="R50" t="n">
-        <v>6763182</v>
+        <v>6763069</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373593</v>
+        <v>128373752</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5700,10 +5700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440325</v>
+        <v>440310</v>
       </c>
       <c r="R51" t="n">
-        <v>6763069</v>
+        <v>6762992</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373752</v>
+        <v>128373782</v>
       </c>
       <c r="B52" t="n">
-        <v>79089</v>
+        <v>91514</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5774,24 +5774,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -5801,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440310</v>
+        <v>440285</v>
       </c>
       <c r="R52" t="n">
-        <v>6762992</v>
+        <v>6762985</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5864,10 +5868,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373782</v>
+        <v>128373403</v>
       </c>
       <c r="B53" t="n">
-        <v>91487</v>
+        <v>79116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5875,28 +5879,24 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440285</v>
+        <v>440444</v>
       </c>
       <c r="R53" t="n">
-        <v>6762985</v>
+        <v>6763182</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5969,10 +5969,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128374431</v>
+        <v>128373544</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,37 +5980,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440332</v>
+        <v>440327</v>
       </c>
       <c r="R54" t="n">
-        <v>6762821</v>
+        <v>6763083</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6045,13 +6050,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6073,7 +6082,7 @@
         <v>128374197</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6174,7 +6183,7 @@
         <v>128374429</v>
       </c>
       <c r="B56" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6272,10 +6281,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128373986</v>
+        <v>128374431</v>
       </c>
       <c r="B57" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6306,14 +6315,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440031</v>
+        <v>440332</v>
       </c>
       <c r="R57" t="n">
-        <v>6762895</v>
+        <v>6762821</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6373,10 +6382,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128373544</v>
+        <v>128373986</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6384,31 +6393,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6416,10 +6420,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440327</v>
+        <v>440031</v>
       </c>
       <c r="R58" t="n">
-        <v>6763083</v>
+        <v>6762895</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6454,17 +6458,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6483,37 +6483,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128373395</v>
+        <v>128373927</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>56907</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6521,10 +6526,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440451</v>
+        <v>440114</v>
       </c>
       <c r="R59" t="n">
-        <v>6763197</v>
+        <v>6763007</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6565,7 +6570,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6584,42 +6588,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128373927</v>
+        <v>128373395</v>
       </c>
       <c r="B60" t="n">
-        <v>56880</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6627,10 +6626,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440114</v>
+        <v>440451</v>
       </c>
       <c r="R60" t="n">
-        <v>6763007</v>
+        <v>6763197</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6671,6 +6670,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>128373803</v>
       </c>
       <c r="B61" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>128373428</v>
       </c>
       <c r="B62" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6891,43 +6891,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373935</v>
+        <v>128373958</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6935,10 +6929,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440107</v>
+        <v>440085</v>
       </c>
       <c r="R63" t="n">
-        <v>6762932</v>
+        <v>6762953</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6998,43 +6992,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373939</v>
+        <v>128373976</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7042,10 +7030,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440091</v>
+        <v>440119</v>
       </c>
       <c r="R64" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7105,37 +7093,43 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373976</v>
+        <v>128373935</v>
       </c>
       <c r="B65" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7143,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440119</v>
+        <v>440107</v>
       </c>
       <c r="R65" t="n">
-        <v>6762953</v>
+        <v>6762932</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7206,37 +7200,43 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373958</v>
+        <v>128373939</v>
       </c>
       <c r="B66" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440085</v>
+        <v>440091</v>
       </c>
       <c r="R66" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7310,7 +7310,7 @@
         <v>128373912</v>
       </c>
       <c r="B67" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128373339</v>
+        <v>128373683</v>
       </c>
       <c r="B68" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440512</v>
+        <v>440312</v>
       </c>
       <c r="R68" t="n">
-        <v>6763195</v>
+        <v>6763096</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128373683</v>
+        <v>128373907</v>
       </c>
       <c r="B69" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440312</v>
+        <v>440185</v>
       </c>
       <c r="R69" t="n">
-        <v>6763096</v>
+        <v>6762972</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7610,10 +7610,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128373907</v>
+        <v>128373339</v>
       </c>
       <c r="B70" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7648,10 +7648,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440185</v>
+        <v>440512</v>
       </c>
       <c r="R70" t="n">
-        <v>6762972</v>
+        <v>6763195</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7714,7 +7714,7 @@
         <v>128373758</v>
       </c>
       <c r="B71" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -2200,43 +2200,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128373765</v>
+        <v>128373503</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2244,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440300</v>
+        <v>440401</v>
       </c>
       <c r="R17" t="n">
-        <v>6762994</v>
+        <v>6763097</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2307,7 +2301,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128373503</v>
+        <v>128373653</v>
       </c>
       <c r="B18" t="n">
         <v>79116</v>
@@ -2345,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440401</v>
+        <v>440307</v>
       </c>
       <c r="R18" t="n">
-        <v>6763097</v>
+        <v>6763084</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2408,37 +2402,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128373653</v>
+        <v>128373765</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440307</v>
+        <v>440300</v>
       </c>
       <c r="R19" t="n">
-        <v>6763084</v>
+        <v>6762994</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128374454</v>
+        <v>128374000</v>
       </c>
       <c r="B27" t="n">
         <v>79116</v>
@@ -3250,14 +3250,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440400</v>
+        <v>440054</v>
       </c>
       <c r="R27" t="n">
-        <v>6762886</v>
+        <v>6762902</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3317,7 +3317,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128374000</v>
+        <v>128373960</v>
       </c>
       <c r="B28" t="n">
         <v>79116</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440054</v>
+        <v>440101</v>
       </c>
       <c r="R28" t="n">
-        <v>6762902</v>
+        <v>6762969</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128373960</v>
+        <v>128374454</v>
       </c>
       <c r="B29" t="n">
         <v>79116</v>
@@ -3452,14 +3452,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440101</v>
+        <v>440400</v>
       </c>
       <c r="R29" t="n">
-        <v>6762969</v>
+        <v>6762886</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3620,48 +3620,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128373955</v>
+        <v>128374425</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440100</v>
+        <v>440328</v>
       </c>
       <c r="R31" t="n">
-        <v>6762947</v>
+        <v>6762829</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3923,7 +3929,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373374</v>
+        <v>128373955</v>
       </c>
       <c r="B34" t="n">
         <v>79116</v>
@@ -3961,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440502</v>
+        <v>440100</v>
       </c>
       <c r="R34" t="n">
-        <v>6763186</v>
+        <v>6762947</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4024,54 +4030,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128374425</v>
+        <v>128373374</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440328</v>
+        <v>440502</v>
       </c>
       <c r="R35" t="n">
-        <v>6762829</v>
+        <v>6763186</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128373466</v>
+        <v>128374321</v>
       </c>
       <c r="B39" t="n">
-        <v>92784</v>
+        <v>96738</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4454,37 +4454,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440428</v>
+        <v>440185</v>
       </c>
       <c r="R39" t="n">
-        <v>6763185</v>
+        <v>6762702</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4517,11 +4518,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4549,10 +4545,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374321</v>
+        <v>128373466</v>
       </c>
       <c r="B40" t="n">
-        <v>96738</v>
+        <v>92784</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4560,38 +4556,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440185</v>
+        <v>440428</v>
       </c>
       <c r="R40" t="n">
-        <v>6762702</v>
+        <v>6763185</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4624,6 +4619,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4954,7 +4954,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128374120</v>
+        <v>128373409</v>
       </c>
       <c r="B44" t="n">
         <v>79116</v>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439959</v>
+        <v>440432</v>
       </c>
       <c r="R44" t="n">
-        <v>6762821</v>
+        <v>6763202</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5055,7 +5055,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373809</v>
+        <v>128373813</v>
       </c>
       <c r="B45" t="n">
         <v>79116</v>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440239</v>
+        <v>440218</v>
       </c>
       <c r="R45" t="n">
-        <v>6763111</v>
+        <v>6763088</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5156,49 +5156,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128374335</v>
+        <v>128373868</v>
       </c>
       <c r="B46" t="n">
-        <v>96738</v>
+        <v>79116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440203</v>
+        <v>440225</v>
       </c>
       <c r="R46" t="n">
-        <v>6762697</v>
+        <v>6763025</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5258,7 +5257,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128373409</v>
+        <v>128374120</v>
       </c>
       <c r="B47" t="n">
         <v>79116</v>
@@ -5296,10 +5295,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440432</v>
+        <v>439959</v>
       </c>
       <c r="R47" t="n">
-        <v>6763202</v>
+        <v>6762821</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5359,7 +5358,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128373813</v>
+        <v>128373809</v>
       </c>
       <c r="B48" t="n">
         <v>79116</v>
@@ -5397,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440218</v>
+        <v>440239</v>
       </c>
       <c r="R48" t="n">
-        <v>6763088</v>
+        <v>6763111</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5460,48 +5459,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128373868</v>
+        <v>128374335</v>
       </c>
       <c r="B49" t="n">
-        <v>79116</v>
+        <v>96738</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440225</v>
+        <v>440203</v>
       </c>
       <c r="R49" t="n">
-        <v>6763025</v>
+        <v>6762697</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373593</v>
+        <v>128373782</v>
       </c>
       <c r="B50" t="n">
-        <v>79116</v>
+        <v>91514</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,24 +5572,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5599,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440325</v>
+        <v>440285</v>
       </c>
       <c r="R50" t="n">
-        <v>6763069</v>
+        <v>6762985</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5662,7 +5666,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373752</v>
+        <v>128373593</v>
       </c>
       <c r="B51" t="n">
         <v>79116</v>
@@ -5700,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440310</v>
+        <v>440325</v>
       </c>
       <c r="R51" t="n">
-        <v>6762992</v>
+        <v>6763069</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,10 +5767,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373782</v>
+        <v>128373752</v>
       </c>
       <c r="B52" t="n">
-        <v>91514</v>
+        <v>79116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5774,28 +5778,24 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440285</v>
+        <v>440310</v>
       </c>
       <c r="R52" t="n">
-        <v>6762985</v>
+        <v>6762992</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5969,10 +5969,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128373544</v>
+        <v>128374431</v>
       </c>
       <c r="B54" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,42 +5980,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440327</v>
+        <v>440332</v>
       </c>
       <c r="R54" t="n">
-        <v>6763083</v>
+        <v>6762821</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,17 +6045,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6180,7 +6171,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128374429</v>
+        <v>128373986</v>
       </c>
       <c r="B56" t="n">
         <v>79116</v>
@@ -6214,14 +6205,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440338</v>
+        <v>440031</v>
       </c>
       <c r="R56" t="n">
-        <v>6762836</v>
+        <v>6762895</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6281,7 +6272,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128374431</v>
+        <v>128374429</v>
       </c>
       <c r="B57" t="n">
         <v>79116</v>
@@ -6319,10 +6310,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440332</v>
+        <v>440338</v>
       </c>
       <c r="R57" t="n">
-        <v>6762821</v>
+        <v>6762836</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6382,10 +6373,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128373986</v>
+        <v>128373544</v>
       </c>
       <c r="B58" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6393,26 +6384,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6420,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440031</v>
+        <v>440327</v>
       </c>
       <c r="R58" t="n">
-        <v>6762895</v>
+        <v>6763083</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6458,13 +6454,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6483,42 +6483,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128373927</v>
+        <v>128373395</v>
       </c>
       <c r="B59" t="n">
-        <v>56907</v>
+        <v>79116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6526,10 +6521,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440114</v>
+        <v>440451</v>
       </c>
       <c r="R59" t="n">
-        <v>6763007</v>
+        <v>6763197</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6570,6 +6565,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6588,37 +6584,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128373395</v>
+        <v>128373927</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>56907</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6626,10 +6627,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440451</v>
+        <v>440114</v>
       </c>
       <c r="R60" t="n">
-        <v>6763197</v>
+        <v>6763007</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6670,7 +6671,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6891,37 +6891,43 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373958</v>
+        <v>128373935</v>
       </c>
       <c r="B63" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6929,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440085</v>
+        <v>440107</v>
       </c>
       <c r="R63" t="n">
-        <v>6762953</v>
+        <v>6762932</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6992,37 +6998,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373976</v>
+        <v>128373939</v>
       </c>
       <c r="B64" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7030,10 +7042,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440119</v>
+        <v>440091</v>
       </c>
       <c r="R64" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7093,43 +7105,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373935</v>
+        <v>128373958</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7137,10 +7143,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440107</v>
+        <v>440085</v>
       </c>
       <c r="R65" t="n">
-        <v>6762932</v>
+        <v>6762953</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7200,43 +7206,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373939</v>
+        <v>128373976</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440091</v>
+        <v>440119</v>
       </c>
       <c r="R66" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128374441</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128373617</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>128373817</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373860</v>
+        <v>128373899</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,31 +1090,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1122,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440187</v>
+        <v>440199</v>
       </c>
       <c r="R6" t="n">
-        <v>6763085</v>
+        <v>6762979</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,17 +1155,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,49 +1180,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128374324</v>
+        <v>128373673</v>
       </c>
       <c r="B7" t="n">
-        <v>96738</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440191</v>
+        <v>440297</v>
       </c>
       <c r="R7" t="n">
-        <v>6762689</v>
+        <v>6763071</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1291,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373899</v>
+        <v>128373873</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440199</v>
+        <v>440201</v>
       </c>
       <c r="R8" t="n">
-        <v>6762979</v>
+        <v>6763012</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1392,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373673</v>
+        <v>128373878</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440297</v>
+        <v>440202</v>
       </c>
       <c r="R9" t="n">
-        <v>6763071</v>
+        <v>6763032</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1493,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373873</v>
+        <v>128374165</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440201</v>
+        <v>440024</v>
       </c>
       <c r="R10" t="n">
-        <v>6763012</v>
+        <v>6762784</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1594,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373878</v>
+        <v>128373481</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440202</v>
+        <v>440418</v>
       </c>
       <c r="R11" t="n">
-        <v>6763032</v>
+        <v>6763099</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1695,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128374165</v>
+        <v>128373475</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440024</v>
+        <v>440406</v>
       </c>
       <c r="R12" t="n">
-        <v>6762784</v>
+        <v>6763080</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1796,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128373481</v>
+        <v>128374108</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440418</v>
+        <v>439941</v>
       </c>
       <c r="R13" t="n">
-        <v>6763099</v>
+        <v>6762833</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1897,48 +1887,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128373475</v>
+        <v>128374324</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>96751</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440406</v>
+        <v>440191</v>
       </c>
       <c r="R14" t="n">
-        <v>6763080</v>
+        <v>6762689</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1998,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128374108</v>
+        <v>128373860</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,26 +2000,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2036,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439941</v>
+        <v>440187</v>
       </c>
       <c r="R15" t="n">
-        <v>6762833</v>
+        <v>6763085</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2074,13 +2070,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>128374090</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,37 +2200,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128373503</v>
+        <v>128373765</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2238,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440401</v>
+        <v>440300</v>
       </c>
       <c r="R17" t="n">
-        <v>6763097</v>
+        <v>6762994</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2301,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128373653</v>
+        <v>128373503</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440307</v>
+        <v>440401</v>
       </c>
       <c r="R18" t="n">
-        <v>6763084</v>
+        <v>6763097</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2402,43 +2408,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128373765</v>
+        <v>128373653</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440300</v>
+        <v>440307</v>
       </c>
       <c r="R19" t="n">
-        <v>6762994</v>
+        <v>6763084</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2512,7 +2512,7 @@
         <v>128373363</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>128374175</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128373893</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>128373390</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>128373797</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128373738</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>128373743</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>128374000</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>128373960</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>128374454</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>128373992</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3620,54 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374425</v>
+        <v>128374114</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440328</v>
+        <v>439954</v>
       </c>
       <c r="R31" t="n">
-        <v>6762829</v>
+        <v>6762847</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3727,10 +3721,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374114</v>
+        <v>128374437</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3761,14 +3755,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439954</v>
+        <v>440322</v>
       </c>
       <c r="R32" t="n">
-        <v>6762847</v>
+        <v>6762821</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3828,10 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128374437</v>
+        <v>128373955</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,14 +3856,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440322</v>
+        <v>440100</v>
       </c>
       <c r="R33" t="n">
-        <v>6762821</v>
+        <v>6762947</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3929,10 +3923,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373955</v>
+        <v>128373374</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3967,10 +3961,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440100</v>
+        <v>440502</v>
       </c>
       <c r="R34" t="n">
-        <v>6762947</v>
+        <v>6763186</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4030,48 +4024,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128373374</v>
+        <v>128374425</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440502</v>
+        <v>440328</v>
       </c>
       <c r="R35" t="n">
-        <v>6763186</v>
+        <v>6762829</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4134,7 +4134,7 @@
         <v>128373433</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B37" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,31 +4243,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4275,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R37" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4313,17 +4308,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4342,10 +4333,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4353,26 +4344,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4380,10 +4376,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R38" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4418,13 +4414,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4443,49 +4443,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128374321</v>
+        <v>128374129</v>
       </c>
       <c r="B39" t="n">
-        <v>96738</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440185</v>
+        <v>439996</v>
       </c>
       <c r="R39" t="n">
-        <v>6762702</v>
+        <v>6762772</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4545,32 +4544,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128373466</v>
+        <v>128373380</v>
       </c>
       <c r="B40" t="n">
-        <v>92784</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4583,10 +4582,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440428</v>
+        <v>440499</v>
       </c>
       <c r="R40" t="n">
-        <v>6763185</v>
+        <v>6763177</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4619,11 +4618,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4651,10 +4645,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128374129</v>
+        <v>128373747</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,10 +4683,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439996</v>
+        <v>440332</v>
       </c>
       <c r="R41" t="n">
-        <v>6762772</v>
+        <v>6762998</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4752,32 +4746,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373380</v>
+        <v>128373466</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>92794</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4790,10 +4784,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440499</v>
+        <v>440428</v>
       </c>
       <c r="R42" t="n">
-        <v>6763177</v>
+        <v>6763185</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4826,6 +4820,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4853,48 +4852,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128373747</v>
+        <v>128374321</v>
       </c>
       <c r="B43" t="n">
-        <v>79116</v>
+        <v>96751</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440332</v>
+        <v>440185</v>
       </c>
       <c r="R43" t="n">
-        <v>6762998</v>
+        <v>6762702</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4957,7 +4957,7 @@
         <v>128373409</v>
       </c>
       <c r="B44" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>128373813</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>128373868</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>128374120</v>
       </c>
       <c r="B47" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>128373809</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>128374335</v>
       </c>
       <c r="B49" t="n">
-        <v>96738</v>
+        <v>96751</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373782</v>
+        <v>128373593</v>
       </c>
       <c r="B50" t="n">
-        <v>91514</v>
+        <v>79120</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,28 +5572,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5603,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440285</v>
+        <v>440325</v>
       </c>
       <c r="R50" t="n">
-        <v>6762985</v>
+        <v>6763069</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5666,10 +5662,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373593</v>
+        <v>128373752</v>
       </c>
       <c r="B51" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5704,10 +5700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440325</v>
+        <v>440310</v>
       </c>
       <c r="R51" t="n">
-        <v>6763069</v>
+        <v>6762992</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5767,10 +5763,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373752</v>
+        <v>128373403</v>
       </c>
       <c r="B52" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5805,10 +5801,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440310</v>
+        <v>440444</v>
       </c>
       <c r="R52" t="n">
-        <v>6762992</v>
+        <v>6763182</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5868,10 +5864,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373403</v>
+        <v>128373782</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>91524</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5879,24 +5875,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440444</v>
+        <v>440285</v>
       </c>
       <c r="R53" t="n">
-        <v>6763182</v>
+        <v>6762985</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5972,7 +5972,7 @@
         <v>128374431</v>
       </c>
       <c r="B54" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>128374197</v>
       </c>
       <c r="B55" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>128373986</v>
       </c>
       <c r="B56" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>128374429</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>128373395</v>
       </c>
       <c r="B59" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>128373803</v>
       </c>
       <c r="B61" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>128373428</v>
       </c>
       <c r="B62" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6891,43 +6891,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373935</v>
+        <v>128373958</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6935,10 +6929,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440107</v>
+        <v>440085</v>
       </c>
       <c r="R63" t="n">
-        <v>6762932</v>
+        <v>6762953</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6998,43 +6992,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373939</v>
+        <v>128373976</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7042,10 +7030,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440091</v>
+        <v>440119</v>
       </c>
       <c r="R64" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7105,37 +7093,43 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373958</v>
+        <v>128373935</v>
       </c>
       <c r="B65" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7143,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440085</v>
+        <v>440107</v>
       </c>
       <c r="R65" t="n">
-        <v>6762953</v>
+        <v>6762932</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7206,37 +7200,43 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373976</v>
+        <v>128373939</v>
       </c>
       <c r="B66" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440119</v>
+        <v>440091</v>
       </c>
       <c r="R66" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7310,7 +7310,7 @@
         <v>128373912</v>
       </c>
       <c r="B67" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>128373683</v>
       </c>
       <c r="B68" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>128373907</v>
       </c>
       <c r="B69" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>128373339</v>
       </c>
       <c r="B70" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>128373758</v>
       </c>
       <c r="B71" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -1079,48 +1079,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373899</v>
+        <v>128374324</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>96751</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440199</v>
+        <v>440191</v>
       </c>
       <c r="R6" t="n">
-        <v>6762979</v>
+        <v>6762689</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,7 +1181,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373673</v>
+        <v>128373899</v>
       </c>
       <c r="B7" t="n">
         <v>79120</v>
@@ -1218,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440297</v>
+        <v>440199</v>
       </c>
       <c r="R7" t="n">
-        <v>6763071</v>
+        <v>6762979</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,7 +1282,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373873</v>
+        <v>128373673</v>
       </c>
       <c r="B8" t="n">
         <v>79120</v>
@@ -1319,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440201</v>
+        <v>440297</v>
       </c>
       <c r="R8" t="n">
-        <v>6763012</v>
+        <v>6763071</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,7 +1383,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373878</v>
+        <v>128373873</v>
       </c>
       <c r="B9" t="n">
         <v>79120</v>
@@ -1420,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440202</v>
+        <v>440201</v>
       </c>
       <c r="R9" t="n">
-        <v>6763032</v>
+        <v>6763012</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1483,7 +1484,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128374165</v>
+        <v>128373878</v>
       </c>
       <c r="B10" t="n">
         <v>79120</v>
@@ -1521,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440024</v>
+        <v>440202</v>
       </c>
       <c r="R10" t="n">
-        <v>6762784</v>
+        <v>6763032</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1584,7 +1585,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373481</v>
+        <v>128374165</v>
       </c>
       <c r="B11" t="n">
         <v>79120</v>
@@ -1622,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440418</v>
+        <v>440024</v>
       </c>
       <c r="R11" t="n">
-        <v>6763099</v>
+        <v>6762784</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1685,7 +1686,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373475</v>
+        <v>128373481</v>
       </c>
       <c r="B12" t="n">
         <v>79120</v>
@@ -1723,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440406</v>
+        <v>440418</v>
       </c>
       <c r="R12" t="n">
-        <v>6763080</v>
+        <v>6763099</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1786,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374108</v>
+        <v>128373475</v>
       </c>
       <c r="B13" t="n">
         <v>79120</v>
@@ -1824,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439941</v>
+        <v>440406</v>
       </c>
       <c r="R13" t="n">
-        <v>6762833</v>
+        <v>6763080</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1887,49 +1888,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374324</v>
+        <v>128374108</v>
       </c>
       <c r="B14" t="n">
-        <v>96751</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440191</v>
+        <v>439941</v>
       </c>
       <c r="R14" t="n">
-        <v>6762689</v>
+        <v>6762833</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -3620,48 +3620,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374114</v>
+        <v>128374425</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439954</v>
+        <v>440328</v>
       </c>
       <c r="R31" t="n">
-        <v>6762847</v>
+        <v>6762829</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3721,7 +3727,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374437</v>
+        <v>128374114</v>
       </c>
       <c r="B32" t="n">
         <v>79120</v>
@@ -3755,14 +3761,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440322</v>
+        <v>439954</v>
       </c>
       <c r="R32" t="n">
-        <v>6762821</v>
+        <v>6762847</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3822,7 +3828,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128373955</v>
+        <v>128374437</v>
       </c>
       <c r="B33" t="n">
         <v>79120</v>
@@ -3856,14 +3862,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440100</v>
+        <v>440322</v>
       </c>
       <c r="R33" t="n">
-        <v>6762947</v>
+        <v>6762821</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3923,7 +3929,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373374</v>
+        <v>128373955</v>
       </c>
       <c r="B34" t="n">
         <v>79120</v>
@@ -3961,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440502</v>
+        <v>440100</v>
       </c>
       <c r="R34" t="n">
-        <v>6763186</v>
+        <v>6762947</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4024,54 +4030,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128374425</v>
+        <v>128373374</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440328</v>
+        <v>440502</v>
       </c>
       <c r="R35" t="n">
-        <v>6762829</v>
+        <v>6763186</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4443,32 +4443,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128374129</v>
+        <v>128373466</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>92794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439996</v>
+        <v>440428</v>
       </c>
       <c r="R39" t="n">
-        <v>6762772</v>
+        <v>6763185</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4517,6 +4517,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4544,7 +4549,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128373380</v>
+        <v>128374129</v>
       </c>
       <c r="B40" t="n">
         <v>79120</v>
@@ -4582,10 +4587,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440499</v>
+        <v>439996</v>
       </c>
       <c r="R40" t="n">
-        <v>6763177</v>
+        <v>6762772</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4645,7 +4650,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128373747</v>
+        <v>128373380</v>
       </c>
       <c r="B41" t="n">
         <v>79120</v>
@@ -4683,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440332</v>
+        <v>440499</v>
       </c>
       <c r="R41" t="n">
-        <v>6762998</v>
+        <v>6763177</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4746,32 +4751,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373466</v>
+        <v>128373747</v>
       </c>
       <c r="B42" t="n">
-        <v>92794</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4784,10 +4789,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440428</v>
+        <v>440332</v>
       </c>
       <c r="R42" t="n">
-        <v>6763185</v>
+        <v>6762998</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4820,11 +4825,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373593</v>
+        <v>128373782</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>91524</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,24 +5572,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5599,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440325</v>
+        <v>440285</v>
       </c>
       <c r="R50" t="n">
-        <v>6763069</v>
+        <v>6762985</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5662,7 +5666,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373752</v>
+        <v>128373593</v>
       </c>
       <c r="B51" t="n">
         <v>79120</v>
@@ -5700,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440310</v>
+        <v>440325</v>
       </c>
       <c r="R51" t="n">
-        <v>6762992</v>
+        <v>6763069</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,7 +5767,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373403</v>
+        <v>128373752</v>
       </c>
       <c r="B52" t="n">
         <v>79120</v>
@@ -5801,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440444</v>
+        <v>440310</v>
       </c>
       <c r="R52" t="n">
-        <v>6763182</v>
+        <v>6762992</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5864,10 +5868,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373782</v>
+        <v>128373403</v>
       </c>
       <c r="B53" t="n">
-        <v>91524</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5875,28 +5879,24 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440285</v>
+        <v>440444</v>
       </c>
       <c r="R53" t="n">
-        <v>6762985</v>
+        <v>6763182</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373935</v>
+        <v>128373939</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7127,7 +7127,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440107</v>
+        <v>440091</v>
       </c>
       <c r="R65" t="n">
-        <v>6762932</v>
+        <v>6762938</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7200,7 +7200,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373939</v>
+        <v>128373935</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7234,7 +7234,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440091</v>
+        <v>440107</v>
       </c>
       <c r="R66" t="n">
-        <v>6762938</v>
+        <v>6762932</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128373907</v>
+        <v>128373758</v>
       </c>
       <c r="B69" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7520,21 +7520,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440185</v>
+        <v>440315</v>
       </c>
       <c r="R69" t="n">
-        <v>6762972</v>
+        <v>6763002</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7610,7 +7610,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128373339</v>
+        <v>128373907</v>
       </c>
       <c r="B70" t="n">
         <v>79120</v>
@@ -7648,10 +7648,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440512</v>
+        <v>440185</v>
       </c>
       <c r="R70" t="n">
-        <v>6763195</v>
+        <v>6762972</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128373758</v>
+        <v>128373339</v>
       </c>
       <c r="B71" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7722,21 +7722,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440315</v>
+        <v>440512</v>
       </c>
       <c r="R71" t="n">
-        <v>6763002</v>
+        <v>6763195</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -1181,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373899</v>
+        <v>128373860</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,26 +1192,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1219,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440199</v>
+        <v>440187</v>
       </c>
       <c r="R7" t="n">
-        <v>6762979</v>
+        <v>6763085</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,13 +1262,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1282,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373673</v>
+        <v>128373899</v>
       </c>
       <c r="B8" t="n">
         <v>79120</v>
@@ -1320,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440297</v>
+        <v>440199</v>
       </c>
       <c r="R8" t="n">
-        <v>6763071</v>
+        <v>6762979</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1383,7 +1392,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373873</v>
+        <v>128373673</v>
       </c>
       <c r="B9" t="n">
         <v>79120</v>
@@ -1421,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440201</v>
+        <v>440297</v>
       </c>
       <c r="R9" t="n">
-        <v>6763012</v>
+        <v>6763071</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,7 +1493,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373878</v>
+        <v>128373873</v>
       </c>
       <c r="B10" t="n">
         <v>79120</v>
@@ -1522,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440202</v>
+        <v>440201</v>
       </c>
       <c r="R10" t="n">
-        <v>6763032</v>
+        <v>6763012</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1585,7 +1594,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128374165</v>
+        <v>128373878</v>
       </c>
       <c r="B11" t="n">
         <v>79120</v>
@@ -1623,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440024</v>
+        <v>440202</v>
       </c>
       <c r="R11" t="n">
-        <v>6762784</v>
+        <v>6763032</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1686,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373481</v>
+        <v>128374165</v>
       </c>
       <c r="B12" t="n">
         <v>79120</v>
@@ -1724,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440418</v>
+        <v>440024</v>
       </c>
       <c r="R12" t="n">
-        <v>6763099</v>
+        <v>6762784</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1787,7 +1796,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128373475</v>
+        <v>128373481</v>
       </c>
       <c r="B13" t="n">
         <v>79120</v>
@@ -1825,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440406</v>
+        <v>440418</v>
       </c>
       <c r="R13" t="n">
-        <v>6763080</v>
+        <v>6763099</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,7 +1897,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374108</v>
+        <v>128373475</v>
       </c>
       <c r="B14" t="n">
         <v>79120</v>
@@ -1926,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439941</v>
+        <v>440406</v>
       </c>
       <c r="R14" t="n">
-        <v>6762833</v>
+        <v>6763080</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1989,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128373860</v>
+        <v>128374108</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,31 +2009,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2032,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440187</v>
+        <v>439941</v>
       </c>
       <c r="R15" t="n">
-        <v>6763085</v>
+        <v>6762833</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2070,17 +2074,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -4954,48 +4954,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128373409</v>
+        <v>128374335</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>96751</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440432</v>
+        <v>440203</v>
       </c>
       <c r="R44" t="n">
-        <v>6763202</v>
+        <v>6762697</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5055,7 +5056,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373813</v>
+        <v>128373409</v>
       </c>
       <c r="B45" t="n">
         <v>79120</v>
@@ -5093,10 +5094,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440218</v>
+        <v>440432</v>
       </c>
       <c r="R45" t="n">
-        <v>6763088</v>
+        <v>6763202</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5156,7 +5157,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373868</v>
+        <v>128373813</v>
       </c>
       <c r="B46" t="n">
         <v>79120</v>
@@ -5194,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440225</v>
+        <v>440218</v>
       </c>
       <c r="R46" t="n">
-        <v>6763025</v>
+        <v>6763088</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5257,7 +5258,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128374120</v>
+        <v>128373868</v>
       </c>
       <c r="B47" t="n">
         <v>79120</v>
@@ -5295,10 +5296,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439959</v>
+        <v>440225</v>
       </c>
       <c r="R47" t="n">
-        <v>6762821</v>
+        <v>6763025</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5358,7 +5359,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128373809</v>
+        <v>128374120</v>
       </c>
       <c r="B48" t="n">
         <v>79120</v>
@@ -5396,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440239</v>
+        <v>439959</v>
       </c>
       <c r="R48" t="n">
-        <v>6763111</v>
+        <v>6762821</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5459,49 +5460,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128374335</v>
+        <v>128373809</v>
       </c>
       <c r="B49" t="n">
-        <v>96751</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440203</v>
+        <v>440239</v>
       </c>
       <c r="R49" t="n">
-        <v>6762697</v>
+        <v>6763111</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373782</v>
+        <v>128373593</v>
       </c>
       <c r="B50" t="n">
-        <v>91524</v>
+        <v>79120</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,28 +5572,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5603,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440285</v>
+        <v>440325</v>
       </c>
       <c r="R50" t="n">
-        <v>6762985</v>
+        <v>6763069</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5666,7 +5662,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373593</v>
+        <v>128373752</v>
       </c>
       <c r="B51" t="n">
         <v>79120</v>
@@ -5704,10 +5700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440325</v>
+        <v>440310</v>
       </c>
       <c r="R51" t="n">
-        <v>6763069</v>
+        <v>6762992</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5767,7 +5763,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373752</v>
+        <v>128373403</v>
       </c>
       <c r="B52" t="n">
         <v>79120</v>
@@ -5805,10 +5801,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440310</v>
+        <v>440444</v>
       </c>
       <c r="R52" t="n">
-        <v>6762992</v>
+        <v>6763182</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5868,10 +5864,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373403</v>
+        <v>128373782</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>91524</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5879,24 +5875,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440444</v>
+        <v>440285</v>
       </c>
       <c r="R53" t="n">
-        <v>6763182</v>
+        <v>6762985</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5969,10 +5969,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128374431</v>
+        <v>128373544</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,37 +5980,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440332</v>
+        <v>440327</v>
       </c>
       <c r="R54" t="n">
-        <v>6762821</v>
+        <v>6763083</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6045,13 +6050,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6070,7 +6079,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128374197</v>
+        <v>128374431</v>
       </c>
       <c r="B55" t="n">
         <v>79120</v>
@@ -6104,14 +6113,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440001</v>
+        <v>440332</v>
       </c>
       <c r="R55" t="n">
-        <v>6762789</v>
+        <v>6762821</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6171,7 +6180,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128373986</v>
+        <v>128374197</v>
       </c>
       <c r="B56" t="n">
         <v>79120</v>
@@ -6209,10 +6218,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440031</v>
+        <v>440001</v>
       </c>
       <c r="R56" t="n">
-        <v>6762895</v>
+        <v>6762789</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6272,7 +6281,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128374429</v>
+        <v>128373986</v>
       </c>
       <c r="B57" t="n">
         <v>79120</v>
@@ -6306,14 +6315,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440338</v>
+        <v>440031</v>
       </c>
       <c r="R57" t="n">
-        <v>6762836</v>
+        <v>6762895</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6373,10 +6382,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128373544</v>
+        <v>128374429</v>
       </c>
       <c r="B58" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6384,42 +6393,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440327</v>
+        <v>440338</v>
       </c>
       <c r="R58" t="n">
-        <v>6763083</v>
+        <v>6762836</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6454,17 +6458,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128374441</v>
+        <v>128373617</v>
       </c>
       <c r="B2" t="n">
         <v>79120</v>
@@ -709,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440344</v>
+        <v>440313</v>
       </c>
       <c r="R2" t="n">
-        <v>6762829</v>
+        <v>6763067</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373419</v>
+        <v>128374441</v>
       </c>
       <c r="B3" t="n">
         <v>79120</v>
@@ -810,14 +810,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440412</v>
+        <v>440344</v>
       </c>
       <c r="R3" t="n">
-        <v>6763165</v>
+        <v>6762829</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128373617</v>
+        <v>128373419</v>
       </c>
       <c r="B4" t="n">
         <v>79120</v>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440313</v>
+        <v>440412</v>
       </c>
       <c r="R4" t="n">
-        <v>6763067</v>
+        <v>6763165</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1079,49 +1079,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374324</v>
+        <v>128373873</v>
       </c>
       <c r="B6" t="n">
-        <v>96751</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440191</v>
+        <v>440201</v>
       </c>
       <c r="R6" t="n">
-        <v>6762689</v>
+        <v>6763012</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1181,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373860</v>
+        <v>128373878</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,31 +1191,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1224,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440187</v>
+        <v>440202</v>
       </c>
       <c r="R7" t="n">
-        <v>6763085</v>
+        <v>6763032</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,17 +1256,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,7 +1281,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373899</v>
+        <v>128373673</v>
       </c>
       <c r="B8" t="n">
         <v>79120</v>
@@ -1329,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440199</v>
+        <v>440297</v>
       </c>
       <c r="R8" t="n">
-        <v>6762979</v>
+        <v>6763071</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1392,7 +1382,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373673</v>
+        <v>128374165</v>
       </c>
       <c r="B9" t="n">
         <v>79120</v>
@@ -1430,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440297</v>
+        <v>440024</v>
       </c>
       <c r="R9" t="n">
-        <v>6763071</v>
+        <v>6762784</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1493,7 +1483,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373873</v>
+        <v>128373475</v>
       </c>
       <c r="B10" t="n">
         <v>79120</v>
@@ -1531,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440201</v>
+        <v>440406</v>
       </c>
       <c r="R10" t="n">
-        <v>6763012</v>
+        <v>6763080</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1594,7 +1584,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373878</v>
+        <v>128374108</v>
       </c>
       <c r="B11" t="n">
         <v>79120</v>
@@ -1632,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440202</v>
+        <v>439941</v>
       </c>
       <c r="R11" t="n">
-        <v>6763032</v>
+        <v>6762833</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1695,7 +1685,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128374165</v>
+        <v>128373481</v>
       </c>
       <c r="B12" t="n">
         <v>79120</v>
@@ -1733,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440024</v>
+        <v>440418</v>
       </c>
       <c r="R12" t="n">
-        <v>6762784</v>
+        <v>6763099</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1796,48 +1786,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128373481</v>
+        <v>128374324</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>96751</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440418</v>
+        <v>440191</v>
       </c>
       <c r="R13" t="n">
-        <v>6763099</v>
+        <v>6762689</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1897,7 +1888,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128373475</v>
+        <v>128373899</v>
       </c>
       <c r="B14" t="n">
         <v>79120</v>
@@ -1935,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440406</v>
+        <v>440199</v>
       </c>
       <c r="R14" t="n">
-        <v>6763080</v>
+        <v>6762979</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1998,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128374108</v>
+        <v>128373860</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,26 +2000,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2036,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439941</v>
+        <v>440187</v>
       </c>
       <c r="R15" t="n">
-        <v>6762833</v>
+        <v>6763085</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2074,13 +2070,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2200,43 +2200,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128373765</v>
+        <v>128373503</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2244,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440300</v>
+        <v>440401</v>
       </c>
       <c r="R17" t="n">
-        <v>6762994</v>
+        <v>6763097</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2307,7 +2301,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128373503</v>
+        <v>128373653</v>
       </c>
       <c r="B18" t="n">
         <v>79120</v>
@@ -2345,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440401</v>
+        <v>440307</v>
       </c>
       <c r="R18" t="n">
-        <v>6763097</v>
+        <v>6763084</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2408,37 +2402,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128373653</v>
+        <v>128373765</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440307</v>
+        <v>440300</v>
       </c>
       <c r="R19" t="n">
-        <v>6763084</v>
+        <v>6762994</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2509,7 +2509,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128373363</v>
+        <v>128374175</v>
       </c>
       <c r="B20" t="n">
         <v>79120</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440512</v>
+        <v>439993</v>
       </c>
       <c r="R20" t="n">
-        <v>6763183</v>
+        <v>6762757</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128374175</v>
+        <v>128373363</v>
       </c>
       <c r="B21" t="n">
         <v>79120</v>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439993</v>
+        <v>440512</v>
       </c>
       <c r="R21" t="n">
-        <v>6762757</v>
+        <v>6763183</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128373738</v>
+        <v>128373743</v>
       </c>
       <c r="B25" t="n">
         <v>79120</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440357</v>
+        <v>440346</v>
       </c>
       <c r="R25" t="n">
-        <v>6763022</v>
+        <v>6763007</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128373743</v>
+        <v>128373738</v>
       </c>
       <c r="B26" t="n">
         <v>79120</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440346</v>
+        <v>440357</v>
       </c>
       <c r="R26" t="n">
-        <v>6763007</v>
+        <v>6763022</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128374000</v>
+        <v>128373960</v>
       </c>
       <c r="B27" t="n">
         <v>79120</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440054</v>
+        <v>440101</v>
       </c>
       <c r="R27" t="n">
-        <v>6762902</v>
+        <v>6762969</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3317,7 +3317,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128373960</v>
+        <v>128374000</v>
       </c>
       <c r="B28" t="n">
         <v>79120</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440101</v>
+        <v>440054</v>
       </c>
       <c r="R28" t="n">
-        <v>6762969</v>
+        <v>6762902</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3620,54 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374425</v>
+        <v>128374114</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440328</v>
+        <v>439954</v>
       </c>
       <c r="R31" t="n">
-        <v>6762829</v>
+        <v>6762847</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3727,7 +3721,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374114</v>
+        <v>128374437</v>
       </c>
       <c r="B32" t="n">
         <v>79120</v>
@@ -3761,14 +3755,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439954</v>
+        <v>440322</v>
       </c>
       <c r="R32" t="n">
-        <v>6762847</v>
+        <v>6762821</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3828,7 +3822,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128374437</v>
+        <v>128373955</v>
       </c>
       <c r="B33" t="n">
         <v>79120</v>
@@ -3862,14 +3856,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440322</v>
+        <v>440100</v>
       </c>
       <c r="R33" t="n">
-        <v>6762821</v>
+        <v>6762947</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3929,7 +3923,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373955</v>
+        <v>128373374</v>
       </c>
       <c r="B34" t="n">
         <v>79120</v>
@@ -3967,10 +3961,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440100</v>
+        <v>440502</v>
       </c>
       <c r="R34" t="n">
-        <v>6762947</v>
+        <v>6763186</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4030,48 +4024,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128373374</v>
+        <v>128374425</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440502</v>
+        <v>440328</v>
       </c>
       <c r="R35" t="n">
-        <v>6763186</v>
+        <v>6762829</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128373466</v>
+        <v>128374321</v>
       </c>
       <c r="B39" t="n">
-        <v>92794</v>
+        <v>96751</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4454,37 +4454,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440428</v>
+        <v>440185</v>
       </c>
       <c r="R39" t="n">
-        <v>6763185</v>
+        <v>6762702</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4517,11 +4518,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4549,7 +4545,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374129</v>
+        <v>128373380</v>
       </c>
       <c r="B40" t="n">
         <v>79120</v>
@@ -4587,10 +4583,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439996</v>
+        <v>440499</v>
       </c>
       <c r="R40" t="n">
-        <v>6762772</v>
+        <v>6763177</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,7 +4646,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128373380</v>
+        <v>128373747</v>
       </c>
       <c r="B41" t="n">
         <v>79120</v>
@@ -4688,10 +4684,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440499</v>
+        <v>440332</v>
       </c>
       <c r="R41" t="n">
-        <v>6763177</v>
+        <v>6762998</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4751,7 +4747,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373747</v>
+        <v>128374129</v>
       </c>
       <c r="B42" t="n">
         <v>79120</v>
@@ -4789,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440332</v>
+        <v>439996</v>
       </c>
       <c r="R42" t="n">
-        <v>6762998</v>
+        <v>6762772</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4852,10 +4848,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128374321</v>
+        <v>128373466</v>
       </c>
       <c r="B43" t="n">
-        <v>96751</v>
+        <v>92794</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4863,38 +4859,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440185</v>
+        <v>440428</v>
       </c>
       <c r="R43" t="n">
-        <v>6762702</v>
+        <v>6763185</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4927,6 +4922,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4954,49 +4954,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128374335</v>
+        <v>128373409</v>
       </c>
       <c r="B44" t="n">
-        <v>96751</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440203</v>
+        <v>440432</v>
       </c>
       <c r="R44" t="n">
-        <v>6762697</v>
+        <v>6763202</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5056,7 +5055,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373409</v>
+        <v>128373813</v>
       </c>
       <c r="B45" t="n">
         <v>79120</v>
@@ -5094,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440432</v>
+        <v>440218</v>
       </c>
       <c r="R45" t="n">
-        <v>6763202</v>
+        <v>6763088</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5157,7 +5156,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373813</v>
+        <v>128373868</v>
       </c>
       <c r="B46" t="n">
         <v>79120</v>
@@ -5195,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440218</v>
+        <v>440225</v>
       </c>
       <c r="R46" t="n">
-        <v>6763088</v>
+        <v>6763025</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5258,7 +5257,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128373868</v>
+        <v>128374120</v>
       </c>
       <c r="B47" t="n">
         <v>79120</v>
@@ -5296,10 +5295,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440225</v>
+        <v>439959</v>
       </c>
       <c r="R47" t="n">
-        <v>6763025</v>
+        <v>6762821</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5359,7 +5358,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128374120</v>
+        <v>128373809</v>
       </c>
       <c r="B48" t="n">
         <v>79120</v>
@@ -5397,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439959</v>
+        <v>440239</v>
       </c>
       <c r="R48" t="n">
-        <v>6762821</v>
+        <v>6763111</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5460,48 +5459,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128373809</v>
+        <v>128374335</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>96751</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440239</v>
+        <v>440203</v>
       </c>
       <c r="R49" t="n">
-        <v>6763111</v>
+        <v>6762697</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373593</v>
+        <v>128373782</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>91524</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,24 +5572,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5599,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440325</v>
+        <v>440285</v>
       </c>
       <c r="R50" t="n">
-        <v>6763069</v>
+        <v>6762985</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5662,7 +5666,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373752</v>
+        <v>128373403</v>
       </c>
       <c r="B51" t="n">
         <v>79120</v>
@@ -5700,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440310</v>
+        <v>440444</v>
       </c>
       <c r="R51" t="n">
-        <v>6762992</v>
+        <v>6763182</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,7 +5767,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373403</v>
+        <v>128373593</v>
       </c>
       <c r="B52" t="n">
         <v>79120</v>
@@ -5801,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440444</v>
+        <v>440325</v>
       </c>
       <c r="R52" t="n">
-        <v>6763182</v>
+        <v>6763069</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5864,10 +5868,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373782</v>
+        <v>128373752</v>
       </c>
       <c r="B53" t="n">
-        <v>91524</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5875,28 +5879,24 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440285</v>
+        <v>440310</v>
       </c>
       <c r="R53" t="n">
-        <v>6762985</v>
+        <v>6762992</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6180,7 +6180,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128374197</v>
+        <v>128373986</v>
       </c>
       <c r="B56" t="n">
         <v>79120</v>
@@ -6218,10 +6218,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440001</v>
+        <v>440031</v>
       </c>
       <c r="R56" t="n">
-        <v>6762789</v>
+        <v>6762895</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6281,7 +6281,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128373986</v>
+        <v>128374429</v>
       </c>
       <c r="B57" t="n">
         <v>79120</v>
@@ -6315,14 +6315,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440031</v>
+        <v>440338</v>
       </c>
       <c r="R57" t="n">
-        <v>6762895</v>
+        <v>6762836</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6382,7 +6382,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128374429</v>
+        <v>128374197</v>
       </c>
       <c r="B58" t="n">
         <v>79120</v>
@@ -6416,14 +6416,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440338</v>
+        <v>440001</v>
       </c>
       <c r="R58" t="n">
-        <v>6762836</v>
+        <v>6762789</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6689,7 +6689,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128373803</v>
+        <v>128373428</v>
       </c>
       <c r="B61" t="n">
         <v>79120</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440226</v>
+        <v>440418</v>
       </c>
       <c r="R61" t="n">
-        <v>6763108</v>
+        <v>6763150</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128373428</v>
+        <v>128373803</v>
       </c>
       <c r="B62" t="n">
         <v>79120</v>
@@ -6828,10 +6828,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440418</v>
+        <v>440226</v>
       </c>
       <c r="R62" t="n">
-        <v>6763150</v>
+        <v>6763108</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6891,37 +6891,43 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373958</v>
+        <v>128373939</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6929,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440085</v>
+        <v>440091</v>
       </c>
       <c r="R63" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6992,37 +6998,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373976</v>
+        <v>128373935</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7030,10 +7042,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440119</v>
+        <v>440107</v>
       </c>
       <c r="R64" t="n">
-        <v>6762953</v>
+        <v>6762932</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7093,43 +7105,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373939</v>
+        <v>128373958</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7137,10 +7143,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440091</v>
+        <v>440085</v>
       </c>
       <c r="R65" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7200,43 +7206,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373935</v>
+        <v>128373976</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440107</v>
+        <v>440119</v>
       </c>
       <c r="R66" t="n">
-        <v>6762932</v>
+        <v>6762953</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7408,7 +7408,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128373683</v>
+        <v>128373339</v>
       </c>
       <c r="B68" t="n">
         <v>79120</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440312</v>
+        <v>440512</v>
       </c>
       <c r="R68" t="n">
-        <v>6763096</v>
+        <v>6763195</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128373758</v>
+        <v>128373683</v>
       </c>
       <c r="B69" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7520,21 +7520,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440315</v>
+        <v>440312</v>
       </c>
       <c r="R69" t="n">
-        <v>6763002</v>
+        <v>6763096</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128373339</v>
+        <v>128373758</v>
       </c>
       <c r="B71" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7722,21 +7722,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440512</v>
+        <v>440315</v>
       </c>
       <c r="R71" t="n">
-        <v>6763195</v>
+        <v>6763002</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7815,7 +7815,7 @@
         <v>128464117</v>
       </c>
       <c r="B72" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>128463867</v>
       </c>
       <c r="B73" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>128532195</v>
       </c>
       <c r="B74" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>128463474</v>
       </c>
       <c r="B75" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>128535275</v>
       </c>
       <c r="B76" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373617</v>
+        <v>128373817</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440313</v>
+        <v>440235</v>
       </c>
       <c r="R2" t="n">
-        <v>6763067</v>
+        <v>6763090</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128374441</v>
+        <v>128373617</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,14 +810,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440344</v>
+        <v>440313</v>
       </c>
       <c r="R3" t="n">
-        <v>6762829</v>
+        <v>6763067</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128373419</v>
+        <v>128374441</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440412</v>
+        <v>440344</v>
       </c>
       <c r="R4" t="n">
-        <v>6763165</v>
+        <v>6762829</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373817</v>
+        <v>128373419</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440235</v>
+        <v>440412</v>
       </c>
       <c r="R5" t="n">
-        <v>6763090</v>
+        <v>6763165</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1082,7 +1082,7 @@
         <v>128373873</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128373878</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128373673</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128374165</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128373475</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128374108</v>
+        <v>128373899</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439941</v>
+        <v>440199</v>
       </c>
       <c r="R11" t="n">
-        <v>6762833</v>
+        <v>6762979</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373481</v>
+        <v>128374108</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440418</v>
+        <v>439941</v>
       </c>
       <c r="R12" t="n">
-        <v>6763099</v>
+        <v>6762833</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1786,49 +1786,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374324</v>
+        <v>128373481</v>
       </c>
       <c r="B13" t="n">
-        <v>96751</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440191</v>
+        <v>440418</v>
       </c>
       <c r="R13" t="n">
-        <v>6762689</v>
+        <v>6763099</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128373899</v>
+        <v>128373860</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,26 +1898,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1926,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440199</v>
+        <v>440187</v>
       </c>
       <c r="R14" t="n">
-        <v>6762979</v>
+        <v>6763085</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1964,13 +1968,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1989,53 +1997,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128373860</v>
+        <v>128374324</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>96755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440187</v>
+        <v>440191</v>
       </c>
       <c r="R15" t="n">
-        <v>6763085</v>
+        <v>6762689</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2070,17 +2074,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>128374090</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>128373503</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128373653</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128374175</v>
+        <v>128373363</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439993</v>
+        <v>440512</v>
       </c>
       <c r="R20" t="n">
-        <v>6762757</v>
+        <v>6763183</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128373363</v>
+        <v>128374175</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440512</v>
+        <v>439993</v>
       </c>
       <c r="R21" t="n">
-        <v>6763183</v>
+        <v>6762757</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2711,10 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128373893</v>
+        <v>128373390</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440212</v>
+        <v>440462</v>
       </c>
       <c r="R22" t="n">
-        <v>6762957</v>
+        <v>6763204</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2812,10 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128373390</v>
+        <v>128373893</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440462</v>
+        <v>440212</v>
       </c>
       <c r="R23" t="n">
-        <v>6763204</v>
+        <v>6762957</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128373797</v>
+        <v>128373738</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440232</v>
+        <v>440357</v>
       </c>
       <c r="R24" t="n">
-        <v>6763126</v>
+        <v>6763022</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3014,10 +3014,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128373743</v>
+        <v>128373797</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440346</v>
+        <v>440232</v>
       </c>
       <c r="R25" t="n">
-        <v>6763007</v>
+        <v>6763126</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3115,10 +3115,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128373738</v>
+        <v>128373743</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440357</v>
+        <v>440346</v>
       </c>
       <c r="R26" t="n">
-        <v>6763022</v>
+        <v>6763007</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3219,7 +3219,7 @@
         <v>128373960</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128374000</v>
+        <v>128373992</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440054</v>
+        <v>440043</v>
       </c>
       <c r="R28" t="n">
-        <v>6762902</v>
+        <v>6762922</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3421,7 +3421,7 @@
         <v>128374454</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128373992</v>
+        <v>128374000</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440043</v>
+        <v>440054</v>
       </c>
       <c r="R30" t="n">
-        <v>6762922</v>
+        <v>6762902</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3620,48 +3620,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374114</v>
+        <v>128374425</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439954</v>
+        <v>440328</v>
       </c>
       <c r="R31" t="n">
-        <v>6762847</v>
+        <v>6762829</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3724,7 +3730,7 @@
         <v>128374437</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3822,10 +3828,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128373955</v>
+        <v>128374114</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3860,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440100</v>
+        <v>439954</v>
       </c>
       <c r="R33" t="n">
-        <v>6762947</v>
+        <v>6762847</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3923,10 +3929,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373374</v>
+        <v>128373955</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3961,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440502</v>
+        <v>440100</v>
       </c>
       <c r="R34" t="n">
-        <v>6763186</v>
+        <v>6762947</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4024,54 +4030,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128374425</v>
+        <v>128373374</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440328</v>
+        <v>440502</v>
       </c>
       <c r="R35" t="n">
-        <v>6762829</v>
+        <v>6763186</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4134,7 +4134,7 @@
         <v>128373433</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,26 +4243,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4270,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R37" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4308,13 +4313,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4333,10 +4342,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4344,31 +4353,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4376,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R38" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4414,17 +4418,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4443,49 +4443,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128374321</v>
+        <v>128373380</v>
       </c>
       <c r="B39" t="n">
-        <v>96751</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440185</v>
+        <v>440499</v>
       </c>
       <c r="R39" t="n">
-        <v>6762702</v>
+        <v>6763177</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4545,10 +4544,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128373380</v>
+        <v>128373747</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4583,10 +4582,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440499</v>
+        <v>440332</v>
       </c>
       <c r="R40" t="n">
-        <v>6763177</v>
+        <v>6762998</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4646,10 +4645,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128373747</v>
+        <v>128374129</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4684,10 +4683,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440332</v>
+        <v>439996</v>
       </c>
       <c r="R41" t="n">
-        <v>6762998</v>
+        <v>6762772</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4747,32 +4746,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128374129</v>
+        <v>128373466</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>92798</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4785,10 +4784,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439996</v>
+        <v>440428</v>
       </c>
       <c r="R42" t="n">
-        <v>6762772</v>
+        <v>6763185</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4821,6 +4820,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4848,10 +4852,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128373466</v>
+        <v>128374321</v>
       </c>
       <c r="B43" t="n">
-        <v>92794</v>
+        <v>96755</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4859,37 +4863,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440428</v>
+        <v>440185</v>
       </c>
       <c r="R43" t="n">
-        <v>6763185</v>
+        <v>6762702</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4922,11 +4927,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4954,48 +4954,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128373409</v>
+        <v>128374335</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>96755</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440432</v>
+        <v>440203</v>
       </c>
       <c r="R44" t="n">
-        <v>6763202</v>
+        <v>6762697</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5055,10 +5056,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373813</v>
+        <v>128373868</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5093,10 +5094,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440218</v>
+        <v>440225</v>
       </c>
       <c r="R45" t="n">
-        <v>6763088</v>
+        <v>6763025</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5156,10 +5157,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373868</v>
+        <v>128373813</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5194,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440225</v>
+        <v>440218</v>
       </c>
       <c r="R46" t="n">
-        <v>6763025</v>
+        <v>6763088</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5260,7 +5261,7 @@
         <v>128374120</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5361,7 +5362,7 @@
         <v>128373809</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5459,49 +5460,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128374335</v>
+        <v>128373409</v>
       </c>
       <c r="B49" t="n">
-        <v>96751</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440203</v>
+        <v>440432</v>
       </c>
       <c r="R49" t="n">
-        <v>6762697</v>
+        <v>6763202</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373782</v>
+        <v>128373403</v>
       </c>
       <c r="B50" t="n">
-        <v>91524</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,28 +5572,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5603,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440285</v>
+        <v>440444</v>
       </c>
       <c r="R50" t="n">
-        <v>6762985</v>
+        <v>6763182</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5666,10 +5662,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373403</v>
+        <v>128373593</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5704,10 +5700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440444</v>
+        <v>440325</v>
       </c>
       <c r="R51" t="n">
-        <v>6763182</v>
+        <v>6763069</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5767,10 +5763,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373593</v>
+        <v>128373752</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5805,10 +5801,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440325</v>
+        <v>440310</v>
       </c>
       <c r="R52" t="n">
-        <v>6763069</v>
+        <v>6762992</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5868,10 +5864,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373752</v>
+        <v>128373782</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>91528</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5879,24 +5875,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440310</v>
+        <v>440285</v>
       </c>
       <c r="R53" t="n">
-        <v>6762992</v>
+        <v>6762985</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5969,10 +5969,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128373544</v>
+        <v>128374431</v>
       </c>
       <c r="B54" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,42 +5980,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440327</v>
+        <v>440332</v>
       </c>
       <c r="R54" t="n">
-        <v>6763083</v>
+        <v>6762821</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,17 +6045,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6079,10 +6070,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128374431</v>
+        <v>128374197</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6113,14 +6104,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440332</v>
+        <v>440001</v>
       </c>
       <c r="R55" t="n">
-        <v>6762821</v>
+        <v>6762789</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6180,10 +6171,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128373986</v>
+        <v>128374429</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6214,14 +6205,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440031</v>
+        <v>440338</v>
       </c>
       <c r="R56" t="n">
-        <v>6762895</v>
+        <v>6762836</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6281,10 +6272,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128374429</v>
+        <v>128373986</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6315,14 +6306,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440338</v>
+        <v>440031</v>
       </c>
       <c r="R57" t="n">
-        <v>6762836</v>
+        <v>6762895</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6382,10 +6373,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128374197</v>
+        <v>128373544</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6393,26 +6384,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6420,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440001</v>
+        <v>440327</v>
       </c>
       <c r="R58" t="n">
-        <v>6762789</v>
+        <v>6763083</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6458,13 +6454,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>128373395</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>128373927</v>
       </c>
       <c r="B60" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128373428</v>
+        <v>128373803</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440418</v>
+        <v>440226</v>
       </c>
       <c r="R61" t="n">
-        <v>6763150</v>
+        <v>6763108</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128373803</v>
+        <v>128373428</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6828,10 +6828,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440226</v>
+        <v>440418</v>
       </c>
       <c r="R62" t="n">
-        <v>6763108</v>
+        <v>6763150</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6891,7 +6891,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373939</v>
+        <v>128373935</v>
       </c>
       <c r="B63" t="n">
         <v>8450</v>
@@ -6925,7 +6925,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440091</v>
+        <v>440107</v>
       </c>
       <c r="R63" t="n">
-        <v>6762938</v>
+        <v>6762932</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6998,7 +6998,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373935</v>
+        <v>128373939</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7032,7 +7032,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7042,10 +7042,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440107</v>
+        <v>440091</v>
       </c>
       <c r="R64" t="n">
-        <v>6762932</v>
+        <v>6762938</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7105,10 +7105,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373958</v>
+        <v>128373976</v>
       </c>
       <c r="B65" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440085</v>
+        <v>440119</v>
       </c>
       <c r="R65" t="n">
         <v>6762953</v>
@@ -7206,10 +7206,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373976</v>
+        <v>128373958</v>
       </c>
       <c r="B66" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440119</v>
+        <v>440085</v>
       </c>
       <c r="R66" t="n">
         <v>6762953</v>
@@ -7310,7 +7310,7 @@
         <v>128373912</v>
       </c>
       <c r="B67" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>128373339</v>
       </c>
       <c r="B68" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128373683</v>
+        <v>128373907</v>
       </c>
       <c r="B69" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440312</v>
+        <v>440185</v>
       </c>
       <c r="R69" t="n">
-        <v>6763096</v>
+        <v>6762972</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7610,10 +7610,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128373907</v>
+        <v>128373683</v>
       </c>
       <c r="B70" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7648,10 +7648,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440185</v>
+        <v>440312</v>
       </c>
       <c r="R70" t="n">
-        <v>6762972</v>
+        <v>6763096</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7714,7 +7714,7 @@
         <v>128373758</v>
       </c>
       <c r="B71" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -2200,37 +2200,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128373503</v>
+        <v>128373765</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2238,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440401</v>
+        <v>440300</v>
       </c>
       <c r="R17" t="n">
-        <v>6763097</v>
+        <v>6762994</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2301,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128373653</v>
+        <v>128373503</v>
       </c>
       <c r="B18" t="n">
         <v>79124</v>
@@ -2339,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440307</v>
+        <v>440401</v>
       </c>
       <c r="R18" t="n">
-        <v>6763084</v>
+        <v>6763097</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2402,43 +2408,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128373765</v>
+        <v>128373653</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440300</v>
+        <v>440307</v>
       </c>
       <c r="R19" t="n">
-        <v>6762994</v>
+        <v>6763084</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2509,7 +2509,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128373363</v>
+        <v>128374175</v>
       </c>
       <c r="B20" t="n">
         <v>79124</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440512</v>
+        <v>439993</v>
       </c>
       <c r="R20" t="n">
-        <v>6763183</v>
+        <v>6762757</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128374175</v>
+        <v>128373363</v>
       </c>
       <c r="B21" t="n">
         <v>79124</v>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439993</v>
+        <v>440512</v>
       </c>
       <c r="R21" t="n">
-        <v>6762757</v>
+        <v>6763183</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128373960</v>
+        <v>128373992</v>
       </c>
       <c r="B27" t="n">
         <v>79124</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440101</v>
+        <v>440043</v>
       </c>
       <c r="R27" t="n">
-        <v>6762969</v>
+        <v>6762922</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3317,7 +3317,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128373992</v>
+        <v>128374454</v>
       </c>
       <c r="B28" t="n">
         <v>79124</v>
@@ -3351,14 +3351,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440043</v>
+        <v>440400</v>
       </c>
       <c r="R28" t="n">
-        <v>6762922</v>
+        <v>6762886</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128374454</v>
+        <v>128374000</v>
       </c>
       <c r="B29" t="n">
         <v>79124</v>
@@ -3452,14 +3452,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440400</v>
+        <v>440054</v>
       </c>
       <c r="R29" t="n">
-        <v>6762886</v>
+        <v>6762902</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128374000</v>
+        <v>128373960</v>
       </c>
       <c r="B30" t="n">
         <v>79124</v>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440054</v>
+        <v>440101</v>
       </c>
       <c r="R30" t="n">
-        <v>6762902</v>
+        <v>6762969</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,31 +4243,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4275,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R37" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4313,17 +4308,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4342,10 +4333,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4353,26 +4344,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4380,10 +4376,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R38" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4418,13 +4414,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4443,32 +4443,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128373380</v>
+        <v>128373466</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>92798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440499</v>
+        <v>440428</v>
       </c>
       <c r="R39" t="n">
-        <v>6763177</v>
+        <v>6763185</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4517,6 +4517,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4544,7 +4549,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128373747</v>
+        <v>128373380</v>
       </c>
       <c r="B40" t="n">
         <v>79124</v>
@@ -4582,10 +4587,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440332</v>
+        <v>440499</v>
       </c>
       <c r="R40" t="n">
-        <v>6762998</v>
+        <v>6763177</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4645,7 +4650,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128374129</v>
+        <v>128373747</v>
       </c>
       <c r="B41" t="n">
         <v>79124</v>
@@ -4683,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439996</v>
+        <v>440332</v>
       </c>
       <c r="R41" t="n">
-        <v>6762772</v>
+        <v>6762998</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4746,32 +4751,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373466</v>
+        <v>128374129</v>
       </c>
       <c r="B42" t="n">
-        <v>92798</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4784,10 +4789,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440428</v>
+        <v>439996</v>
       </c>
       <c r="R42" t="n">
-        <v>6763185</v>
+        <v>6762772</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4820,11 +4825,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6891,43 +6891,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373935</v>
+        <v>128373976</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6935,10 +6929,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440107</v>
+        <v>440119</v>
       </c>
       <c r="R63" t="n">
-        <v>6762932</v>
+        <v>6762953</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6998,43 +6992,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373939</v>
+        <v>128373958</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7042,10 +7030,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440091</v>
+        <v>440085</v>
       </c>
       <c r="R64" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7105,37 +7093,43 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373976</v>
+        <v>128373935</v>
       </c>
       <c r="B65" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7143,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440119</v>
+        <v>440107</v>
       </c>
       <c r="R65" t="n">
-        <v>6762953</v>
+        <v>6762932</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7206,37 +7200,43 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373958</v>
+        <v>128373939</v>
       </c>
       <c r="B66" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440085</v>
+        <v>440091</v>
       </c>
       <c r="R66" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373817</v>
+        <v>128374441</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440235</v>
+        <v>440344</v>
       </c>
       <c r="R2" t="n">
-        <v>6763090</v>
+        <v>6762829</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373617</v>
+        <v>128373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440313</v>
+        <v>440412</v>
       </c>
       <c r="R3" t="n">
-        <v>6763067</v>
+        <v>6763165</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128374441</v>
+        <v>128373617</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440344</v>
+        <v>440313</v>
       </c>
       <c r="R4" t="n">
-        <v>6762829</v>
+        <v>6763067</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373419</v>
+        <v>128373817</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440412</v>
+        <v>440235</v>
       </c>
       <c r="R5" t="n">
-        <v>6763165</v>
+        <v>6763090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373873</v>
+        <v>128373899</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440201</v>
+        <v>440199</v>
       </c>
       <c r="R6" t="n">
-        <v>6763012</v>
+        <v>6762979</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373878</v>
+        <v>128373673</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440202</v>
+        <v>440297</v>
       </c>
       <c r="R7" t="n">
-        <v>6763032</v>
+        <v>6763071</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373673</v>
+        <v>128373873</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440297</v>
+        <v>440201</v>
       </c>
       <c r="R8" t="n">
-        <v>6763071</v>
+        <v>6763012</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128374165</v>
+        <v>128373878</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440024</v>
+        <v>440202</v>
       </c>
       <c r="R9" t="n">
-        <v>6762784</v>
+        <v>6763032</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373475</v>
+        <v>128374165</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440406</v>
+        <v>440024</v>
       </c>
       <c r="R10" t="n">
-        <v>6763080</v>
+        <v>6762784</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373899</v>
+        <v>128373481</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440199</v>
+        <v>440418</v>
       </c>
       <c r="R11" t="n">
-        <v>6762979</v>
+        <v>6763099</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128374108</v>
+        <v>128373475</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439941</v>
+        <v>440406</v>
       </c>
       <c r="R12" t="n">
-        <v>6762833</v>
+        <v>6763080</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128373481</v>
+        <v>128374108</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440418</v>
+        <v>439941</v>
       </c>
       <c r="R13" t="n">
-        <v>6763099</v>
+        <v>6762833</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
         <v>128373860</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128374324</v>
       </c>
       <c r="B15" t="n">
-        <v>96755</v>
+        <v>96762</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>128374090</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>128373503</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>128373653</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128374175</v>
+        <v>128373363</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439993</v>
+        <v>440512</v>
       </c>
       <c r="R20" t="n">
-        <v>6762757</v>
+        <v>6763183</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128373363</v>
+        <v>128374175</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440512</v>
+        <v>439993</v>
       </c>
       <c r="R21" t="n">
-        <v>6763183</v>
+        <v>6762757</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2711,10 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128373390</v>
+        <v>128373893</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440462</v>
+        <v>440212</v>
       </c>
       <c r="R22" t="n">
-        <v>6763204</v>
+        <v>6762957</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2812,10 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128373893</v>
+        <v>128373390</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440212</v>
+        <v>440462</v>
       </c>
       <c r="R23" t="n">
-        <v>6762957</v>
+        <v>6763204</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128373738</v>
+        <v>128373797</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440357</v>
+        <v>440232</v>
       </c>
       <c r="R24" t="n">
-        <v>6763022</v>
+        <v>6763126</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3014,10 +3014,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128373797</v>
+        <v>128373738</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440232</v>
+        <v>440357</v>
       </c>
       <c r="R25" t="n">
-        <v>6763126</v>
+        <v>6763022</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3118,7 +3118,7 @@
         <v>128373743</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128373992</v>
+        <v>128374000</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440043</v>
+        <v>440054</v>
       </c>
       <c r="R27" t="n">
-        <v>6762922</v>
+        <v>6762902</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128374454</v>
+        <v>128373960</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,14 +3351,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440400</v>
+        <v>440101</v>
       </c>
       <c r="R28" t="n">
-        <v>6762886</v>
+        <v>6762969</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128374000</v>
+        <v>128374454</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3452,14 +3452,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440054</v>
+        <v>440400</v>
       </c>
       <c r="R29" t="n">
-        <v>6762902</v>
+        <v>6762886</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128373960</v>
+        <v>128373992</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440101</v>
+        <v>440043</v>
       </c>
       <c r="R30" t="n">
-        <v>6762969</v>
+        <v>6762922</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3620,54 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374425</v>
+        <v>128374114</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440328</v>
+        <v>439954</v>
       </c>
       <c r="R31" t="n">
-        <v>6762829</v>
+        <v>6762847</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3730,7 +3724,7 @@
         <v>128374437</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3828,10 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128374114</v>
+        <v>128373955</v>
       </c>
       <c r="B33" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3866,10 +3860,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439954</v>
+        <v>440100</v>
       </c>
       <c r="R33" t="n">
-        <v>6762847</v>
+        <v>6762947</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3929,10 +3923,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373955</v>
+        <v>128373374</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3967,10 +3961,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440100</v>
+        <v>440502</v>
       </c>
       <c r="R34" t="n">
-        <v>6762947</v>
+        <v>6763186</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4030,48 +4024,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128373374</v>
+        <v>128374425</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440502</v>
+        <v>440328</v>
       </c>
       <c r="R35" t="n">
-        <v>6763186</v>
+        <v>6762829</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4134,7 +4134,7 @@
         <v>128373433</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373886</v>
+        <v>128373732</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,26 +4243,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4270,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440198</v>
+        <v>440292</v>
       </c>
       <c r="R37" t="n">
-        <v>6762963</v>
+        <v>6763172</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4308,13 +4313,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4333,10 +4342,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373732</v>
+        <v>128373886</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4344,31 +4353,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4376,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440292</v>
+        <v>440198</v>
       </c>
       <c r="R38" t="n">
-        <v>6763172</v>
+        <v>6762963</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4414,17 +4418,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>128373466</v>
       </c>
       <c r="B39" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4549,48 +4549,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128373380</v>
+        <v>128374321</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>96762</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440499</v>
+        <v>440185</v>
       </c>
       <c r="R40" t="n">
-        <v>6763177</v>
+        <v>6762702</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,10 +4651,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128373747</v>
+        <v>128374129</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4688,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440332</v>
+        <v>439996</v>
       </c>
       <c r="R41" t="n">
-        <v>6762998</v>
+        <v>6762772</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4751,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128374129</v>
+        <v>128373380</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4789,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439996</v>
+        <v>440499</v>
       </c>
       <c r="R42" t="n">
-        <v>6762772</v>
+        <v>6763177</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4852,49 +4853,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128374321</v>
+        <v>128373747</v>
       </c>
       <c r="B43" t="n">
-        <v>96755</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440185</v>
+        <v>440332</v>
       </c>
       <c r="R43" t="n">
-        <v>6762702</v>
+        <v>6762998</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4954,49 +4954,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128374335</v>
+        <v>128373409</v>
       </c>
       <c r="B44" t="n">
-        <v>96755</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440203</v>
+        <v>440432</v>
       </c>
       <c r="R44" t="n">
-        <v>6762697</v>
+        <v>6763202</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5056,10 +5055,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373868</v>
+        <v>128373813</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5094,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440225</v>
+        <v>440218</v>
       </c>
       <c r="R45" t="n">
-        <v>6763025</v>
+        <v>6763088</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5157,10 +5156,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373813</v>
+        <v>128373868</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5195,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440218</v>
+        <v>440225</v>
       </c>
       <c r="R46" t="n">
-        <v>6763088</v>
+        <v>6763025</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5261,7 +5260,7 @@
         <v>128374120</v>
       </c>
       <c r="B47" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5362,7 +5361,7 @@
         <v>128373809</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5460,48 +5459,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128373409</v>
+        <v>128374335</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>96762</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440432</v>
+        <v>440203</v>
       </c>
       <c r="R49" t="n">
-        <v>6763202</v>
+        <v>6762697</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373403</v>
+        <v>128373593</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440444</v>
+        <v>440325</v>
       </c>
       <c r="R50" t="n">
-        <v>6763182</v>
+        <v>6763069</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373593</v>
+        <v>128373752</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5700,10 +5700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440325</v>
+        <v>440310</v>
       </c>
       <c r="R51" t="n">
-        <v>6763069</v>
+        <v>6762992</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373752</v>
+        <v>128373403</v>
       </c>
       <c r="B52" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440310</v>
+        <v>440444</v>
       </c>
       <c r="R52" t="n">
-        <v>6762992</v>
+        <v>6763182</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5867,7 +5867,7 @@
         <v>128373782</v>
       </c>
       <c r="B53" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>128374431</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>128374197</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6171,10 +6171,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128374429</v>
+        <v>128373986</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6205,14 +6205,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440338</v>
+        <v>440031</v>
       </c>
       <c r="R56" t="n">
-        <v>6762836</v>
+        <v>6762895</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6272,10 +6272,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128373986</v>
+        <v>128374429</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6306,14 +6306,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440031</v>
+        <v>440338</v>
       </c>
       <c r="R57" t="n">
-        <v>6762895</v>
+        <v>6762836</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6376,7 +6376,7 @@
         <v>128373544</v>
       </c>
       <c r="B58" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>128373395</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>128373927</v>
       </c>
       <c r="B60" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>128373803</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>128373428</v>
       </c>
       <c r="B62" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6891,37 +6891,43 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373976</v>
+        <v>128373935</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6929,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440119</v>
+        <v>440107</v>
       </c>
       <c r="R63" t="n">
-        <v>6762953</v>
+        <v>6762932</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6992,37 +6998,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373958</v>
+        <v>128373939</v>
       </c>
       <c r="B64" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7030,10 +7042,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440085</v>
+        <v>440091</v>
       </c>
       <c r="R64" t="n">
-        <v>6762953</v>
+        <v>6762938</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7093,43 +7105,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373935</v>
+        <v>128373958</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7137,10 +7143,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440107</v>
+        <v>440085</v>
       </c>
       <c r="R65" t="n">
-        <v>6762932</v>
+        <v>6762953</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7200,43 +7206,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373939</v>
+        <v>128373976</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440091</v>
+        <v>440119</v>
       </c>
       <c r="R66" t="n">
-        <v>6762938</v>
+        <v>6762953</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7310,7 +7310,7 @@
         <v>128373912</v>
       </c>
       <c r="B67" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128373339</v>
+        <v>128373683</v>
       </c>
       <c r="B68" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440512</v>
+        <v>440312</v>
       </c>
       <c r="R68" t="n">
-        <v>6763195</v>
+        <v>6763096</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7512,7 +7512,7 @@
         <v>128373907</v>
       </c>
       <c r="B69" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7610,10 +7610,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128373683</v>
+        <v>128373339</v>
       </c>
       <c r="B70" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7648,10 +7648,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440312</v>
+        <v>440512</v>
       </c>
       <c r="R70" t="n">
-        <v>6763096</v>
+        <v>6763195</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7714,7 +7714,7 @@
         <v>128373758</v>
       </c>
       <c r="B71" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>128464117</v>
       </c>
       <c r="B72" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>128463867</v>
       </c>
       <c r="B73" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>128532195</v>
       </c>
       <c r="B74" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>128463474</v>
       </c>
       <c r="B75" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>128535275</v>
       </c>
       <c r="B76" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128374441</v>
+        <v>128374321</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440344</v>
+        <v>440185</v>
       </c>
       <c r="R2" t="n">
-        <v>6762829</v>
+        <v>6762702</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,48 +777,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373419</v>
+        <v>128374324</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440412</v>
+        <v>440191</v>
       </c>
       <c r="R3" t="n">
-        <v>6763165</v>
+        <v>6762689</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,48 +879,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128373617</v>
+        <v>128374335</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440313</v>
+        <v>440203</v>
       </c>
       <c r="R4" t="n">
-        <v>6763067</v>
+        <v>6762697</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373817</v>
+        <v>128373466</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440235</v>
+        <v>440428</v>
       </c>
       <c r="R5" t="n">
-        <v>6763090</v>
+        <v>6763185</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1052,6 +1055,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373899</v>
+        <v>127276666</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,40 +1098,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440199</v>
+        <v>440591</v>
       </c>
       <c r="R6" t="n">
-        <v>6762979</v>
+        <v>6763079</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1147,12 +1152,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1161,29 +1176,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128373673</v>
+        <v>128373782</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,24 +1205,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1218,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440297</v>
+        <v>440285</v>
       </c>
       <c r="R7" t="n">
-        <v>6763071</v>
+        <v>6762985</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,14 +1299,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373873</v>
+        <v>127276668</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1310,22 +1328,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440201</v>
+        <v>440591</v>
       </c>
       <c r="R8" t="n">
-        <v>6763012</v>
+        <v>6763079</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1349,12 +1364,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1363,33 +1388,32 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373878</v>
+        <v>127276679</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1411,22 +1435,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440202</v>
+        <v>440602</v>
       </c>
       <c r="R9" t="n">
-        <v>6763032</v>
+        <v>6763069</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1450,12 +1471,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1464,33 +1495,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128374165</v>
+        <v>128373339</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1521,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440024</v>
+        <v>440512</v>
       </c>
       <c r="R10" t="n">
-        <v>6762784</v>
+        <v>6763195</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1584,14 +1614,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373481</v>
+        <v>128373363</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1622,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440418</v>
+        <v>440512</v>
       </c>
       <c r="R11" t="n">
-        <v>6763099</v>
+        <v>6763183</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1685,14 +1715,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373475</v>
+        <v>128373374</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1723,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440406</v>
+        <v>440502</v>
       </c>
       <c r="R12" t="n">
-        <v>6763080</v>
+        <v>6763186</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1786,14 +1816,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374108</v>
+        <v>128373380</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1824,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439941</v>
+        <v>440499</v>
       </c>
       <c r="R13" t="n">
-        <v>6762833</v>
+        <v>6763177</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1887,42 +1917,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128373860</v>
+        <v>128373390</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1930,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440187</v>
+        <v>440462</v>
       </c>
       <c r="R14" t="n">
-        <v>6763085</v>
+        <v>6763204</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1968,17 +1993,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1997,49 +2018,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128374324</v>
+        <v>128373395</v>
       </c>
       <c r="B15" t="n">
-        <v>96762</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440191</v>
+        <v>440451</v>
       </c>
       <c r="R15" t="n">
-        <v>6762689</v>
+        <v>6763197</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2099,14 +2119,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128374090</v>
+        <v>128373403</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2137,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439942</v>
+        <v>440444</v>
       </c>
       <c r="R16" t="n">
-        <v>6762855</v>
+        <v>6763182</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2200,43 +2220,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128373765</v>
+        <v>128373409</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2244,10 +2258,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440300</v>
+        <v>440432</v>
       </c>
       <c r="R17" t="n">
-        <v>6762994</v>
+        <v>6763202</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2307,14 +2321,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128373503</v>
+        <v>128373419</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2345,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440401</v>
+        <v>440412</v>
       </c>
       <c r="R18" t="n">
-        <v>6763097</v>
+        <v>6763165</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2408,14 +2422,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128373653</v>
+        <v>128373428</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2446,10 +2460,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440307</v>
+        <v>440418</v>
       </c>
       <c r="R19" t="n">
-        <v>6763084</v>
+        <v>6763150</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2509,14 +2523,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128373363</v>
+        <v>128373433</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2547,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440512</v>
+        <v>440433</v>
       </c>
       <c r="R20" t="n">
-        <v>6763183</v>
+        <v>6763160</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2610,14 +2624,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128374175</v>
+        <v>128373475</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2648,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439993</v>
+        <v>440406</v>
       </c>
       <c r="R21" t="n">
-        <v>6762757</v>
+        <v>6763080</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2711,14 +2725,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128373893</v>
+        <v>128373481</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2749,10 +2763,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440212</v>
+        <v>440418</v>
       </c>
       <c r="R22" t="n">
-        <v>6762957</v>
+        <v>6763099</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2812,14 +2826,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128373390</v>
+        <v>128373503</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2850,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440462</v>
+        <v>440401</v>
       </c>
       <c r="R23" t="n">
-        <v>6763204</v>
+        <v>6763097</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2913,14 +2927,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128373797</v>
+        <v>128373531</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2951,10 +2965,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440232</v>
+        <v>440356</v>
       </c>
       <c r="R24" t="n">
-        <v>6763126</v>
+        <v>6763054</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3014,14 +3028,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128373738</v>
+        <v>128373593</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3052,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440357</v>
+        <v>440325</v>
       </c>
       <c r="R25" t="n">
-        <v>6763022</v>
+        <v>6763069</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3115,14 +3129,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128373743</v>
+        <v>128373617</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3153,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440346</v>
+        <v>440313</v>
       </c>
       <c r="R26" t="n">
-        <v>6763007</v>
+        <v>6763067</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3216,14 +3230,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128374000</v>
+        <v>128373653</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3254,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440054</v>
+        <v>440307</v>
       </c>
       <c r="R27" t="n">
-        <v>6762902</v>
+        <v>6763084</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3317,14 +3331,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128373960</v>
+        <v>128373673</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3355,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440101</v>
+        <v>440297</v>
       </c>
       <c r="R28" t="n">
-        <v>6762969</v>
+        <v>6763071</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3418,14 +3432,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128374454</v>
+        <v>128373683</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3452,14 +3466,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440400</v>
+        <v>440312</v>
       </c>
       <c r="R29" t="n">
-        <v>6762886</v>
+        <v>6763096</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3519,14 +3533,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128373992</v>
+        <v>128373738</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3557,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440043</v>
+        <v>440357</v>
       </c>
       <c r="R30" t="n">
-        <v>6762922</v>
+        <v>6763022</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3620,14 +3634,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374114</v>
+        <v>128373743</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3658,10 +3672,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439954</v>
+        <v>440346</v>
       </c>
       <c r="R31" t="n">
-        <v>6762847</v>
+        <v>6763007</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3721,14 +3735,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374437</v>
+        <v>128373747</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3755,14 +3769,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440322</v>
+        <v>440332</v>
       </c>
       <c r="R32" t="n">
-        <v>6762821</v>
+        <v>6762998</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3822,14 +3836,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128373955</v>
+        <v>128373752</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3860,10 +3874,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440100</v>
+        <v>440310</v>
       </c>
       <c r="R33" t="n">
-        <v>6762947</v>
+        <v>6762992</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3923,14 +3937,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128373374</v>
+        <v>128373797</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3961,10 +3975,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440502</v>
+        <v>440232</v>
       </c>
       <c r="R34" t="n">
-        <v>6763186</v>
+        <v>6763126</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4024,54 +4038,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128374425</v>
+        <v>128373803</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440328</v>
+        <v>440226</v>
       </c>
       <c r="R35" t="n">
-        <v>6762829</v>
+        <v>6763108</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4131,14 +4139,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128373433</v>
+        <v>128373809</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4169,10 +4177,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440433</v>
+        <v>440239</v>
       </c>
       <c r="R36" t="n">
-        <v>6763160</v>
+        <v>6763111</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4232,42 +4240,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373732</v>
+        <v>128373813</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4275,10 +4278,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440292</v>
+        <v>440218</v>
       </c>
       <c r="R37" t="n">
-        <v>6763172</v>
+        <v>6763088</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4313,17 +4316,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4342,14 +4341,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373886</v>
+        <v>128373817</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4380,10 +4379,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440198</v>
+        <v>440235</v>
       </c>
       <c r="R38" t="n">
-        <v>6762963</v>
+        <v>6763090</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4443,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128373466</v>
+        <v>128373868</v>
       </c>
       <c r="B39" t="n">
-        <v>92803</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4481,10 +4480,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440428</v>
+        <v>440225</v>
       </c>
       <c r="R39" t="n">
-        <v>6763185</v>
+        <v>6763025</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4517,11 +4516,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar från förra året.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4549,49 +4543,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374321</v>
+        <v>128373873</v>
       </c>
       <c r="B40" t="n">
-        <v>96762</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440185</v>
+        <v>440201</v>
       </c>
       <c r="R40" t="n">
-        <v>6762702</v>
+        <v>6763012</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4651,14 +4644,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128374129</v>
+        <v>128373878</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4689,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439996</v>
+        <v>440202</v>
       </c>
       <c r="R41" t="n">
-        <v>6762772</v>
+        <v>6763032</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4752,14 +4745,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128373380</v>
+        <v>128373886</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4790,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440499</v>
+        <v>440198</v>
       </c>
       <c r="R42" t="n">
-        <v>6763177</v>
+        <v>6762963</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4853,14 +4846,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128373747</v>
+        <v>128373893</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4891,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440332</v>
+        <v>440212</v>
       </c>
       <c r="R43" t="n">
-        <v>6762998</v>
+        <v>6762957</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4954,14 +4947,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128373409</v>
+        <v>128373899</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4992,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440432</v>
+        <v>440199</v>
       </c>
       <c r="R44" t="n">
-        <v>6763202</v>
+        <v>6762979</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5055,14 +5048,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128373813</v>
+        <v>128373907</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5093,10 +5086,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440218</v>
+        <v>440185</v>
       </c>
       <c r="R45" t="n">
-        <v>6763088</v>
+        <v>6762972</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5156,14 +5149,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128373868</v>
+        <v>128373912</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5194,10 +5187,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440225</v>
+        <v>440171</v>
       </c>
       <c r="R46" t="n">
-        <v>6763025</v>
+        <v>6762953</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5257,14 +5250,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128374120</v>
+        <v>128373955</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5295,10 +5288,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439959</v>
+        <v>440100</v>
       </c>
       <c r="R47" t="n">
-        <v>6762821</v>
+        <v>6762947</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5358,14 +5351,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128373809</v>
+        <v>128373958</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5396,10 +5389,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440239</v>
+        <v>440085</v>
       </c>
       <c r="R48" t="n">
-        <v>6763111</v>
+        <v>6762953</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5459,49 +5452,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128374335</v>
+        <v>128373960</v>
       </c>
       <c r="B49" t="n">
-        <v>96762</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440203</v>
+        <v>440101</v>
       </c>
       <c r="R49" t="n">
-        <v>6762697</v>
+        <v>6762969</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5561,14 +5553,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128373593</v>
+        <v>128373976</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5599,10 +5591,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440325</v>
+        <v>440119</v>
       </c>
       <c r="R50" t="n">
-        <v>6763069</v>
+        <v>6762953</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5662,14 +5654,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128373752</v>
+        <v>128373986</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5700,10 +5692,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440310</v>
+        <v>440031</v>
       </c>
       <c r="R51" t="n">
-        <v>6762992</v>
+        <v>6762895</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,14 +5755,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128373403</v>
+        <v>128373992</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5801,10 +5793,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440444</v>
+        <v>440043</v>
       </c>
       <c r="R52" t="n">
-        <v>6763182</v>
+        <v>6762922</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5864,39 +5856,35 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128373782</v>
+        <v>128374000</v>
       </c>
       <c r="B53" t="n">
-        <v>91533</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -5906,10 +5894,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440285</v>
+        <v>440054</v>
       </c>
       <c r="R53" t="n">
-        <v>6762985</v>
+        <v>6762902</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5969,14 +5957,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128374431</v>
+        <v>128374090</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6003,14 +5991,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440332</v>
+        <v>439942</v>
       </c>
       <c r="R54" t="n">
-        <v>6762821</v>
+        <v>6762855</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6070,14 +6058,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128374197</v>
+        <v>128374108</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6108,10 +6096,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440001</v>
+        <v>439941</v>
       </c>
       <c r="R55" t="n">
-        <v>6762789</v>
+        <v>6762833</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6171,14 +6159,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128373986</v>
+        <v>128374114</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6209,10 +6197,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440031</v>
+        <v>439954</v>
       </c>
       <c r="R56" t="n">
-        <v>6762895</v>
+        <v>6762847</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6272,14 +6260,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128374429</v>
+        <v>128374120</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6306,14 +6294,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dovsjövasseln, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440338</v>
+        <v>439959</v>
       </c>
       <c r="R57" t="n">
-        <v>6762836</v>
+        <v>6762821</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6373,42 +6361,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128373544</v>
+        <v>128374129</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6416,10 +6399,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440327</v>
+        <v>439996</v>
       </c>
       <c r="R58" t="n">
-        <v>6763083</v>
+        <v>6762772</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6454,17 +6437,13 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6483,14 +6462,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128373395</v>
+        <v>128374165</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6521,10 +6500,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440451</v>
+        <v>440024</v>
       </c>
       <c r="R59" t="n">
-        <v>6763197</v>
+        <v>6762784</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6584,42 +6563,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128373927</v>
+        <v>128374175</v>
       </c>
       <c r="B60" t="n">
-        <v>56913</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6627,10 +6601,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440114</v>
+        <v>439993</v>
       </c>
       <c r="R60" t="n">
-        <v>6763007</v>
+        <v>6762757</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6671,6 +6645,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6689,14 +6664,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128373803</v>
+        <v>128374197</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -6727,10 +6702,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440226</v>
+        <v>440001</v>
       </c>
       <c r="R61" t="n">
-        <v>6763108</v>
+        <v>6762789</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6790,14 +6765,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128373428</v>
+        <v>128374429</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6824,14 +6799,14 @@
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440418</v>
+        <v>440338</v>
       </c>
       <c r="R62" t="n">
-        <v>6763150</v>
+        <v>6762836</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6891,54 +6866,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128373935</v>
+        <v>128374431</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440107</v>
+        <v>440332</v>
       </c>
       <c r="R63" t="n">
-        <v>6762932</v>
+        <v>6762821</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6998,54 +6967,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128373939</v>
+        <v>128374437</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440091</v>
+        <v>440322</v>
       </c>
       <c r="R64" t="n">
-        <v>6762938</v>
+        <v>6762821</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7105,14 +7068,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128373958</v>
+        <v>128374441</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -7139,14 +7102,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440085</v>
+        <v>440344</v>
       </c>
       <c r="R65" t="n">
-        <v>6762953</v>
+        <v>6762829</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7206,14 +7169,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128373976</v>
+        <v>128374454</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -7240,14 +7203,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440119</v>
+        <v>440400</v>
       </c>
       <c r="R66" t="n">
-        <v>6762953</v>
+        <v>6762886</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7307,51 +7270,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128373912</v>
+        <v>128532195</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>57950</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Skarpmyrbäcken, Skarpmyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440171</v>
+        <v>440078</v>
       </c>
       <c r="R67" t="n">
-        <v>6762953</v>
+        <v>6762917</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7378,40 +7338,54 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128373683</v>
+        <v>128373544</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7419,26 +7393,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7446,10 +7425,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440312</v>
+        <v>440327</v>
       </c>
       <c r="R68" t="n">
-        <v>6763096</v>
+        <v>6763083</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7484,13 +7463,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7509,10 +7492,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128373907</v>
+        <v>128373732</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7520,26 +7503,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7547,10 +7535,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440185</v>
+        <v>440292</v>
       </c>
       <c r="R69" t="n">
-        <v>6762972</v>
+        <v>6763172</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7585,13 +7573,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7610,10 +7602,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128373339</v>
+        <v>128373860</v>
       </c>
       <c r="B70" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7621,26 +7613,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7648,10 +7645,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440512</v>
+        <v>440187</v>
       </c>
       <c r="R70" t="n">
-        <v>6763195</v>
+        <v>6763085</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7686,13 +7683,17 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7711,10 +7712,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128373758</v>
+        <v>128463474</v>
       </c>
       <c r="B71" t="n">
-        <v>78787</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7722,40 +7723,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Dlr</t>
+          <t>Skarpmyrbäcken, Skarpmyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440315</v>
+        <v>440318</v>
       </c>
       <c r="R71" t="n">
-        <v>6763002</v>
+        <v>6763131</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7782,68 +7785,82 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128464117</v>
+        <v>128463867</v>
       </c>
       <c r="B72" t="n">
-        <v>56913</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7852,10 +7869,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440375</v>
+        <v>440308</v>
       </c>
       <c r="R72" t="n">
-        <v>6763136</v>
+        <v>6763123</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7887,7 +7904,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7897,12 +7914,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Tjäderspillning nedanför betad Tall</t>
+          <t>Färska ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7929,10 +7946,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128463867</v>
+        <v>128463926</v>
       </c>
       <c r="B73" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7969,10 +7986,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440308</v>
+        <v>440369</v>
       </c>
       <c r="R73" t="n">
-        <v>6763123</v>
+        <v>6763073</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8019,7 +8036,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack. Kåda</t>
+          <t>Ringhack Färska</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8046,10 +8063,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128532195</v>
+        <v>128535275</v>
       </c>
       <c r="B74" t="n">
-        <v>57720</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8057,16 +8074,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8075,19 +8092,27 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Skarpmyrbäcken, Skarpmyrbäcken, Dlr</t>
+          <t>venjan, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440078</v>
+        <v>440421</v>
       </c>
       <c r="R74" t="n">
-        <v>6762917</v>
+        <v>6762924</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8116,7 +8141,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8126,12 +8151,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Födohål</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8158,53 +8183,64 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128463474</v>
+        <v>128373522</v>
       </c>
       <c r="B75" t="n">
-        <v>57723</v>
+        <v>57141</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skarpmyrbäcken, Skarpmyrbäcken, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440318</v>
+        <v>440372</v>
       </c>
       <c r="R75" t="n">
-        <v>6763131</v>
+        <v>6763069</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8231,24 +8267,9 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8263,44 +8284,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128535275</v>
+        <v>128373927</v>
       </c>
       <c r="B76" t="n">
-        <v>57723</v>
+        <v>57141</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8308,23 +8329,23 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>venjan, Dlr</t>
+          <t>Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440421</v>
+        <v>440114</v>
       </c>
       <c r="R76" t="n">
-        <v>6762924</v>
+        <v>6763007</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8351,24 +8372,9 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8383,15 +8389,661 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128464117</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skarpmyrbäcken, Skarpmyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>440375</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6763136</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Tjäderspillning nedanför betad Tall</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
           <t>FREDRIK Månsson</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
+      <c r="AX77" t="inlineStr">
         <is>
           <t>FREDRIK Månsson</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128373765</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Skarpmyrrönningen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>440300</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6762994</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128373935</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Skarpmyrrönningen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>440107</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6762932</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128373939</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Skarpmyrrönningen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>440091</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6762938</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128374425</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Dovsjövasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>440328</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6762829</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128373758</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Skarpmyrrönningen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>440315</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6763002</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40313-2025 artfynd.xlsx
+++ b/artfynd/A 40313-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374321</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374324</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374335</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373466</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127276666</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373782</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127276668</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127276679</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373339</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373363</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373374</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1914,6 +1974,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373380</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373390</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373395</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373403</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373409</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2419,6 +2504,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373419</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2520,6 +2610,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373428</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2621,6 +2716,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373433</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2722,6 +2822,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373475</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2823,6 +2928,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373481</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2924,6 +3034,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373503</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3025,6 +3140,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373531</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3126,6 +3246,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373593</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3227,6 +3352,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373617</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3328,6 +3458,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373653</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3429,6 +3564,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373673</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3530,6 +3670,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373683</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3631,6 +3776,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373738</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3732,6 +3882,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373743</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3833,6 +3988,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373747</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3934,6 +4094,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373752</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4035,6 +4200,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373797</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4136,6 +4306,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373803</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4237,6 +4412,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373809</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4338,6 +4518,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373813</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4439,6 +4624,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373817</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4540,6 +4730,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373868</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4641,6 +4836,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373873</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4742,6 +4942,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373878</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4843,6 +5048,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373886</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4944,6 +5154,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373893</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5045,6 +5260,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373899</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5146,6 +5366,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373907</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5247,6 +5472,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373912</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5348,6 +5578,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373955</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5449,6 +5684,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373958</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5550,6 +5790,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373960</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5651,6 +5896,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373976</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5752,6 +6002,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373986</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5853,6 +6108,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373992</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5954,6 +6214,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374000</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6055,6 +6320,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374090</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6156,6 +6426,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374108</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6257,6 +6532,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374114</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6358,6 +6638,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374120</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6459,6 +6744,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374129</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6560,6 +6850,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374165</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6661,6 +6956,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374175</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6762,6 +7062,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374197</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6863,6 +7168,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374429</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6964,6 +7274,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374431</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7065,6 +7380,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374437</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7166,6 +7486,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374441</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7267,6 +7592,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374454</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7379,6 +7709,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532195</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7489,6 +7824,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373544</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7599,6 +7939,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373732</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7709,6 +8054,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373860</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7826,6 +8176,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128463474</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7943,6 +8298,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128463867</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8060,6 +8420,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128463926</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8180,6 +8545,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128535275</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8293,6 +8663,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373522</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8398,6 +8773,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373927</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8515,6 +8895,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128464117</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8622,6 +9007,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373765</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8729,6 +9119,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373935</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8836,6 +9231,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373939</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8943,6 +9343,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374425</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9044,8 +9449,96 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373758</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>